--- a/Dados/Processados/pib_munic_forecast.xlsx
+++ b/Dados/Processados/pib_munic_forecast.xlsx
@@ -1537,88 +1537,88 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.009263029693289924</v>
+        <v>0.002901327757004211</v>
       </c>
       <c r="C4">
-        <v>0.08259187461073782</v>
+        <v>0.08756907348531356</v>
       </c>
       <c r="D4">
-        <v>0.04689990309808997</v>
+        <v>0.04635802247289154</v>
       </c>
       <c r="E4">
-        <v>0.03136933119137471</v>
+        <v>0.02842594520243511</v>
       </c>
       <c r="F4">
-        <v>0.04372471844065605</v>
+        <v>0.04269185634796901</v>
       </c>
       <c r="G4">
-        <v>-0.001284352406772014</v>
+        <v>-0.009277004886210239</v>
       </c>
       <c r="H4">
-        <v>-0.0005128665556767657</v>
+        <v>-0.008386223530700596</v>
       </c>
       <c r="I4">
-        <v>0.08088760647165916</v>
+        <v>0.08560127293404596</v>
       </c>
       <c r="J4">
-        <v>0.03550716506267423</v>
+        <v>0.03320361579680463</v>
       </c>
       <c r="K4">
-        <v>0.01671934103396196</v>
+        <v>0.0115106147759644</v>
       </c>
       <c r="L4">
-        <v>0.0153454002633543</v>
+        <v>0.009924220391291816</v>
       </c>
       <c r="M4">
-        <v>0.07541675075078998</v>
+        <v>0.07928445420313202</v>
       </c>
       <c r="N4">
-        <v>-0.1039407668221769</v>
+        <v>-0.1278072667891268</v>
       </c>
       <c r="O4">
-        <v>-0.04655284352712684</v>
+        <v>-0.06154540076776678</v>
       </c>
       <c r="P4">
-        <v>0.05543308177897475</v>
+        <v>0.05621069373234942</v>
       </c>
       <c r="Q4">
-        <v>0.04170518224912879</v>
+        <v>0.04036003758079977</v>
       </c>
       <c r="R4">
-        <v>0.02158363904675202</v>
+        <v>0.01712708327151047</v>
       </c>
       <c r="S4">
-        <v>-0.04394602795842116</v>
+        <v>-0.05853549112061164</v>
       </c>
       <c r="T4">
-        <v>0.12614516963572</v>
+        <v>0.1378570510602585</v>
       </c>
       <c r="U4">
-        <v>0.01539139102201326</v>
+        <v>0.009977322739547434</v>
       </c>
       <c r="V4">
-        <v>0.02051458935576243</v>
+        <v>0.01589272552989415</v>
       </c>
       <c r="W4">
-        <v>0.06661472263431928</v>
+        <v>0.06912136109430486</v>
       </c>
       <c r="X4">
-        <v>0.02225435991813929</v>
+        <v>0.0179015182739603</v>
       </c>
       <c r="Y4">
-        <v>0.002909067576084317</v>
+        <v>-0.004435152853218362</v>
       </c>
       <c r="Z4">
-        <v>0.02553960923137112</v>
+        <v>0.02169476844474857</v>
       </c>
       <c r="AA4">
-        <v>0.03173139089053222</v>
+        <v>0.02884399049663341</v>
       </c>
       <c r="AB4">
-        <v>0.02711687882356147</v>
+        <v>0.02351593255727356</v>
       </c>
       <c r="AC4">
-        <v>0.02426843182479751</v>
+        <v>0.0202270278093068</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1626,88 +1626,88 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.01976169525081049</v>
+        <v>0.01568868105223251</v>
       </c>
       <c r="C5">
-        <v>0.0485141135261493</v>
+        <v>0.05701616663577484</v>
       </c>
       <c r="D5">
-        <v>0.03451920476741407</v>
+        <v>0.03690048855850867</v>
       </c>
       <c r="E5">
-        <v>0.02842962978474783</v>
+        <v>0.02814759619668963</v>
       </c>
       <c r="F5">
-        <v>0.03327420714779037</v>
+        <v>0.03511098269212126</v>
       </c>
       <c r="G5">
-        <v>0.01562604110008427</v>
+        <v>0.009744270197607072</v>
       </c>
       <c r="H5">
-        <v>0.01592854257694741</v>
+        <v>0.01017907276984095</v>
       </c>
       <c r="I5">
-        <v>0.04784586584758176</v>
+        <v>0.05605565625234311</v>
       </c>
       <c r="J5">
-        <v>0.03005208450028856</v>
+        <v>0.03047964260838123</v>
       </c>
       <c r="K5">
-        <v>0.02268533304572607</v>
+        <v>0.0198909918861879</v>
       </c>
       <c r="L5">
-        <v>0.02214660753100502</v>
+        <v>0.01911665107318516</v>
       </c>
       <c r="M5">
-        <v>0.04570073002568867</v>
+        <v>0.05297233056804525</v>
       </c>
       <c r="N5">
-        <v>-0.02462578843904343</v>
+        <v>-0.04811197302546494</v>
       </c>
       <c r="O5">
-        <v>-0.002123844267006859</v>
+        <v>-0.01576864925818585</v>
       </c>
       <c r="P5">
-        <v>0.03786508486312829</v>
+        <v>0.04170971225912837</v>
       </c>
       <c r="Q5">
-        <v>0.03248234209978168</v>
+        <v>0.03397279003499234</v>
       </c>
       <c r="R5">
-        <v>0.0245926361163948</v>
+        <v>0.02263246703452754</v>
       </c>
       <c r="S5">
-        <v>-0.001101705548164765</v>
+        <v>-0.01429947116113657</v>
       </c>
       <c r="T5">
-        <v>0.06559146633645598</v>
+        <v>0.08156241680904652</v>
       </c>
       <c r="U5">
-        <v>0.02216464061922905</v>
+        <v>0.01914257105620949</v>
       </c>
       <c r="V5">
-        <v>0.02417345913485284</v>
+        <v>0.02202996012551785</v>
       </c>
       <c r="W5">
-        <v>0.04224943341299867</v>
+        <v>0.04801158571383547</v>
       </c>
       <c r="X5">
-        <v>0.02485562739986363</v>
+        <v>0.02301047935933703</v>
       </c>
       <c r="Y5">
-        <v>0.01727029126503622</v>
+        <v>0.01210764444797655</v>
       </c>
       <c r="Z5">
-        <v>0.02614378163847397</v>
+        <v>0.02486201668798006</v>
       </c>
       <c r="AA5">
-        <v>0.0285715942725635</v>
+        <v>0.02835164982680147</v>
       </c>
       <c r="AB5">
-        <v>0.02676223287821032</v>
+        <v>0.02575095181856871</v>
       </c>
       <c r="AC5">
-        <v>0.02564534988849739</v>
+        <v>0.02414559239405537</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -2338,88 +2338,88 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>-0.008663845000904162</v>
+        <v>-0.0141216469199525</v>
       </c>
       <c r="C13">
-        <v>0.06146870956848705</v>
+        <v>0.06362879709594065</v>
       </c>
       <c r="D13">
-        <v>0.02733249560496495</v>
+        <v>0.02578466309880634</v>
       </c>
       <c r="E13">
-        <v>0.01247887718280434</v>
+        <v>0.009317625292234365</v>
       </c>
       <c r="F13">
-        <v>0.02429571231039551</v>
+        <v>0.02241802044643861</v>
       </c>
       <c r="G13">
-        <v>-0.01875148311288547</v>
+        <v>-0.02530501742590157</v>
       </c>
       <c r="H13">
-        <v>-0.0180136251306363</v>
+        <v>-0.02448701234833403</v>
       </c>
       <c r="I13">
-        <v>0.05983872782802234</v>
+        <v>0.06182176461527523</v>
       </c>
       <c r="J13">
-        <v>0.0164363493086054</v>
+        <v>0.01370496319616185</v>
       </c>
       <c r="K13">
-        <v>-0.001532542679494958</v>
+        <v>-0.006215733249682102</v>
       </c>
       <c r="L13">
-        <v>-0.00284659550793144</v>
+        <v>-0.007672520208300421</v>
       </c>
       <c r="M13">
-        <v>0.05460633820267001</v>
+        <v>0.05602102601202393</v>
       </c>
       <c r="N13">
-        <v>-0.116933264020406</v>
+        <v>-0.1341514312874968</v>
       </c>
       <c r="O13">
-        <v>-0.06204679108270833</v>
+        <v>-0.07330311815283172</v>
       </c>
       <c r="P13">
-        <v>0.03549372629339656</v>
+        <v>0.03483237729712288</v>
       </c>
       <c r="Q13">
-        <v>0.02236420456175178</v>
+        <v>0.02027670980975559</v>
       </c>
       <c r="R13">
-        <v>0.0031197281452785</v>
+        <v>-0.001058126706911307</v>
       </c>
       <c r="S13">
-        <v>-0.05955360255191383</v>
+        <v>-0.07053911623567916</v>
       </c>
       <c r="T13">
-        <v>0.1031235841741767</v>
+        <v>0.1098082784495576</v>
       </c>
       <c r="U13">
-        <v>-0.002802609414942141</v>
+        <v>-0.007623756288585234</v>
       </c>
       <c r="V13">
-        <v>0.002097276668303456</v>
+        <v>-0.002191638195372193</v>
       </c>
       <c r="W13">
-        <v>0.04618797680757848</v>
+        <v>0.04668825123469841</v>
       </c>
       <c r="X13">
-        <v>0.003761213336629231</v>
+        <v>-0.0003469625583447378</v>
       </c>
       <c r="Y13">
-        <v>-0.01474084778771249</v>
+        <v>-0.02085874166662501</v>
       </c>
       <c r="Z13">
-        <v>0.006903263739764173</v>
+        <v>0.003136381453063608</v>
       </c>
       <c r="AA13">
-        <v>0.01282515526255764</v>
+        <v>0.009701516548143926</v>
       </c>
       <c r="AB13">
-        <v>0.008411782602559051</v>
+        <v>0.004808757600044025</v>
       </c>
       <c r="AC13">
-        <v>0.005687494980086236</v>
+        <v>0.00178855430679755</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -2516,88 +2516,88 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.1313793000436998</v>
+        <v>0.1313238873907746</v>
       </c>
       <c r="C15">
-        <v>0.1321332848426567</v>
+        <v>0.1319244854585343</v>
       </c>
       <c r="D15">
-        <v>0.1311418912827295</v>
+        <v>0.1311347758287043</v>
       </c>
       <c r="E15">
-        <v>0.1310889699353054</v>
+        <v>0.1310926205239155</v>
       </c>
       <c r="F15">
-        <v>0.1316573267802249</v>
+        <v>0.1315453538195057</v>
       </c>
       <c r="G15">
-        <v>0.1310565440528398</v>
+        <v>0.131066791193694</v>
       </c>
       <c r="H15">
-        <v>0.1302664721041765</v>
+        <v>0.1304374473575651</v>
       </c>
       <c r="I15">
-        <v>0.1316368706069334</v>
+        <v>0.1315290591433138</v>
       </c>
       <c r="J15">
-        <v>0.1310278818145008</v>
+        <v>0.1310439598514867</v>
       </c>
       <c r="K15">
-        <v>0.1308253075479674</v>
+        <v>0.1308825962361643</v>
       </c>
       <c r="L15">
-        <v>0.131278647969098</v>
+        <v>0.1312437114487589</v>
       </c>
       <c r="M15">
-        <v>0.1307193498372595</v>
+        <v>0.130798194008953</v>
       </c>
       <c r="N15">
-        <v>0.1307238615949156</v>
+        <v>0.1308017879181859</v>
       </c>
       <c r="O15">
-        <v>0.1299197823844559</v>
+        <v>0.1301612863844733</v>
       </c>
       <c r="P15">
-        <v>0.1317742411163353</v>
+        <v>0.1316384837134485</v>
       </c>
       <c r="Q15">
-        <v>0.1317375377639689</v>
+        <v>0.1316092470994715</v>
       </c>
       <c r="R15">
-        <v>0.1314808930883972</v>
+        <v>0.1314048128768421</v>
       </c>
       <c r="S15">
-        <v>0.130431797948135</v>
+        <v>0.1305691401749397</v>
       </c>
       <c r="T15">
-        <v>0.1325710487196626</v>
+        <v>0.132273192937821</v>
       </c>
       <c r="U15">
-        <v>0.131077106621598</v>
+        <v>0.1310831706208143</v>
       </c>
       <c r="V15">
-        <v>0.1311401425964448</v>
+        <v>0.131133382886028</v>
       </c>
       <c r="W15">
-        <v>0.1317073599189983</v>
+        <v>0.1315852084777334</v>
       </c>
       <c r="X15">
-        <v>0.1311615487818518</v>
+        <v>0.1311504343088304</v>
       </c>
       <c r="Y15">
-        <v>0.1309235237666101</v>
+        <v>0.1309608318600403</v>
       </c>
       <c r="Z15">
-        <v>0.1312019705808109</v>
+        <v>0.1311826329080379</v>
       </c>
       <c r="AA15">
-        <v>0.1312781544346258</v>
+        <v>0.1312433183163632</v>
       </c>
       <c r="AB15">
-        <v>0.1312213773497593</v>
+        <v>0.1311980916652277</v>
       </c>
       <c r="AC15">
-        <v>0.1311863299786311</v>
+        <v>0.1311701741483112</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2961,88 +2961,88 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.011743031853736</v>
+        <v>0.01040892597863472</v>
       </c>
       <c r="C20">
-        <v>0.01812977942561313</v>
+        <v>0.0218000574105283</v>
       </c>
       <c r="D20">
-        <v>0.01502110353346538</v>
+        <v>0.01625555525695308</v>
       </c>
       <c r="E20">
-        <v>0.01366843198208962</v>
+        <v>0.01384298778775279</v>
       </c>
       <c r="F20">
-        <v>0.01474455338564896</v>
+        <v>0.01576231217104221</v>
       </c>
       <c r="G20">
-        <v>0.01082438289515678</v>
+        <v>0.008770462753154131</v>
       </c>
       <c r="H20">
-        <v>0.0108915772630998</v>
+        <v>0.008890307770998959</v>
       </c>
       <c r="I20">
-        <v>0.01798134219860728</v>
+        <v>0.02153531108335938</v>
       </c>
       <c r="J20">
-        <v>0.01402882631886261</v>
+        <v>0.01448577180438877</v>
       </c>
       <c r="K20">
-        <v>0.01239245676154422</v>
+        <v>0.01156721263342019</v>
       </c>
       <c r="L20">
-        <v>0.01227279017071683</v>
+        <v>0.01135378038973426</v>
       </c>
       <c r="M20">
-        <v>0.01750484520031572</v>
+        <v>0.02068545129582958</v>
       </c>
       <c r="N20">
-        <v>0.001883281937637172</v>
+        <v>-0.007176504777144047</v>
       </c>
       <c r="O20">
-        <v>0.006881617588121718</v>
+        <v>0.001738314181115555</v>
       </c>
       <c r="P20">
-        <v>0.01576432072557974</v>
+        <v>0.01758112584237849</v>
       </c>
       <c r="Q20">
-        <v>0.01456865714888054</v>
+        <v>0.01544859112150091</v>
       </c>
       <c r="R20">
-        <v>0.01281612419496757</v>
+        <v>0.01232284785513914</v>
       </c>
       <c r="S20">
-        <v>0.007108664298355672</v>
+        <v>0.002143265040429681</v>
       </c>
       <c r="T20">
-        <v>0.02192315570968258</v>
+        <v>0.02856576207259044</v>
       </c>
       <c r="U20">
-        <v>0.01227679584360756</v>
+        <v>0.011360924737598</v>
       </c>
       <c r="V20">
-        <v>0.01272301280713881</v>
+        <v>0.01215677834250742</v>
       </c>
       <c r="W20">
-        <v>0.01673821193664232</v>
+        <v>0.0193181168007231</v>
       </c>
       <c r="X20">
-        <v>0.01287454220089092</v>
+        <v>0.01242703972681922</v>
       </c>
       <c r="Y20">
-        <v>0.01118961863456491</v>
+        <v>0.009421881689694333</v>
       </c>
       <c r="Z20">
-        <v>0.01316067868780703</v>
+        <v>0.01293738059957797</v>
       </c>
       <c r="AA20">
-        <v>0.01369996641996427</v>
+        <v>0.01389923127043601</v>
       </c>
       <c r="AB20">
-        <v>0.01329805467878926</v>
+        <v>0.01318239857645182</v>
       </c>
       <c r="AC20">
-        <v>0.01304996251296479</v>
+        <v>0.0127399119373096</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -3050,88 +3050,88 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.008333318379619131</v>
+        <v>0.008886877902114359</v>
       </c>
       <c r="C21">
-        <v>0.01713050143447482</v>
+        <v>0.01226353736857456</v>
       </c>
       <c r="D21">
-        <v>0.01284857380641877</v>
+        <v>0.01061998722646488</v>
       </c>
       <c r="E21">
-        <v>0.01098538771418204</v>
+        <v>0.00990483273702231</v>
       </c>
       <c r="F21">
-        <v>0.01246765030086156</v>
+        <v>0.0104737757684315</v>
       </c>
       <c r="G21">
-        <v>0.007067960235928048</v>
+        <v>0.008401190207801956</v>
       </c>
       <c r="H21">
-        <v>0.007160514567909637</v>
+        <v>0.008436715723105975</v>
       </c>
       <c r="I21">
-        <v>0.01692604220958301</v>
+        <v>0.01218505893145088</v>
       </c>
       <c r="J21">
-        <v>0.01148179921578667</v>
+        <v>0.01009537243429823</v>
       </c>
       <c r="K21">
-        <v>0.009227844072090262</v>
+        <v>0.009230227429871124</v>
       </c>
       <c r="L21">
-        <v>0.009063013868107477</v>
+        <v>0.009166959965142191</v>
       </c>
       <c r="M21">
-        <v>0.01626970950316479</v>
+        <v>0.0119331360110734</v>
       </c>
       <c r="N21">
-        <v>-0.005247619947888031</v>
+        <v>0.003674049695512772</v>
       </c>
       <c r="O21">
-        <v>0.001637147798459601</v>
+        <v>0.006316658817105725</v>
       </c>
       <c r="P21">
-        <v>0.0138722901213293</v>
+        <v>0.01101292452970815</v>
       </c>
       <c r="Q21">
-        <v>0.01222536870508881</v>
+        <v>0.01038077981292918</v>
       </c>
       <c r="R21">
-        <v>0.009811408699353374</v>
+        <v>0.009454219474898726</v>
       </c>
       <c r="S21">
-        <v>0.001949884672659224</v>
+        <v>0.006436697916007329</v>
       </c>
       <c r="T21">
-        <v>0.02235554363182898</v>
+        <v>0.0142690871097058</v>
       </c>
       <c r="U21">
-        <v>0.009068531330208645</v>
+        <v>0.009169077755634737</v>
       </c>
       <c r="V21">
-        <v>0.009683155951925537</v>
+        <v>0.009404991687889941</v>
       </c>
       <c r="W21">
-        <v>0.01521373960916534</v>
+        <v>0.01152781868203338</v>
       </c>
       <c r="X21">
-        <v>0.009891874364548955</v>
+        <v>0.009485104946806431</v>
       </c>
       <c r="Y21">
-        <v>0.007571040343852933</v>
+        <v>0.008594289544057639</v>
       </c>
       <c r="Z21">
-        <v>0.01028600220908102</v>
+        <v>0.009636384681346019</v>
       </c>
       <c r="AA21">
-        <v>0.01102882362884645</v>
+        <v>0.009921504925326383</v>
       </c>
       <c r="AB21">
-        <v>0.01047522555420498</v>
+        <v>0.009709015067187023</v>
       </c>
       <c r="AC21">
-        <v>0.01013350041591334</v>
+        <v>0.009577849281964108</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -3139,88 +3139,88 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.03859058909987918</v>
+        <v>0.03312070925062929</v>
       </c>
       <c r="C22">
-        <v>0.09904445157529407</v>
+        <v>0.1040820762432143</v>
       </c>
       <c r="D22">
-        <v>0.06961922962162559</v>
+        <v>0.06954244736934877</v>
       </c>
       <c r="E22">
-        <v>0.05681549516664976</v>
+        <v>0.05451329187238381</v>
       </c>
       <c r="F22">
-        <v>0.06700153972305084</v>
+        <v>0.06646977598063332</v>
       </c>
       <c r="G22">
-        <v>0.02989510251924875</v>
+        <v>0.0229138574605034</v>
       </c>
       <c r="H22">
-        <v>0.03053113189617875</v>
+        <v>0.02366043529997145</v>
       </c>
       <c r="I22">
-        <v>0.09763941660144332</v>
+        <v>0.1024328317064011</v>
       </c>
       <c r="J22">
-        <v>0.0602268135923425</v>
+        <v>0.05851753260774781</v>
       </c>
       <c r="K22">
-        <v>0.04473773107205019</v>
+        <v>0.04033628786845783</v>
       </c>
       <c r="L22">
-        <v>0.04360502502043861</v>
+        <v>0.03900670582800807</v>
       </c>
       <c r="M22">
-        <v>0.09312912655467391</v>
+        <v>0.09713860675291745</v>
       </c>
       <c r="N22">
-        <v>-0.0547370332558974</v>
+        <v>-0.07642821598515559</v>
       </c>
       <c r="O22">
-        <v>-0.007425206286110727</v>
+        <v>-0.02089310575033723</v>
       </c>
       <c r="P22">
-        <v>0.07665416397840021</v>
+        <v>0.07780012584047778</v>
       </c>
       <c r="Q22">
-        <v>0.06533659104802184</v>
+        <v>0.06451544206192633</v>
       </c>
       <c r="R22">
-        <v>0.04874796201780827</v>
+        <v>0.04504353829406445</v>
       </c>
       <c r="S22">
-        <v>-0.005276091976909246</v>
+        <v>-0.01837045321897446</v>
       </c>
       <c r="T22">
-        <v>0.1349507161667462</v>
+        <v>0.146229219778387</v>
       </c>
       <c r="U22">
-        <v>0.04364294078199518</v>
+        <v>0.0390512117397968</v>
       </c>
       <c r="V22">
-        <v>0.04786661466982772</v>
+        <v>0.04400900369119397</v>
       </c>
       <c r="W22">
-        <v>0.08587254699369896</v>
+        <v>0.08862075885615739</v>
       </c>
       <c r="X22">
-        <v>0.04930091859804465</v>
+        <v>0.04569260442837599</v>
       </c>
       <c r="Y22">
-        <v>0.03335224731991551</v>
+        <v>0.02697188966723605</v>
       </c>
       <c r="Z22">
-        <v>0.05200934814446878</v>
+        <v>0.04887178695117217</v>
       </c>
       <c r="AA22">
-        <v>0.05711398489856084</v>
+        <v>0.05486366219683205</v>
       </c>
       <c r="AB22">
-        <v>0.05330968280977374</v>
+        <v>0.0503981331864588</v>
       </c>
       <c r="AC22">
-        <v>0.05096136240017717</v>
+        <v>0.04764165048083634</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -3317,88 +3317,88 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.03159214394294087</v>
+        <v>0.03176065205543443</v>
       </c>
       <c r="C24">
-        <v>0.02001799795465269</v>
+        <v>0.0201869786717032</v>
       </c>
       <c r="D24">
-        <v>0.03523651934967253</v>
+        <v>0.03540487865218683</v>
       </c>
       <c r="E24">
-        <v>0.03604889567586742</v>
+        <v>0.0362172218067979</v>
       </c>
       <c r="F24">
-        <v>0.02732425678972365</v>
+        <v>0.02749293917191445</v>
       </c>
       <c r="G24">
-        <v>0.0365466535855434</v>
+        <v>0.03671495939163466</v>
       </c>
       <c r="H24">
-        <v>0.0486747602631999</v>
+        <v>0.04884257084497924</v>
       </c>
       <c r="I24">
-        <v>0.02763827205417643</v>
+        <v>0.02780694161425101</v>
       </c>
       <c r="J24">
-        <v>0.03698663716524619</v>
+        <v>0.03715492500558473</v>
       </c>
       <c r="K24">
-        <v>0.04009628093733826</v>
+        <v>0.04026444180227674</v>
       </c>
       <c r="L24">
-        <v>0.03313721727475998</v>
+        <v>0.03330566229761408</v>
       </c>
       <c r="M24">
-        <v>0.04172279915629181</v>
+        <v>0.04189089360596967</v>
       </c>
       <c r="N24">
-        <v>0.04165354080805073</v>
+        <v>0.04182163808573949</v>
       </c>
       <c r="O24">
-        <v>0.05399666785899675</v>
+        <v>0.05416426113249399</v>
       </c>
       <c r="P24">
-        <v>0.02552954740547926</v>
+        <v>0.02569830307064352</v>
       </c>
       <c r="Q24">
-        <v>0.02609296719741185</v>
+        <v>0.0262616998565797</v>
       </c>
       <c r="R24">
-        <v>0.03003262612195842</v>
+        <v>0.03020119791390009</v>
       </c>
       <c r="S24">
-        <v>0.04613690345725292</v>
+        <v>0.04630481766678092</v>
       </c>
       <c r="T24">
-        <v>0.01329804414673182</v>
+        <v>0.01346729925817785</v>
       </c>
       <c r="U24">
-        <v>0.03623100508303865</v>
+        <v>0.03639932377793577</v>
       </c>
       <c r="V24">
-        <v>0.03526336279582094</v>
+        <v>0.0354317210022427</v>
       </c>
       <c r="W24">
-        <v>0.02655621630241263</v>
+        <v>0.02672493004583169</v>
       </c>
       <c r="X24">
-        <v>0.03493476424145222</v>
+        <v>0.03510313586546647</v>
       </c>
       <c r="Y24">
-        <v>0.0385885995430173</v>
+        <v>0.03875682197077848</v>
       </c>
       <c r="Z24">
-        <v>0.03431426393042603</v>
+        <v>0.03448266089119296</v>
       </c>
       <c r="AA24">
-        <v>0.0331447933426578</v>
+        <v>0.03331323805615999</v>
       </c>
       <c r="AB24">
-        <v>0.03401635768976918</v>
+        <v>0.03418476681487612</v>
       </c>
       <c r="AC24">
-        <v>0.03455435711695238</v>
+        <v>0.03472274427404706</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -3406,88 +3406,88 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.03044923148923321</v>
+        <v>0.0284286510427386</v>
       </c>
       <c r="C25">
-        <v>0.05378299831869236</v>
+        <v>0.05535118066878075</v>
       </c>
       <c r="D25">
-        <v>0.04242555580207555</v>
+        <v>0.04224694915466245</v>
       </c>
       <c r="E25">
-        <v>0.03748361591460821</v>
+        <v>0.03654493267344509</v>
       </c>
       <c r="F25">
-        <v>0.04141518916503869</v>
+        <v>0.04108118685329039</v>
       </c>
       <c r="G25">
-        <v>0.02709297850500685</v>
+        <v>0.02455620211236497</v>
       </c>
       <c r="H25">
-        <v>0.027338470861827</v>
+        <v>0.02483945150359113</v>
       </c>
       <c r="I25">
-        <v>0.05324068791660017</v>
+        <v>0.05472546224219542</v>
       </c>
       <c r="J25">
-        <v>0.0388003044679413</v>
+        <v>0.0380641295885624</v>
       </c>
       <c r="K25">
-        <v>0.03282188348486959</v>
+        <v>0.03116621991070902</v>
       </c>
       <c r="L25">
-        <v>0.03238468563162455</v>
+        <v>0.03066178047568513</v>
       </c>
       <c r="M25">
-        <v>0.05149982220554081</v>
+        <v>0.05271684918698204</v>
       </c>
       <c r="N25">
-        <v>-0.005573032260798003</v>
+        <v>-0.01313388234912348</v>
       </c>
       <c r="O25">
-        <v>0.01268821844485665</v>
+        <v>0.007935971769366746</v>
       </c>
       <c r="P25">
-        <v>0.04514087474481947</v>
+        <v>0.04537988757881276</v>
       </c>
       <c r="Q25">
-        <v>0.04077255819696873</v>
+        <v>0.04033971843102808</v>
       </c>
       <c r="R25">
-        <v>0.03436973816261917</v>
+        <v>0.03295213659201868</v>
       </c>
       <c r="S25">
-        <v>0.01351772594243226</v>
+        <v>0.008893058567298938</v>
       </c>
       <c r="T25">
-        <v>0.06764197062231538</v>
+        <v>0.07134168040925651</v>
       </c>
       <c r="U25">
-        <v>0.03239932022241984</v>
+        <v>0.03067866588502049</v>
       </c>
       <c r="V25">
-        <v>0.03402955884782511</v>
+        <v>0.03255963726914265</v>
       </c>
       <c r="W25">
-        <v>0.04869895343517781</v>
+        <v>0.04948520326372064</v>
       </c>
       <c r="X25">
-        <v>0.03458316637682629</v>
+        <v>0.03319839033501785</v>
       </c>
       <c r="Y25">
-        <v>0.02842735495956739</v>
+        <v>0.02609580735024898</v>
       </c>
       <c r="Z25">
-        <v>0.03562855638041753</v>
+        <v>0.03440456264093637</v>
       </c>
       <c r="AA25">
-        <v>0.03759882591972961</v>
+        <v>0.0366778621228035</v>
       </c>
       <c r="AB25">
-        <v>0.0361304549297919</v>
+        <v>0.03498365382083706</v>
       </c>
       <c r="AC25">
-        <v>0.03522405857007758</v>
+        <v>0.03393785255669923</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -3584,88 +3584,88 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>0.07375652323150447</v>
+        <v>0.0689349772840572</v>
       </c>
       <c r="C27">
-        <v>0.09691984949146609</v>
+        <v>0.1101607527963702</v>
       </c>
       <c r="D27">
-        <v>0.08564536696089507</v>
+        <v>0.09009458092595829</v>
       </c>
       <c r="E27">
-        <v>0.08073952527630252</v>
+        <v>0.08136323009498761</v>
       </c>
       <c r="F27">
-        <v>0.08464238050667552</v>
+        <v>0.08830947916900472</v>
       </c>
       <c r="G27">
-        <v>0.07042478586338889</v>
+        <v>0.06300519607464013</v>
       </c>
       <c r="H27">
-        <v>0.07066848503107634</v>
+        <v>0.06343892856482164</v>
       </c>
       <c r="I27">
-        <v>0.09638150037408427</v>
+        <v>0.1092026063017194</v>
       </c>
       <c r="J27">
-        <v>0.08204659613059365</v>
+        <v>0.08368953716388364</v>
       </c>
       <c r="K27">
-        <v>0.07611184428523544</v>
+        <v>0.07312694591286234</v>
       </c>
       <c r="L27">
-        <v>0.07567783992627852</v>
+        <v>0.07235451081123144</v>
       </c>
       <c r="M27">
-        <v>0.0946533507472037</v>
+        <v>0.1061268689153919</v>
       </c>
       <c r="N27">
-        <v>0.03799738267084167</v>
+        <v>0.005291341446862295</v>
       </c>
       <c r="O27">
-        <v>0.05612524479878585</v>
+        <v>0.03755506584539891</v>
       </c>
       <c r="P27">
-        <v>0.08834085196468043</v>
+        <v>0.09489196876290902</v>
       </c>
       <c r="Q27">
-        <v>0.08400444361089039</v>
+        <v>0.08717408769018595</v>
       </c>
       <c r="R27">
-        <v>0.07764839272020377</v>
+        <v>0.07586167408328465</v>
       </c>
       <c r="S27">
-        <v>0.05694869319191757</v>
+        <v>0.03902062818390906</v>
       </c>
       <c r="T27">
-        <v>0.1106775894844491</v>
+        <v>0.1346465927893881</v>
       </c>
       <c r="U27">
-        <v>0.07569236761928883</v>
+        <v>0.07238036700321496</v>
       </c>
       <c r="V27">
-        <v>0.07731069823165181</v>
+        <v>0.07526064998939827</v>
       </c>
       <c r="W27">
-        <v>0.09187294081110428</v>
+        <v>0.1011783328298828</v>
       </c>
       <c r="X27">
-        <v>0.07786026195652951</v>
+        <v>0.07623875609114067</v>
       </c>
       <c r="Y27">
-        <v>0.07174941541833818</v>
+        <v>0.06536275388203097</v>
       </c>
       <c r="Z27">
-        <v>0.07889801595051882</v>
+        <v>0.0780857366462244</v>
       </c>
       <c r="AA27">
-        <v>0.08085389373453487</v>
+        <v>0.08156678153366535</v>
       </c>
       <c r="AB27">
-        <v>0.07939624840194978</v>
+        <v>0.07897248404014884</v>
       </c>
       <c r="AC27">
-        <v>0.07849647277830733</v>
+        <v>0.07737107552673281</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3931,88 +3931,88 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.05468496413766613</v>
+        <v>0.05141904223445452</v>
       </c>
       <c r="C31">
-        <v>0.142310697232023</v>
+        <v>0.1302650751946314</v>
       </c>
       <c r="D31">
-        <v>0.0996598799049591</v>
+        <v>0.09188767588515011</v>
       </c>
       <c r="E31">
-        <v>0.0811013201699381</v>
+        <v>0.07518859947359866</v>
       </c>
       <c r="F31">
-        <v>0.09586563108471892</v>
+        <v>0.08847359354911273</v>
       </c>
       <c r="G31">
-        <v>0.04208116423075781</v>
+        <v>0.04007808578489795</v>
       </c>
       <c r="H31">
-        <v>0.04300306629194873</v>
+        <v>0.04090761745026436</v>
       </c>
       <c r="I31">
-        <v>0.140274148787216</v>
+        <v>0.1284325796464191</v>
       </c>
       <c r="J31">
-        <v>0.08604590543926106</v>
+        <v>0.07963775977562586</v>
       </c>
       <c r="K31">
-        <v>0.06359502876696307</v>
+        <v>0.05943635889053732</v>
       </c>
       <c r="L31">
-        <v>0.06195321145225893</v>
+        <v>0.05795904420752796</v>
       </c>
       <c r="M31">
-        <v>0.1337366430657731</v>
+        <v>0.1225501022806071</v>
       </c>
       <c r="N31">
-        <v>-0.08059011990190151</v>
+        <v>-0.0703020933067366</v>
       </c>
       <c r="O31">
-        <v>-0.01201330193684772</v>
+        <v>-0.008596360770903526</v>
       </c>
       <c r="P31">
-        <v>0.1098567681605895</v>
+        <v>0.1010628822897451</v>
       </c>
       <c r="Q31">
-        <v>0.09345234693313596</v>
+        <v>0.08630210949940911</v>
       </c>
       <c r="R31">
-        <v>0.06940771652769356</v>
+        <v>0.06466664176048215</v>
       </c>
       <c r="S31">
-        <v>-0.008898236841975802</v>
+        <v>-0.005793411038330219</v>
       </c>
       <c r="T31">
-        <v>0.1943555563803607</v>
+        <v>0.1770952760375601</v>
       </c>
       <c r="U31">
-        <v>0.06200816900610549</v>
+        <v>0.05800849526430064</v>
       </c>
       <c r="V31">
-        <v>0.06813023475373792</v>
+        <v>0.06351715785320494</v>
       </c>
       <c r="W31">
-        <v>0.1232184879347168</v>
+        <v>0.1130858184811153</v>
       </c>
       <c r="X31">
-        <v>0.07020920751153709</v>
+        <v>0.06538782699109658</v>
       </c>
       <c r="Y31">
-        <v>0.04709217320797517</v>
+        <v>0.04458701444123198</v>
       </c>
       <c r="Z31">
-        <v>0.0741349802384054</v>
+        <v>0.06892025513618852</v>
       </c>
       <c r="AA31">
-        <v>0.08153397046735264</v>
+        <v>0.07557790017791852</v>
       </c>
       <c r="AB31">
-        <v>0.07601976929322699</v>
+        <v>0.07061619689543658</v>
       </c>
       <c r="AC31">
-        <v>0.07261596200936613</v>
+        <v>0.06755343562867044</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -4020,88 +4020,88 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>0.006014243522135712</v>
+        <v>0.006933700124104696</v>
       </c>
       <c r="C32">
-        <v>0.0201196559406244</v>
+        <v>0.02492052071516823</v>
       </c>
       <c r="D32">
-        <v>0.00157284299273472</v>
+        <v>0.001270152535047412</v>
       </c>
       <c r="E32">
-        <v>0.0005827999146889714</v>
+        <v>7.677770474653033E-06</v>
       </c>
       <c r="F32">
-        <v>0.01121551785482642</v>
+        <v>0.01356621716730614</v>
       </c>
       <c r="G32">
-        <v>-2.381768004753194E-05</v>
+        <v>-0.0007658637269441822</v>
       </c>
       <c r="H32">
-        <v>-0.01480434202429535</v>
+        <v>-0.01961356783755659</v>
       </c>
       <c r="I32">
-        <v>0.01083282743297679</v>
+        <v>0.01307822122961166</v>
       </c>
       <c r="J32">
-        <v>-0.0005600256953387566</v>
+        <v>-0.001449620931936766</v>
       </c>
       <c r="K32">
-        <v>-0.004349748749145752</v>
+        <v>-0.006282167945542437</v>
       </c>
       <c r="L32">
-        <v>0.004131262558860309</v>
+        <v>0.004532576374016464</v>
       </c>
       <c r="M32">
-        <v>-0.006331986601315676</v>
+        <v>-0.008809861256307446</v>
       </c>
       <c r="N32">
-        <v>-0.006247581448110226</v>
+        <v>-0.008702230206422105</v>
       </c>
       <c r="O32">
-        <v>-0.02129015113433792</v>
+        <v>-0.02788408708145407</v>
       </c>
       <c r="P32">
-        <v>0.01340273029034567</v>
+        <v>0.01635528823485334</v>
       </c>
       <c r="Q32">
-        <v>0.01271609055571729</v>
+        <v>0.01547970478142182</v>
       </c>
       <c r="R32">
-        <v>0.007914827985231266</v>
+        <v>0.009357271356311554</v>
       </c>
       <c r="S32">
-        <v>-0.0117114557808374</v>
+        <v>-0.01566960729821582</v>
       </c>
       <c r="T32">
-        <v>0.02830926405424528</v>
+        <v>0.03536367597220538</v>
       </c>
       <c r="U32">
-        <v>0.0003608631691151797</v>
+        <v>-0.00027532965297139</v>
       </c>
       <c r="V32">
-        <v>0.00154012888328423</v>
+        <v>0.001228436433452885</v>
       </c>
       <c r="W32">
-        <v>0.01215152884333317</v>
+        <v>0.01475979174861134</v>
       </c>
       <c r="X32">
-        <v>0.001940591961439636</v>
+        <v>0.001739095556803646</v>
       </c>
       <c r="Y32">
-        <v>-0.002512337342369071</v>
+        <v>-0.003939153197363465</v>
       </c>
       <c r="Z32">
-        <v>0.002696795728152231</v>
+        <v>0.002703385084723968</v>
       </c>
       <c r="AA32">
-        <v>0.00412202960445336</v>
+        <v>0.004520802773251301</v>
       </c>
       <c r="AB32">
-        <v>0.003059854081723916</v>
+        <v>0.003166346767518953</v>
       </c>
       <c r="AC32">
-        <v>0.002404194147158668</v>
+        <v>0.002330267873695504</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -4198,88 +4198,88 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>0.02160273635298092</v>
+        <v>0.02052959455399523</v>
       </c>
       <c r="C34">
-        <v>0.04551255482791296</v>
+        <v>0.04298094997593466</v>
       </c>
       <c r="D34">
-        <v>0.03387472580114208</v>
+        <v>0.03205301105855067</v>
       </c>
       <c r="E34">
-        <v>0.02881078192585698</v>
+        <v>0.02729796016178295</v>
       </c>
       <c r="F34">
-        <v>0.03283941576906532</v>
+        <v>0.031080853385065</v>
       </c>
       <c r="G34">
-        <v>0.01816362597721904</v>
+        <v>0.0173002647511587</v>
       </c>
       <c r="H34">
-        <v>0.01841517891899021</v>
+        <v>0.01753647334090856</v>
       </c>
       <c r="I34">
-        <v>0.04495685615457568</v>
+        <v>0.04245914808790795</v>
       </c>
       <c r="J34">
-        <v>0.03015997618704541</v>
+        <v>0.02856485559735227</v>
       </c>
       <c r="K34">
-        <v>0.02403396312122946</v>
+        <v>0.02281252013716139</v>
       </c>
       <c r="L34">
-        <v>0.0235859719595315</v>
+        <v>0.02239185576416693</v>
       </c>
       <c r="M34">
-        <v>0.04317301287522517</v>
+        <v>0.04078411657214275</v>
       </c>
       <c r="N34">
-        <v>-0.01530882591702462</v>
+        <v>-0.01413041779916419</v>
       </c>
       <c r="O34">
-        <v>0.003403248849497238</v>
+        <v>0.00344024848195155</v>
       </c>
       <c r="P34">
-        <v>0.0366570790961354</v>
+        <v>0.03466564497715581</v>
       </c>
       <c r="Q34">
-        <v>0.03218091986888671</v>
+        <v>0.03046252474679867</v>
       </c>
       <c r="R34">
-        <v>0.02562003041336691</v>
+        <v>0.02430183970419302</v>
       </c>
       <c r="S34">
-        <v>0.004253234787712242</v>
+        <v>0.004238386553243199</v>
       </c>
       <c r="T34">
-        <v>0.05971367008078265</v>
+        <v>0.05631581850554648</v>
       </c>
       <c r="U34">
-        <v>0.02360096784133351</v>
+        <v>0.02240593691967864</v>
       </c>
       <c r="V34">
-        <v>0.02527145293228127</v>
+        <v>0.02397452492645252</v>
       </c>
       <c r="W34">
-        <v>0.04030299774389468</v>
+        <v>0.03808916805769033</v>
       </c>
       <c r="X34">
-        <v>0.02583872762999798</v>
+        <v>0.02450719671874004</v>
       </c>
       <c r="Y34">
-        <v>0.01953094480914831</v>
+        <v>0.01858417918584753</v>
       </c>
       <c r="Z34">
-        <v>0.02690992566690553</v>
+        <v>0.02551305328260772</v>
       </c>
       <c r="AA34">
-        <v>0.02892883617440938</v>
+        <v>0.0274088132783007</v>
       </c>
       <c r="AB34">
-        <v>0.02742421482116341</v>
+        <v>0.02599597157008857</v>
       </c>
       <c r="AC34">
-        <v>0.02649544182940848</v>
+        <v>0.02512385233731187</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -4376,88 +4376,88 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>0.0004578492931882894</v>
+        <v>-0.003656593822529343</v>
       </c>
       <c r="C36">
-        <v>0.04854873133513669</v>
+        <v>0.05157338897515602</v>
       </c>
       <c r="D36">
-        <v>0.02514104785407704</v>
+        <v>0.02469083034658048</v>
       </c>
       <c r="E36">
-        <v>0.01495571215909013</v>
+        <v>0.0129934795944755</v>
       </c>
       <c r="F36">
-        <v>0.02305868270849262</v>
+        <v>0.02229933769171904</v>
       </c>
       <c r="G36">
-        <v>-0.006459386468488704</v>
+        <v>-0.01160069457309807</v>
       </c>
       <c r="H36">
-        <v>-0.005953426840953024</v>
+        <v>-0.01101962514083554</v>
       </c>
       <c r="I36">
-        <v>0.0474310298612276</v>
+        <v>0.05028976450091367</v>
       </c>
       <c r="J36">
-        <v>0.01766940662458819</v>
+        <v>0.01611002252909869</v>
       </c>
       <c r="K36">
-        <v>0.005347883897660562</v>
+        <v>0.001959367366319492</v>
       </c>
       <c r="L36">
-        <v>0.004446819335600417</v>
+        <v>0.0009245395954589723</v>
       </c>
       <c r="M36">
-        <v>0.04384310648077576</v>
+        <v>0.04616921319954811</v>
       </c>
       <c r="N36">
-        <v>-0.07378401870643544</v>
+        <v>-0.0889196815095174</v>
       </c>
       <c r="O36">
-        <v>-0.0361475899188062</v>
+        <v>-0.04569611757708809</v>
       </c>
       <c r="P36">
-        <v>0.03073731886921826</v>
+        <v>0.03111786887808071</v>
       </c>
       <c r="Q36">
-        <v>0.02173422059708857</v>
+        <v>0.02077825892329004</v>
       </c>
       <c r="R36">
-        <v>0.008538011632705657</v>
+        <v>0.00562307018165303</v>
       </c>
       <c r="S36">
-        <v>-0.03443797537134031</v>
+        <v>-0.04373271041884857</v>
       </c>
       <c r="T36">
-        <v>0.07711206648575254</v>
+        <v>0.0843769567624338</v>
       </c>
       <c r="U36">
-        <v>0.00447698122008363</v>
+        <v>0.000959179017536959</v>
       </c>
       <c r="V36">
-        <v>0.007836902231020137</v>
+        <v>0.004817880953461914</v>
       </c>
       <c r="W36">
-        <v>0.03807051731268448</v>
+        <v>0.03953968205113439</v>
       </c>
       <c r="X36">
-        <v>0.008977887077972393</v>
+        <v>0.006128245221986354</v>
       </c>
       <c r="Y36">
-        <v>-0.003709237247197631</v>
+        <v>-0.008442285167122036</v>
       </c>
       <c r="Z36">
-        <v>0.01113243536492396</v>
+        <v>0.008602636619534861</v>
       </c>
       <c r="AA36">
-        <v>0.01519315992338983</v>
+        <v>0.01326617652538605</v>
       </c>
       <c r="AB36">
-        <v>0.01216684803011418</v>
+        <v>0.009790608045268549</v>
       </c>
       <c r="AC36">
-        <v>0.0102987655753242</v>
+        <v>0.007645208388162818</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -4910,88 +4910,88 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>0.05090766265374543</v>
+        <v>0.05060891196882167</v>
       </c>
       <c r="C42">
-        <v>0.03835847661301267</v>
+        <v>0.04326414759539011</v>
       </c>
       <c r="D42">
-        <v>0.0444666485224024</v>
+        <v>0.04683912714237128</v>
       </c>
       <c r="E42">
-        <v>0.04712448441761877</v>
+        <v>0.04839470041463372</v>
       </c>
       <c r="F42">
-        <v>0.0450100360941646</v>
+        <v>0.04715716001439103</v>
       </c>
       <c r="G42">
-        <v>0.05271269668046957</v>
+        <v>0.05166535894229734</v>
       </c>
       <c r="H42">
-        <v>0.05258066787946928</v>
+        <v>0.05158808537007471</v>
       </c>
       <c r="I42">
-        <v>0.03865013779988488</v>
+        <v>0.04343485051488613</v>
       </c>
       <c r="J42">
-        <v>0.04641635316156202</v>
+        <v>0.04798024666406239</v>
       </c>
       <c r="K42">
-        <v>0.04963162130470933</v>
+        <v>0.04986207285041151</v>
       </c>
       <c r="L42">
-        <v>0.04986675167337549</v>
+        <v>0.04999968951728422</v>
       </c>
       <c r="M42">
-        <v>0.0395863967348304</v>
+        <v>0.04398282241102142</v>
       </c>
       <c r="N42">
-        <v>0.07028087799061793</v>
+        <v>0.06194763157527438</v>
       </c>
       <c r="O42">
-        <v>0.06045975334680773</v>
+        <v>0.05619954192573437</v>
       </c>
       <c r="P42">
-        <v>0.04300631668564988</v>
+        <v>0.04598442682849008</v>
       </c>
       <c r="Q42">
-        <v>0.04535565091207151</v>
+        <v>0.04735944081517391</v>
       </c>
       <c r="R42">
-        <v>0.04879916607118165</v>
+        <v>0.04937485499246878</v>
       </c>
       <c r="S42">
-        <v>0.06001363403888198</v>
+        <v>0.05593843804309868</v>
       </c>
       <c r="T42">
-        <v>0.03090495129741925</v>
+        <v>0.03890176209749815</v>
       </c>
       <c r="U42">
-        <v>0.04985888101092041</v>
+        <v>0.04999508299053358</v>
       </c>
       <c r="V42">
-        <v>0.04898211867972361</v>
+        <v>0.04948193315649342</v>
       </c>
       <c r="W42">
-        <v>0.04109273831833281</v>
+        <v>0.04486445122430188</v>
       </c>
       <c r="X42">
-        <v>0.0486843817594157</v>
+        <v>0.04930767424298024</v>
       </c>
       <c r="Y42">
-        <v>0.05199505265415178</v>
+        <v>0.05124533757515876</v>
       </c>
       <c r="Z42">
-        <v>0.04812215819148212</v>
+        <v>0.04897861707399265</v>
       </c>
       <c r="AA42">
-        <v>0.04706252306356097</v>
+        <v>0.04835843578804071</v>
       </c>
       <c r="AB42">
-        <v>0.04785223099474159</v>
+        <v>0.04882063458400446</v>
       </c>
       <c r="AC42">
-        <v>0.04833970207593614</v>
+        <v>0.04910594075594379</v>
       </c>
     </row>
     <row r="43" spans="1:29">
@@ -4999,88 +4999,88 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>0.05181693119972496</v>
+        <v>0.04653201799376773</v>
       </c>
       <c r="C43">
-        <v>0.1028908043830909</v>
+        <v>0.1099010474366714</v>
       </c>
       <c r="D43">
-        <v>0.07803118428743142</v>
+        <v>0.07905690150465094</v>
       </c>
       <c r="E43">
-        <v>0.06721407049105707</v>
+        <v>0.0656357536667201</v>
       </c>
       <c r="F43">
-        <v>0.07581965376748234</v>
+        <v>0.0763129830606866</v>
       </c>
       <c r="G43">
-        <v>0.04447063171278334</v>
+        <v>0.03741722329603553</v>
       </c>
       <c r="H43">
-        <v>0.04500797510835924</v>
+        <v>0.03808392286927817</v>
       </c>
       <c r="I43">
-        <v>0.1017037738918327</v>
+        <v>0.1084282597771159</v>
       </c>
       <c r="J43">
-        <v>0.07009609055607383</v>
+        <v>0.06921157047817286</v>
       </c>
       <c r="K43">
-        <v>0.05701028587833606</v>
+        <v>0.05297558346127826</v>
       </c>
       <c r="L43">
-        <v>0.05605332989793749</v>
+        <v>0.05178825679271477</v>
       </c>
       <c r="M43">
-        <v>0.09789329806057251</v>
+        <v>0.1037004774474757</v>
       </c>
       <c r="N43">
-        <v>-0.02703002668724987</v>
+        <v>-0.05129598846825968</v>
       </c>
       <c r="O43">
-        <v>0.012940922260982</v>
+        <v>-0.001702721247902449</v>
       </c>
       <c r="P43">
-        <v>0.08397458195432705</v>
+        <v>0.08643106990563011</v>
       </c>
       <c r="Q43">
-        <v>0.07441303764729934</v>
+        <v>0.07456774830994188</v>
       </c>
       <c r="R43">
-        <v>0.06039829151392225</v>
+        <v>0.05717919316409804</v>
       </c>
       <c r="S43">
-        <v>0.0147565811318995</v>
+        <v>0.0005500262583687694</v>
       </c>
       <c r="T43">
-        <v>0.1332258719724944</v>
+        <v>0.1475387606432635</v>
       </c>
       <c r="U43">
-        <v>0.05608536267000691</v>
+        <v>0.05182800090354649</v>
       </c>
       <c r="V43">
-        <v>0.05965369355379091</v>
+        <v>0.05625534605563054</v>
       </c>
       <c r="W43">
-        <v>0.09176264554200161</v>
+        <v>0.09609397581093922</v>
       </c>
       <c r="X43">
-        <v>0.06086545164395342</v>
+        <v>0.0577588140580963</v>
       </c>
       <c r="Y43">
-        <v>0.04739136775669772</v>
+        <v>0.04104107629220968</v>
       </c>
       <c r="Z43">
-        <v>0.06315364269603718</v>
+        <v>0.06059784773838725</v>
       </c>
       <c r="AA43">
-        <v>0.06746624671421175</v>
+        <v>0.06594863697698948</v>
       </c>
       <c r="AB43">
-        <v>0.06425221812318593</v>
+        <v>0.06196088629898955</v>
       </c>
       <c r="AC43">
-        <v>0.06226826186493326</v>
+        <v>0.05949932670488396</v>
       </c>
     </row>
     <row r="44" spans="1:29">
@@ -5177,88 +5177,88 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>-0.002074139043907068</v>
+        <v>-0.009304443201095164</v>
       </c>
       <c r="C45">
-        <v>0.0897050524327013</v>
+        <v>0.09289675121290826</v>
       </c>
       <c r="D45">
-        <v>0.04503258702942427</v>
+        <v>0.0431514957995744</v>
       </c>
       <c r="E45">
-        <v>0.02559435185236235</v>
+        <v>0.02150594825841579</v>
       </c>
       <c r="F45">
-        <v>0.04105849087427159</v>
+        <v>0.03872612042593952</v>
       </c>
       <c r="G45">
-        <v>-0.0152753588698613</v>
+        <v>-0.02400472996792955</v>
       </c>
       <c r="H45">
-        <v>-0.01430975866534592</v>
+        <v>-0.02292948085492085</v>
       </c>
       <c r="I45">
-        <v>0.08757197162336802</v>
+        <v>0.09052144802066985</v>
       </c>
       <c r="J45">
-        <v>0.03077331038634618</v>
+        <v>0.02727300437950446</v>
       </c>
       <c r="K45">
-        <v>0.007258262509876497</v>
+        <v>0.001087700924415805</v>
       </c>
       <c r="L45">
-        <v>0.005538623080057592</v>
+        <v>-0.0008272124765559274</v>
       </c>
       <c r="M45">
-        <v>0.08072458823267346</v>
+        <v>0.08289650875196912</v>
       </c>
       <c r="N45">
-        <v>-0.1437612599574932</v>
+        <v>-0.1670808711416319</v>
       </c>
       <c r="O45">
-        <v>-0.07193390189027125</v>
+        <v>-0.08709714424267209</v>
       </c>
       <c r="P45">
-        <v>0.05571280762936297</v>
+        <v>0.05504451081046581</v>
       </c>
       <c r="Q45">
-        <v>0.03853081709153594</v>
+        <v>0.03591141618276274</v>
       </c>
       <c r="R45">
-        <v>0.01334647157982352</v>
+        <v>0.007867257693003588</v>
       </c>
       <c r="S45">
-        <v>-0.06867118275847822</v>
+        <v>-0.0834639264408825</v>
       </c>
       <c r="T45">
-        <v>0.1442168370930913</v>
+        <v>0.1535986315879465</v>
       </c>
       <c r="U45">
-        <v>0.005596185621099481</v>
+        <v>-0.0007631134105984122</v>
       </c>
       <c r="V45">
-        <v>0.01200843718970322</v>
+        <v>0.006377282562070347</v>
       </c>
       <c r="W45">
-        <v>0.06970787271242346</v>
+        <v>0.0706287880783151</v>
       </c>
       <c r="X45">
-        <v>0.01418595322380291</v>
+        <v>0.008802066829181179</v>
       </c>
       <c r="Y45">
-        <v>-0.01002682814526467</v>
+        <v>-0.01816020137335064</v>
       </c>
       <c r="Z45">
-        <v>0.01829780751670693</v>
+        <v>0.01338084349119004</v>
       </c>
       <c r="AA45">
-        <v>0.02604750976712766</v>
+        <v>0.0220105646033852</v>
       </c>
       <c r="AB45">
-        <v>0.02027193554333599</v>
+        <v>0.01557914398830296</v>
       </c>
       <c r="AC45">
-        <v>0.01670678784729852</v>
+        <v>0.01160915529113486</v>
       </c>
     </row>
     <row r="46" spans="1:29">
@@ -5355,88 +5355,88 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>0.01819666521530383</v>
+        <v>0.01250097711136023</v>
       </c>
       <c r="C47">
-        <v>0.08295183259323675</v>
+        <v>0.08766994251996757</v>
       </c>
       <c r="D47">
-        <v>0.05143299997079642</v>
+        <v>0.05108231353140774</v>
       </c>
       <c r="E47">
-        <v>0.03771827714342134</v>
+        <v>0.03516201608575696</v>
       </c>
       <c r="F47">
-        <v>0.04862906089089615</v>
+        <v>0.04782745051059667</v>
       </c>
       <c r="G47">
-        <v>0.008882492953932078</v>
+        <v>0.001688918076154119</v>
       </c>
       <c r="H47">
-        <v>0.009563775953461404</v>
+        <v>0.002479763661128145</v>
       </c>
       <c r="I47">
-        <v>0.08144682908844736</v>
+        <v>0.0859229073261415</v>
       </c>
       <c r="J47">
-        <v>0.04137231158538929</v>
+        <v>0.03940368512457021</v>
       </c>
       <c r="K47">
-        <v>0.0247811776187211</v>
+        <v>0.02014439778536325</v>
       </c>
       <c r="L47">
-        <v>0.02356787929569112</v>
+        <v>0.01873597922407881</v>
       </c>
       <c r="M47">
-        <v>0.07661563096574092</v>
+        <v>0.08031476547008934</v>
       </c>
       <c r="N47">
-        <v>-0.08177123690328368</v>
+        <v>-0.1035435654417629</v>
       </c>
       <c r="O47">
-        <v>-0.03109316359357146</v>
+        <v>-0.04471554454638667</v>
       </c>
       <c r="P47">
-        <v>0.05896847137183338</v>
+        <v>0.05982962454947986</v>
       </c>
       <c r="Q47">
-        <v>0.04684565077097179</v>
+        <v>0.04575723590005366</v>
       </c>
       <c r="R47">
-        <v>0.02907673733125952</v>
+        <v>0.02513076092080073</v>
       </c>
       <c r="S47">
-        <v>-0.02879113935379277</v>
+        <v>-0.0420433133182628</v>
       </c>
       <c r="T47">
-        <v>0.1214128353865884</v>
+        <v>0.1323161677652908</v>
       </c>
       <c r="U47">
-        <v>0.02360849277157706</v>
+        <v>0.01878312407888516</v>
       </c>
       <c r="V47">
-        <v>0.02813268193596055</v>
+        <v>0.02403488440273275</v>
       </c>
       <c r="W47">
-        <v>0.06884274425807493</v>
+        <v>0.0712918584850218</v>
       </c>
       <c r="X47">
-        <v>0.0296690368873135</v>
+        <v>0.02581831292079335</v>
       </c>
       <c r="Y47">
-        <v>0.01258561432699517</v>
+        <v>0.005987568109302097</v>
       </c>
       <c r="Z47">
-        <v>0.03257017175990097</v>
+        <v>0.02918600256956641</v>
       </c>
       <c r="AA47">
-        <v>0.03803800448190789</v>
+        <v>0.03553316134288545</v>
       </c>
       <c r="AB47">
-        <v>0.03396302550739137</v>
+        <v>0.03080285230378599</v>
       </c>
       <c r="AC47">
-        <v>0.03144762161169681</v>
+        <v>0.02788292612522167</v>
       </c>
     </row>
     <row r="48" spans="1:29">
@@ -5622,88 +5622,88 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>0.05146059970108895</v>
+        <v>0.05045449404984647</v>
       </c>
       <c r="C50">
-        <v>0.0877284473947712</v>
+        <v>0.08130854013379687</v>
       </c>
       <c r="D50">
-        <v>0.07007548984218399</v>
+        <v>0.06629068822138728</v>
       </c>
       <c r="E50">
-        <v>0.06239419584194934</v>
+        <v>0.05975600215263289</v>
       </c>
       <c r="F50">
-        <v>0.06850506944779797</v>
+        <v>0.0649546888086622</v>
       </c>
       <c r="G50">
-        <v>0.04624395067296418</v>
+        <v>0.04601654860359396</v>
       </c>
       <c r="H50">
-        <v>0.04662552127286729</v>
+        <v>0.0463411611081221</v>
       </c>
       <c r="I50">
-        <v>0.08688553029486482</v>
+        <v>0.08059144759317745</v>
       </c>
       <c r="J50">
-        <v>0.06444073467390554</v>
+        <v>0.06149704849117174</v>
       </c>
       <c r="K50">
-        <v>0.05514843038169775</v>
+        <v>0.05359183207801766</v>
       </c>
       <c r="L50">
-        <v>0.05446889049988676</v>
+        <v>0.05301372898774438</v>
       </c>
       <c r="M50">
-        <v>0.084179689745188</v>
+        <v>0.07828951532190861</v>
       </c>
       <c r="N50">
-        <v>-0.004529073325829906</v>
+        <v>0.002822553869983063</v>
       </c>
       <c r="O50">
-        <v>0.02385452475027127</v>
+        <v>0.02696925401234924</v>
       </c>
       <c r="P50">
-        <v>0.07429593031263886</v>
+        <v>0.06988113190775655</v>
       </c>
       <c r="Q50">
-        <v>0.0675062233444856</v>
+        <v>0.06410494321684583</v>
       </c>
       <c r="R50">
-        <v>0.05755427244375612</v>
+        <v>0.05563854746296139</v>
       </c>
       <c r="S50">
-        <v>0.02514383443621781</v>
+        <v>0.02806610488705961</v>
       </c>
       <c r="T50">
-        <v>0.1092695513396421</v>
+        <v>0.09963414410753335</v>
       </c>
       <c r="U50">
-        <v>0.05449163715343405</v>
+        <v>0.05303308018560787</v>
       </c>
       <c r="V50">
-        <v>0.05702552919935567</v>
+        <v>0.05518873118031083</v>
       </c>
       <c r="W50">
-        <v>0.07982627854004694</v>
+        <v>0.07458594980899821</v>
       </c>
       <c r="X50">
-        <v>0.05788600550781614</v>
+        <v>0.05592076181801563</v>
       </c>
       <c r="Y50">
-        <v>0.04831798194162922</v>
+        <v>0.04778098350702201</v>
       </c>
       <c r="Z50">
-        <v>0.05951086298187293</v>
+        <v>0.05730307233745493</v>
       </c>
       <c r="AA50">
-        <v>0.06257326761158991</v>
+        <v>0.05990834338554775</v>
       </c>
       <c r="AB50">
-        <v>0.06029096763790338</v>
+        <v>0.05796672862085937</v>
       </c>
       <c r="AC50">
-        <v>0.05888214902046847</v>
+        <v>0.05676820824233039</v>
       </c>
     </row>
     <row r="51" spans="1:29">
@@ -5711,88 +5711,88 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>0.0326481946226051</v>
+        <v>0.03243970178670583</v>
       </c>
       <c r="C51">
-        <v>0.05293939231617512</v>
+        <v>0.0530300742267867</v>
       </c>
       <c r="D51">
-        <v>0.0262590630251287</v>
+        <v>0.02595636841489527</v>
       </c>
       <c r="E51">
-        <v>0.02483484661615331</v>
+        <v>0.02451115326599499</v>
       </c>
       <c r="F51">
-        <v>0.04013043495786689</v>
+        <v>0.04003226076305723</v>
       </c>
       <c r="G51">
-        <v>0.0239622030397725</v>
+        <v>0.0236256433756242</v>
       </c>
       <c r="H51">
-        <v>0.002699829945977429</v>
+        <v>0.002049776461670295</v>
       </c>
       <c r="I51">
-        <v>0.03957991954046525</v>
+        <v>0.03947362851031946</v>
       </c>
       <c r="J51">
-        <v>0.02319084644839133</v>
+        <v>0.02284291385218742</v>
       </c>
       <c r="K51">
-        <v>0.01773917886099889</v>
+        <v>0.01731086652116672</v>
       </c>
       <c r="L51">
-        <v>0.02993945149298423</v>
+        <v>0.02969102077114025</v>
       </c>
       <c r="M51">
-        <v>0.0148876507425203</v>
+        <v>0.01441729528552483</v>
       </c>
       <c r="N51">
-        <v>0.01500907091792779</v>
+        <v>0.01454050568794343</v>
       </c>
       <c r="O51">
-        <v>-0.006630264839633374</v>
+        <v>-0.007417881851956989</v>
       </c>
       <c r="P51">
-        <v>0.0432768271802441</v>
+        <v>0.0432250435982395</v>
       </c>
       <c r="Q51">
-        <v>0.04228906856771729</v>
+        <v>0.04222272140809744</v>
       </c>
       <c r="R51">
-        <v>0.03538226108800317</v>
+        <v>0.0352140795069683</v>
       </c>
       <c r="S51">
-        <v>0.007149070021189108</v>
+        <v>0.006564616423678664</v>
       </c>
       <c r="T51">
-        <v>0.06472046984415505</v>
+        <v>0.06498485273271212</v>
       </c>
       <c r="U51">
-        <v>0.02451558176615839</v>
+        <v>0.02418718115416123</v>
       </c>
       <c r="V51">
-        <v>0.02621200247542376</v>
+        <v>0.02590861400136616</v>
       </c>
       <c r="W51">
-        <v>0.04147692405351711</v>
+        <v>0.04139860258203873</v>
       </c>
       <c r="X51">
-        <v>0.02678808456694601</v>
+        <v>0.02649318988494068</v>
       </c>
       <c r="Y51">
-        <v>0.02038236836820231</v>
+        <v>0.01999302738741655</v>
       </c>
       <c r="Z51">
-        <v>0.02787591381090878</v>
+        <v>0.02759705815445652</v>
       </c>
       <c r="AA51">
-        <v>0.02992616952024861</v>
+        <v>0.02967754296812953</v>
       </c>
       <c r="AB51">
-        <v>0.02839818771599283</v>
+        <v>0.02812703250017115</v>
       </c>
       <c r="AC51">
-        <v>0.02745499478002605</v>
+        <v>0.0271699330658404</v>
       </c>
     </row>
     <row r="52" spans="1:29">
@@ -6156,88 +6156,88 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>0.008518476388653232</v>
+        <v>0.008386894336477395</v>
       </c>
       <c r="C56">
-        <v>0.04016403079410824</v>
+        <v>0.0411671090570271</v>
       </c>
       <c r="D56">
-        <v>-0.001445825109213568</v>
+        <v>-0.001934680013443444</v>
       </c>
       <c r="E56">
-        <v>-0.003666991081572831</v>
+        <v>-0.004235486520766453</v>
       </c>
       <c r="F56">
-        <v>0.02018755808506039</v>
+        <v>0.0204743742617438</v>
       </c>
       <c r="G56">
-        <v>-0.005027940306451794</v>
+        <v>-0.005645232965518512</v>
       </c>
       <c r="H56">
-        <v>-0.03818811126777431</v>
+        <v>-0.03999437124747935</v>
       </c>
       <c r="I56">
-        <v>0.01932899045117716</v>
+        <v>0.01958502244220495</v>
       </c>
       <c r="J56">
-        <v>-0.006230925332135828</v>
+        <v>-0.006891351359978716</v>
       </c>
       <c r="K56">
-        <v>-0.01473318556549567</v>
+        <v>-0.01569846254180979</v>
       </c>
       <c r="L56">
-        <v>0.004294000368394311</v>
+        <v>0.004010948532158354</v>
       </c>
       <c r="M56">
-        <v>-0.01918034484976966</v>
+        <v>-0.02030507598163812</v>
       </c>
       <c r="N56">
-        <v>-0.01899098151967923</v>
+        <v>-0.02010892297572041</v>
       </c>
       <c r="O56">
-        <v>-0.05273905235094463</v>
+        <v>-0.05506704044395169</v>
       </c>
       <c r="P56">
-        <v>0.02509457874287453</v>
+        <v>0.02555733753489134</v>
       </c>
       <c r="Q56">
-        <v>0.02355409949742913</v>
+        <v>0.02396162396984329</v>
       </c>
       <c r="R56">
-        <v>0.01278244593769085</v>
+        <v>0.01280374972123389</v>
       </c>
       <c r="S56">
-        <v>-0.03124920746380324</v>
+        <v>-0.0328066710825487</v>
       </c>
       <c r="T56">
-        <v>0.05853745238788206</v>
+        <v>0.06019931488532093</v>
       </c>
       <c r="U56">
-        <v>-0.004164907140192941</v>
+        <v>-0.004751255500676108</v>
       </c>
       <c r="V56">
-        <v>-0.001519219356735499</v>
+        <v>-0.002010705832495213</v>
       </c>
       <c r="W56">
-        <v>0.02228750282840364</v>
+        <v>0.02264961311855507</v>
       </c>
       <c r="X56">
-        <v>-0.000620778690758805</v>
+        <v>-0.001080051322005331</v>
       </c>
       <c r="Y56">
-        <v>-0.01061094504439327</v>
+        <v>-0.01142841791942219</v>
       </c>
       <c r="Z56">
-        <v>0.001075767764681696</v>
+        <v>0.0006773252870497706</v>
       </c>
       <c r="AA56">
-        <v>0.004273286194831746</v>
+        <v>0.003989491646036536</v>
       </c>
       <c r="AB56">
-        <v>0.001890290767585762</v>
+        <v>0.001521053242892425</v>
       </c>
       <c r="AC56">
-        <v>0.0004193148389723435</v>
+        <v>-2.664944215583637E-06</v>
       </c>
     </row>
     <row r="57" spans="1:29">
@@ -6957,88 +6957,88 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>0.03155803162120052</v>
+        <v>0.0309132649622613</v>
       </c>
       <c r="C65">
-        <v>-0.005427270775425277</v>
+        <v>0.00805271088350077</v>
       </c>
       <c r="D65">
-        <v>0.0125748995984999</v>
+        <v>0.01917982253868957</v>
       </c>
       <c r="E65">
-        <v>0.02040814583344409</v>
+        <v>0.02402153904666453</v>
       </c>
       <c r="F65">
-        <v>0.01417638622838649</v>
+        <v>0.02016969876888296</v>
       </c>
       <c r="G65">
-        <v>0.03687787699586467</v>
+        <v>0.03420145256646076</v>
       </c>
       <c r="H65">
-        <v>0.03648875812279911</v>
+        <v>0.03396093883629336</v>
       </c>
       <c r="I65">
-        <v>-0.004567678993232065</v>
+        <v>0.008584023138616441</v>
       </c>
       <c r="J65">
-        <v>0.01832112213670781</v>
+        <v>0.02273155316061572</v>
       </c>
       <c r="K65">
-        <v>0.027797247853113</v>
+        <v>0.02858873075170059</v>
       </c>
       <c r="L65">
-        <v>0.02849023047043343</v>
+        <v>0.02901706215829577</v>
       </c>
       <c r="M65">
-        <v>-0.001808311196937869</v>
+        <v>0.01028958379765619</v>
       </c>
       <c r="N65">
-        <v>0.08865529875099284</v>
+        <v>0.06620499109099329</v>
       </c>
       <c r="O65">
-        <v>0.05971021309784678</v>
+        <v>0.0483140816483151</v>
       </c>
       <c r="P65">
-        <v>0.008270969892907744</v>
+        <v>0.0165195707248542</v>
       </c>
       <c r="Q65">
-        <v>0.0151949916193299</v>
+        <v>0.02079929707187542</v>
       </c>
       <c r="R65">
-        <v>0.02534381314876327</v>
+        <v>0.02707226682946396</v>
       </c>
       <c r="S65">
-        <v>0.05839539814052198</v>
+        <v>0.04750139670354555</v>
       </c>
       <c r="T65">
-        <v>-0.02739450329738667</v>
+        <v>-0.005525199110140912</v>
       </c>
       <c r="U65">
-        <v>0.02846703383998921</v>
+        <v>0.02900272435948508</v>
       </c>
       <c r="V65">
-        <v>0.02588301605237891</v>
+        <v>0.02740554725003055</v>
       </c>
       <c r="W65">
-        <v>0.00263121968559224</v>
+        <v>0.01303365047408997</v>
       </c>
       <c r="X65">
-        <v>0.02500551770336366</v>
+        <v>0.02686316697565658</v>
       </c>
       <c r="Y65">
-        <v>0.03476281700389837</v>
+        <v>0.03289413749282277</v>
       </c>
       <c r="Z65">
-        <v>0.02334851711328242</v>
+        <v>0.02583897765872549</v>
       </c>
       <c r="AA65">
-        <v>0.020225531645616</v>
+        <v>0.02390866551999643</v>
       </c>
       <c r="AB65">
-        <v>0.02255298033789975</v>
+        <v>0.02534725769709723</v>
       </c>
       <c r="AC65">
-        <v>0.02398966836603722</v>
+        <v>0.02623527218483441</v>
       </c>
     </row>
     <row r="66" spans="1:29">
@@ -7669,88 +7669,88 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>0.03196029988297584</v>
+        <v>0.03251471489491962</v>
       </c>
       <c r="C73">
-        <v>0.04150255998491352</v>
+        <v>0.04444945211895562</v>
       </c>
       <c r="D73">
-        <v>0.02895570860899954</v>
+        <v>0.02875679937622013</v>
       </c>
       <c r="E73">
-        <v>0.02828594807435168</v>
+        <v>0.02791911355560109</v>
       </c>
       <c r="F73">
-        <v>0.03547894301594882</v>
+        <v>0.03691556759947585</v>
       </c>
       <c r="G73">
-        <v>0.02787557348198597</v>
+        <v>0.02740584805340511</v>
       </c>
       <c r="H73">
-        <v>0.01787660262233448</v>
+        <v>0.01489989155610724</v>
       </c>
       <c r="I73">
-        <v>0.03522005434006559</v>
+        <v>0.0365917692242547</v>
       </c>
       <c r="J73">
-        <v>0.02751283071354724</v>
+        <v>0.02695215683403073</v>
       </c>
       <c r="K73">
-        <v>0.02494909687714159</v>
+        <v>0.02374563245479505</v>
       </c>
       <c r="L73">
-        <v>0.03068647012277545</v>
+        <v>0.03092150497465542</v>
       </c>
       <c r="M73">
-        <v>0.02360812019328945</v>
+        <v>0.02206844024096255</v>
       </c>
       <c r="N73">
-        <v>0.02366521997186626</v>
+        <v>0.02213985632536864</v>
       </c>
       <c r="O73">
-        <v>0.01348897639324091</v>
+        <v>0.009412180518877572</v>
       </c>
       <c r="P73">
-        <v>0.03695858425852325</v>
+        <v>0.03876619095571678</v>
       </c>
       <c r="Q73">
-        <v>0.03649407498011595</v>
+        <v>0.03818521788259839</v>
       </c>
       <c r="R73">
-        <v>0.0332460383466586</v>
+        <v>0.03412281932080648</v>
       </c>
       <c r="S73">
-        <v>0.01996892889576527</v>
+        <v>0.01751681500962662</v>
       </c>
       <c r="T73">
-        <v>0.04704280003139936</v>
+        <v>0.05137876534313222</v>
       </c>
       <c r="U73">
-        <v>0.02813580867469352</v>
+        <v>0.02773133055002877</v>
       </c>
       <c r="V73">
-        <v>0.02893357763316429</v>
+        <v>0.02872911962548146</v>
       </c>
       <c r="W73">
-        <v>0.03611215103891283</v>
+        <v>0.03770753630306339</v>
       </c>
       <c r="X73">
-        <v>0.02920448944627602</v>
+        <v>0.02906795563139992</v>
       </c>
       <c r="Y73">
-        <v>0.02619209899842298</v>
+        <v>0.02530028549589171</v>
       </c>
       <c r="Z73">
-        <v>0.02971605853890165</v>
+        <v>0.02970778756085924</v>
       </c>
       <c r="AA73">
-        <v>0.03068022406276341</v>
+        <v>0.03091369287520174</v>
       </c>
       <c r="AB73">
-        <v>0.02996166619213279</v>
+        <v>0.0300149750374331</v>
       </c>
       <c r="AC73">
-        <v>0.0295181146355799</v>
+        <v>0.02946021429771109</v>
       </c>
     </row>
     <row r="74" spans="1:29">
@@ -8292,88 +8292,88 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>0.01922395403550458</v>
+        <v>0.0169877228260358</v>
       </c>
       <c r="C80">
-        <v>0.06360220071218703</v>
+        <v>0.05991756598882229</v>
       </c>
       <c r="D80">
-        <v>0.04200159977610814</v>
+        <v>0.03902195879722406</v>
       </c>
       <c r="E80">
-        <v>0.03260257607837946</v>
+        <v>0.02992969753313011</v>
       </c>
       <c r="F80">
-        <v>0.0400799940542363</v>
+        <v>0.03716306984963489</v>
       </c>
       <c r="G80">
-        <v>0.01284073164659715</v>
+        <v>0.01081283407873055</v>
       </c>
       <c r="H80">
-        <v>0.0133076309881321</v>
+        <v>0.01126449490370486</v>
       </c>
       <c r="I80">
-        <v>0.06257078623996415</v>
+        <v>0.05891981450370961</v>
       </c>
       <c r="J80">
-        <v>0.03510677224367278</v>
+        <v>0.0323521625171147</v>
       </c>
       <c r="K80">
-        <v>0.0237364760089109</v>
+        <v>0.02135296650044956</v>
       </c>
       <c r="L80">
-        <v>0.02290497399212856</v>
+        <v>0.02054860278977681</v>
       </c>
       <c r="M80">
-        <v>0.05925985198228429</v>
+        <v>0.05571694149612915</v>
       </c>
       <c r="N80">
-        <v>-0.04928641200334452</v>
+        <v>-0.04928662303761545</v>
       </c>
       <c r="O80">
-        <v>-0.01455553060029812</v>
+        <v>-0.01568927741914768</v>
       </c>
       <c r="P80">
-        <v>0.04716583642626718</v>
+        <v>0.04401764668597809</v>
       </c>
       <c r="Q80">
-        <v>0.03885778094858899</v>
+        <v>0.03598074695798919</v>
       </c>
       <c r="R80">
-        <v>0.02668032460441946</v>
+        <v>0.0242007346743683</v>
       </c>
       <c r="S80">
-        <v>-0.01297789898099642</v>
+        <v>-0.01416313605356595</v>
       </c>
       <c r="T80">
-        <v>0.08996043494289005</v>
+        <v>0.08541552830842469</v>
       </c>
       <c r="U80">
-        <v>0.02293280736704279</v>
+        <v>0.02057552774759374</v>
       </c>
       <c r="V80">
-        <v>0.02603334112950209</v>
+        <v>0.02357486724635855</v>
       </c>
       <c r="W80">
-        <v>0.05393290901123952</v>
+        <v>0.05056385764515725</v>
       </c>
       <c r="X80">
-        <v>0.02708624148903878</v>
+        <v>0.02459340336902834</v>
       </c>
       <c r="Y80">
-        <v>0.01537856824592763</v>
+        <v>0.01326784155065218</v>
       </c>
       <c r="Z80">
-        <v>0.029074457784838</v>
+        <v>0.0265167288751981</v>
       </c>
       <c r="AA80">
-        <v>0.03282169278012194</v>
+        <v>0.03014166277161022</v>
       </c>
       <c r="AB80">
-        <v>0.03002901337775173</v>
+        <v>0.02744012997737546</v>
       </c>
       <c r="AC80">
-        <v>0.02830514763707476</v>
+        <v>0.02577252723452426</v>
       </c>
     </row>
     <row r="81" spans="1:29">
@@ -8381,88 +8381,88 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>0.03948405605993477</v>
+        <v>0.04046742669927329</v>
       </c>
       <c r="C81">
-        <v>0.03452940223933559</v>
+        <v>0.03189618580985219</v>
       </c>
       <c r="D81">
-        <v>0.03694102297629036</v>
+        <v>0.03606813868866357</v>
       </c>
       <c r="E81">
-        <v>0.03799038639556042</v>
+        <v>0.03788347170137899</v>
       </c>
       <c r="F81">
-        <v>0.03715556257270394</v>
+        <v>0.03643927875773051</v>
       </c>
       <c r="G81">
-        <v>0.04019671732001903</v>
+        <v>0.04170028605815415</v>
       </c>
       <c r="H81">
-        <v>0.04014458987516468</v>
+        <v>0.04161010884235371</v>
       </c>
       <c r="I81">
-        <v>0.03464455554164272</v>
+        <v>0.0320953938128782</v>
       </c>
       <c r="J81">
-        <v>0.03771080290529109</v>
+        <v>0.0373998097684624</v>
       </c>
       <c r="K81">
-        <v>0.03898025102232334</v>
+        <v>0.03959587552838861</v>
       </c>
       <c r="L81">
-        <v>0.03907308489821532</v>
+        <v>0.03975647232117777</v>
       </c>
       <c r="M81">
-        <v>0.03501420811464952</v>
+        <v>0.03273486961953556</v>
       </c>
       <c r="N81">
-        <v>0.04713296452894344</v>
+        <v>0.05369955943808043</v>
       </c>
       <c r="O81">
-        <v>0.04325540047171365</v>
+        <v>0.04699161640066795</v>
       </c>
       <c r="P81">
-        <v>0.03636445660052516</v>
+        <v>0.03507071495849742</v>
       </c>
       <c r="Q81">
-        <v>0.03729201777963449</v>
+        <v>0.03667533772200263</v>
       </c>
       <c r="R81">
-        <v>0.03865158209591742</v>
+        <v>0.03902729886428742</v>
       </c>
       <c r="S81">
-        <v>0.04307926420866975</v>
+        <v>0.04668691169382546</v>
       </c>
       <c r="T81">
-        <v>0.03158661076569182</v>
+        <v>0.02680534081416997</v>
       </c>
       <c r="U81">
-        <v>0.03906997741318186</v>
+        <v>0.03975109656663537</v>
       </c>
       <c r="V81">
-        <v>0.03872381521430126</v>
+        <v>0.03915225763643976</v>
       </c>
       <c r="W81">
-        <v>0.03560894000065412</v>
+        <v>0.03376371854503904</v>
       </c>
       <c r="X81">
-        <v>0.03860626309857448</v>
+        <v>0.03894889983639199</v>
       </c>
       <c r="Y81">
-        <v>0.03991337800978133</v>
+        <v>0.04121012679185127</v>
       </c>
       <c r="Z81">
-        <v>0.03838428669788593</v>
+        <v>0.03856489456156166</v>
       </c>
       <c r="AA81">
-        <v>0.03796592289182277</v>
+        <v>0.03784115137161893</v>
       </c>
       <c r="AB81">
-        <v>0.03827771438217771</v>
+        <v>0.03838053112808004</v>
       </c>
       <c r="AC81">
-        <v>0.03847017710024028</v>
+        <v>0.03871347957987469</v>
       </c>
     </row>
     <row r="82" spans="1:29">
@@ -9538,88 +9538,88 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>0.08866657495913932</v>
+        <v>0.08743704044211806</v>
       </c>
       <c r="C94">
-        <v>0.1688223242361253</v>
+        <v>0.1673736567633491</v>
       </c>
       <c r="D94">
-        <v>0.06342776756300064</v>
+        <v>0.06226723189527382</v>
       </c>
       <c r="E94">
-        <v>0.05780172541812637</v>
+        <v>0.05665657044680034</v>
       </c>
       <c r="F94">
-        <v>0.1182234591510196</v>
+        <v>0.1169131208556755</v>
       </c>
       <c r="G94">
-        <v>0.05435454596756498</v>
+        <v>0.05321881503168037</v>
       </c>
       <c r="H94">
-        <v>-0.02963761026084921</v>
+        <v>-0.03054372012001026</v>
       </c>
       <c r="I94">
-        <v>0.116048773534293</v>
+        <v>0.1147443804804485</v>
       </c>
       <c r="J94">
-        <v>0.051307477653727</v>
+        <v>0.05018007691364271</v>
       </c>
       <c r="K94">
-        <v>0.02977190804982072</v>
+        <v>0.02870338210117358</v>
       </c>
       <c r="L94">
-        <v>0.07796630292825515</v>
+        <v>0.07676602123787027</v>
       </c>
       <c r="M94">
-        <v>0.01850759648119042</v>
+        <v>0.01746986535276322</v>
       </c>
       <c r="N94">
-        <v>0.01898723919544057</v>
+        <v>0.01794819680080191</v>
       </c>
       <c r="O94">
-        <v>-0.06649402207349051</v>
+        <v>-0.06729937241718478</v>
       </c>
       <c r="P94">
-        <v>0.1306525641211932</v>
+        <v>0.1293082466473863</v>
       </c>
       <c r="Q94">
-        <v>0.1267506489712081</v>
+        <v>0.1254169987072724</v>
       </c>
       <c r="R94">
-        <v>0.09946688105326945</v>
+        <v>0.09820782023253556</v>
       </c>
       <c r="S94">
-        <v>-0.01206190194991016</v>
+        <v>-0.01301606097518099</v>
       </c>
       <c r="T94">
-        <v>0.2153607844495772</v>
+        <v>0.2137848882947058</v>
       </c>
       <c r="U94">
-        <v>0.05654054243348385</v>
+        <v>0.05539883533405305</v>
       </c>
       <c r="V94">
-        <v>0.06324186559309466</v>
+        <v>0.06208183815152146</v>
       </c>
       <c r="W94">
-        <v>0.1235424572695651</v>
+        <v>0.1222175776869162</v>
       </c>
       <c r="X94">
-        <v>0.06551754652570181</v>
+        <v>0.06435129773764235</v>
       </c>
       <c r="Y94">
-        <v>0.04021322544421462</v>
+        <v>0.03911615460935224</v>
       </c>
       <c r="Z94">
-        <v>0.06981476788503457</v>
+        <v>0.0686367711833632</v>
       </c>
       <c r="AA94">
-        <v>0.07791383552378855</v>
+        <v>0.07671369727086792</v>
       </c>
       <c r="AB94">
-        <v>0.0718778918475543</v>
+        <v>0.07069425489604342</v>
       </c>
       <c r="AC94">
-        <v>0.06815202324004796</v>
+        <v>0.06697857221541172</v>
       </c>
     </row>
     <row r="95" spans="1:29">
@@ -9627,88 +9627,88 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>0.0179002102195522</v>
+        <v>0.01286783410465882</v>
       </c>
       <c r="C95">
-        <v>0.100472015080037</v>
+        <v>0.09723289388597325</v>
       </c>
       <c r="D95">
-        <v>0.06028113916829748</v>
+        <v>0.05616917177542585</v>
       </c>
       <c r="E95">
-        <v>0.04279296852689838</v>
+        <v>0.03830120141774363</v>
       </c>
       <c r="F95">
-        <v>0.05670572858839817</v>
+        <v>0.05251611214053465</v>
       </c>
       <c r="G95">
-        <v>0.006023350880832973</v>
+        <v>0.000733038821713286</v>
       </c>
       <c r="H95">
-        <v>0.006892081040444475</v>
+        <v>0.001620635646964821</v>
       </c>
       <c r="I95">
-        <v>0.09855292721811351</v>
+        <v>0.09527212819276445</v>
       </c>
       <c r="J95">
-        <v>0.04745236840358662</v>
+        <v>0.04306179190993437</v>
       </c>
       <c r="K95">
-        <v>0.02629637527157384</v>
+        <v>0.02144634304901848</v>
       </c>
       <c r="L95">
-        <v>0.02474925190793437</v>
+        <v>0.01986562000096294</v>
       </c>
       <c r="M95">
-        <v>0.09239248065016287</v>
+        <v>0.08897789199600345</v>
       </c>
       <c r="N95">
-        <v>-0.1095727072369319</v>
+        <v>-0.1173734791364104</v>
       </c>
       <c r="O95">
-        <v>-0.04495114652638216</v>
+        <v>-0.05134849831252192</v>
       </c>
       <c r="P95">
-        <v>0.06988990861872169</v>
+        <v>0.06598661987989188</v>
       </c>
       <c r="Q95">
-        <v>0.05443163374204941</v>
+        <v>0.05019262959119771</v>
       </c>
       <c r="R95">
-        <v>0.0317738086983177</v>
+        <v>0.02704273275221313</v>
       </c>
       <c r="S95">
-        <v>-0.04201574686627893</v>
+        <v>-0.04834934904813215</v>
       </c>
       <c r="T95">
-        <v>0.1495151192211504</v>
+        <v>0.1473410926799456</v>
       </c>
       <c r="U95">
-        <v>0.02480103971331502</v>
+        <v>0.01991853250910375</v>
       </c>
       <c r="V95">
-        <v>0.03057000734879513</v>
+        <v>0.02581278782138724</v>
       </c>
       <c r="W95">
-        <v>0.0824809738096019</v>
+        <v>0.07885113179571876</v>
       </c>
       <c r="X95">
-        <v>0.03252907264622786</v>
+        <v>0.02781439916090762</v>
       </c>
       <c r="Y95">
-        <v>0.01074534339158752</v>
+        <v>0.005557581304826295</v>
       </c>
       <c r="Z95">
-        <v>0.03622842132021297</v>
+        <v>0.03159408851806778</v>
       </c>
       <c r="AA95">
-        <v>0.04320066515515341</v>
+        <v>0.03871775220615732</v>
       </c>
       <c r="AB95">
-        <v>0.03800450271254005</v>
+        <v>0.033408741995648</v>
       </c>
       <c r="AC95">
-        <v>0.03479701444510374</v>
+        <v>0.03013159503383288</v>
       </c>
     </row>
     <row r="96" spans="1:29">
@@ -9983,88 +9983,88 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>0.02833760252888654</v>
+        <v>0.02020033818166684</v>
       </c>
       <c r="C99">
-        <v>0.1220099825847931</v>
+        <v>0.1284121639562436</v>
       </c>
       <c r="D99">
-        <v>0.07641602942432513</v>
+        <v>0.07574130288887107</v>
       </c>
       <c r="E99">
-        <v>0.05657682923278817</v>
+        <v>0.05282274276098436</v>
       </c>
       <c r="F99">
-        <v>0.07235995702452569</v>
+        <v>0.07105566343363134</v>
       </c>
       <c r="G99">
-        <v>0.01486407262692046</v>
+        <v>0.004635501786456973</v>
       </c>
       <c r="H99">
-        <v>0.01584959088965738</v>
+        <v>0.005773988184275654</v>
       </c>
       <c r="I99">
-        <v>0.1198329013417888</v>
+        <v>0.1258971650203302</v>
       </c>
       <c r="J99">
-        <v>0.06186261748483175</v>
+        <v>0.05892896955985578</v>
       </c>
       <c r="K99">
-        <v>0.03786250954883071</v>
+        <v>0.03120366251639692</v>
       </c>
       <c r="L99">
-        <v>0.03610739800734177</v>
+        <v>0.02917612970225045</v>
       </c>
       <c r="M99">
-        <v>0.1128442725573968</v>
+        <v>0.1178237897098229</v>
       </c>
       <c r="N99">
-        <v>-0.1162721900146366</v>
+        <v>-0.1468551980038974</v>
       </c>
       <c r="O99">
-        <v>-0.04296320270459571</v>
+        <v>-0.06216748794709932</v>
       </c>
       <c r="P99">
-        <v>0.08731655782322001</v>
+        <v>0.08833376695616645</v>
       </c>
       <c r="Q99">
-        <v>0.0697801432843479</v>
+        <v>0.06807542150088271</v>
       </c>
       <c r="R99">
-        <v>0.04407630403410078</v>
+        <v>0.03838193690034829</v>
       </c>
       <c r="S99">
-        <v>-0.0396331813608482</v>
+        <v>-0.05832059423883483</v>
       </c>
       <c r="T99">
-        <v>0.1776462169869584</v>
+        <v>0.1926840283018214</v>
       </c>
       <c r="U99">
-        <v>0.03616614792804503</v>
+        <v>0.02924399854661649</v>
       </c>
       <c r="V99">
-        <v>0.04271066914559595</v>
+        <v>0.03680433372064505</v>
       </c>
       <c r="W99">
-        <v>0.1016003081404334</v>
+        <v>0.1048345828830314</v>
       </c>
       <c r="X99">
-        <v>0.04493310220740826</v>
+        <v>0.03937172380016432</v>
       </c>
       <c r="Y99">
-        <v>0.020220868180026</v>
+        <v>0.01082375735076229</v>
       </c>
       <c r="Z99">
-        <v>0.04912977437091912</v>
+        <v>0.0442197863423973</v>
       </c>
       <c r="AA99">
-        <v>0.05703933472814392</v>
+        <v>0.05335703647758845</v>
       </c>
       <c r="AB99">
-        <v>0.05114462400964736</v>
+        <v>0.04654737274447124</v>
       </c>
       <c r="AC99">
-        <v>0.0475059357125972</v>
+        <v>0.04234390205424876</v>
       </c>
     </row>
     <row r="100" spans="1:29">
@@ -10161,88 +10161,88 @@
         <v>100</v>
       </c>
       <c r="B101">
-        <v>0.04863312114280263</v>
+        <v>0.04780501255048697</v>
       </c>
       <c r="C101">
-        <v>0.09074487292664335</v>
+        <v>0.08917302319082977</v>
       </c>
       <c r="D101">
-        <v>0.03537330632011821</v>
+        <v>0.03477938104768472</v>
       </c>
       <c r="E101">
-        <v>0.03241752969189827</v>
+        <v>0.03187580677620075</v>
       </c>
       <c r="F101">
-        <v>0.06416154152211978</v>
+        <v>0.06305918347115155</v>
       </c>
       <c r="G101">
-        <v>0.03060647101319065</v>
+        <v>0.03009673344114632</v>
       </c>
       <c r="H101">
-        <v>-0.01352082948346997</v>
+        <v>-0.01325122904318647</v>
       </c>
       <c r="I101">
-        <v>0.06301901810083639</v>
+        <v>0.06193683830510154</v>
       </c>
       <c r="J101">
-        <v>0.02900562034860092</v>
+        <v>0.02852415560904199</v>
       </c>
       <c r="K101">
-        <v>0.01769139061631506</v>
+        <v>0.01740974796447362</v>
       </c>
       <c r="L101">
-        <v>0.04301147573559609</v>
+        <v>0.04228265175639642</v>
       </c>
       <c r="M101">
-        <v>0.01177341346467235</v>
+        <v>0.0115962889795543</v>
       </c>
       <c r="N101">
-        <v>0.01202540530692476</v>
+        <v>0.01184383036099779</v>
       </c>
       <c r="O101">
-        <v>-0.03288423235721236</v>
+        <v>-0.032272652332008</v>
       </c>
       <c r="P101">
-        <v>0.07069147091733451</v>
+        <v>0.06947378693121434</v>
       </c>
       <c r="Q101">
-        <v>0.06864150589598629</v>
+        <v>0.06746002660961203</v>
       </c>
       <c r="R101">
-        <v>0.0543073218523966</v>
+        <v>0.05337900046091144</v>
       </c>
       <c r="S101">
-        <v>-0.004287008173188011</v>
+        <v>-0.004180487456004498</v>
       </c>
       <c r="T101">
-        <v>0.1151949729205776</v>
+        <v>0.1131913067782306</v>
       </c>
       <c r="U101">
-        <v>0.03175493686128621</v>
+        <v>0.03122491608403314</v>
       </c>
       <c r="V101">
-        <v>0.03527563824660604</v>
+        <v>0.03468343790276374</v>
       </c>
       <c r="W101">
-        <v>0.06695600518227321</v>
+        <v>0.06580429374394807</v>
       </c>
       <c r="X101">
-        <v>0.03647122198748047</v>
+        <v>0.03585790628317656</v>
       </c>
       <c r="Y101">
-        <v>0.02317698797364972</v>
+        <v>0.02279846347105425</v>
       </c>
       <c r="Z101">
-        <v>0.03872887063872198</v>
+        <v>0.03807568230698358</v>
       </c>
       <c r="AA101">
-        <v>0.04298391072206219</v>
+        <v>0.04225557357216356</v>
       </c>
       <c r="AB101">
-        <v>0.03981278246030193</v>
+        <v>0.03914045102044088</v>
       </c>
       <c r="AC101">
-        <v>0.03785530772650189</v>
+        <v>0.03721754750334912</v>
       </c>
     </row>
     <row r="102" spans="1:29">
@@ -10695,88 +10695,88 @@
         <v>106</v>
       </c>
       <c r="B107">
-        <v>0.005813340663761987</v>
+        <v>0.002190068909472521</v>
       </c>
       <c r="C107">
-        <v>0.0379267380173474</v>
+        <v>0.04358069622634951</v>
       </c>
       <c r="D107">
-        <v>0.02229591136504067</v>
+        <v>0.02343428463691665</v>
       </c>
       <c r="E107">
-        <v>0.01549450289705992</v>
+        <v>0.01466801926709548</v>
       </c>
       <c r="F107">
-        <v>0.02090538125795969</v>
+        <v>0.02164204469414834</v>
       </c>
       <c r="G107">
-        <v>0.001194254234667153</v>
+        <v>-0.003763424046319113</v>
       </c>
       <c r="H107">
-        <v>0.00153211625495101</v>
+        <v>-0.003327957165872876</v>
       </c>
       <c r="I107">
-        <v>0.03718037633649859</v>
+        <v>0.04261871833794768</v>
       </c>
       <c r="J107">
-        <v>0.01730661248970057</v>
+        <v>0.01700362866962893</v>
       </c>
       <c r="K107">
-        <v>0.009078733554439743</v>
+        <v>0.00639880019670061</v>
       </c>
       <c r="L107">
-        <v>0.0084770343737628</v>
+        <v>0.005623276315808921</v>
       </c>
       <c r="M107">
-        <v>0.03478448746321559</v>
+        <v>0.03953068182923375</v>
       </c>
       <c r="N107">
-        <v>-0.04376276412185446</v>
+        <v>-0.06170806227890488</v>
       </c>
       <c r="O107">
-        <v>-0.01863048246453739</v>
+        <v>-0.02931532312872421</v>
       </c>
       <c r="P107">
-        <v>0.02603290405839202</v>
+        <v>0.02825085605579609</v>
       </c>
       <c r="Q107">
-        <v>0.02002095210512805</v>
+        <v>0.02050211306218886</v>
       </c>
       <c r="R107">
-        <v>0.01120898850536445</v>
+        <v>0.009144463876965579</v>
       </c>
       <c r="S107">
-        <v>-0.01748886207927697</v>
+        <v>-0.02784390036446822</v>
       </c>
       <c r="T107">
-        <v>0.05700032728184151</v>
+        <v>0.06816444911145866</v>
       </c>
       <c r="U107">
-        <v>0.008497175417973582</v>
+        <v>0.005649235900387354</v>
       </c>
       <c r="V107">
-        <v>0.01074081233872599</v>
+        <v>0.008541036434561607</v>
       </c>
       <c r="W107">
-        <v>0.03092975571693116</v>
+        <v>0.03456235775687647</v>
       </c>
       <c r="X107">
-        <v>0.01150272183609468</v>
+        <v>0.009523053743647574</v>
       </c>
       <c r="Y107">
-        <v>0.003030707029355704</v>
+        <v>-0.001396438941222331</v>
       </c>
       <c r="Z107">
-        <v>0.01294145330282074</v>
+        <v>0.0113774199227424</v>
       </c>
       <c r="AA107">
-        <v>0.01565306215157776</v>
+        <v>0.01487238465824762</v>
       </c>
       <c r="AB107">
-        <v>0.01363219765048854</v>
+        <v>0.01226771320285732</v>
       </c>
       <c r="AC107">
-        <v>0.01238475797767065</v>
+        <v>0.01065990104803006</v>
       </c>
     </row>
     <row r="108" spans="1:29">
@@ -10784,88 +10784,88 @@
         <v>107</v>
       </c>
       <c r="B108">
-        <v>0.05052375163557913</v>
+        <v>0.05100037771808085</v>
       </c>
       <c r="C108">
-        <v>0.09564594802073276</v>
+        <v>0.08048666939025109</v>
       </c>
       <c r="D108">
-        <v>0.07368323812423741</v>
+        <v>0.06613455619984801</v>
       </c>
       <c r="E108">
-        <v>0.06412665072213838</v>
+        <v>0.0598895516100095</v>
       </c>
       <c r="F108">
-        <v>0.07172941891662338</v>
+        <v>0.06485778140505209</v>
       </c>
       <c r="G108">
-        <v>0.04403352194487514</v>
+        <v>0.04675916560938918</v>
       </c>
       <c r="H108">
-        <v>0.0445082483110231</v>
+        <v>0.04706938809894232</v>
       </c>
       <c r="I108">
-        <v>0.09459724308407325</v>
+        <v>0.07980136543526539</v>
       </c>
       <c r="J108">
-        <v>0.06667282682459998</v>
+        <v>0.06155341767195931</v>
       </c>
       <c r="K108">
-        <v>0.05511192079331528</v>
+        <v>0.05399863810575066</v>
       </c>
       <c r="L108">
-        <v>0.05426647961198042</v>
+        <v>0.05344616222333315</v>
       </c>
       <c r="M108">
-        <v>0.09123080486307293</v>
+        <v>0.07760147741488931</v>
       </c>
       <c r="N108">
-        <v>-0.01913511103526138</v>
+        <v>0.005479953031044364</v>
       </c>
       <c r="O108">
-        <v>0.01617799321410397</v>
+        <v>0.02855623422220421</v>
       </c>
       <c r="P108">
-        <v>0.07893404719755576</v>
+        <v>0.06956583615194017</v>
       </c>
       <c r="Q108">
-        <v>0.07048671682928509</v>
+        <v>0.06404570488519262</v>
       </c>
       <c r="R108">
-        <v>0.05810511958781586</v>
+        <v>0.05595462295928212</v>
       </c>
       <c r="S108">
-        <v>0.01778207199324516</v>
+        <v>0.02960446189142419</v>
       </c>
       <c r="T108">
-        <v>0.1224460474024997</v>
+        <v>0.09799990257749767</v>
       </c>
       <c r="U108">
-        <v>0.05429477958106418</v>
+        <v>0.05346465558601422</v>
       </c>
       <c r="V108">
-        <v>0.05744729018716697</v>
+        <v>0.05552474695297042</v>
       </c>
       <c r="W108">
-        <v>0.08581456188657226</v>
+        <v>0.07406209030684087</v>
       </c>
       <c r="X108">
-        <v>0.0585178411970602</v>
+        <v>0.05622432680183687</v>
       </c>
       <c r="Y108">
-        <v>0.04661390242413792</v>
+        <v>0.04844538342527881</v>
       </c>
       <c r="Z108">
-        <v>0.06053938762742769</v>
+        <v>0.05754535974016838</v>
       </c>
       <c r="AA108">
-        <v>0.06434944066062612</v>
+        <v>0.06003513958298405</v>
       </c>
       <c r="AB108">
-        <v>0.06150994523502761</v>
+        <v>0.0581795962577806</v>
       </c>
       <c r="AC108">
-        <v>0.0597571808894877</v>
+        <v>0.05703420607588389</v>
       </c>
     </row>
     <row r="109" spans="1:29">
@@ -11051,88 +11051,88 @@
         <v>110</v>
       </c>
       <c r="B111">
-        <v>0.02763507952333548</v>
+        <v>0.02782393146844528</v>
       </c>
       <c r="C111">
-        <v>0.03306346177793738</v>
+        <v>0.03069401553755535</v>
       </c>
       <c r="D111">
-        <v>0.03042125917663999</v>
+        <v>0.02929703514124739</v>
       </c>
       <c r="E111">
-        <v>0.02927156315951137</v>
+        <v>0.02868917002263257</v>
       </c>
       <c r="F111">
-        <v>0.03018620684397468</v>
+        <v>0.02917275871343725</v>
       </c>
       <c r="G111">
-        <v>0.02685427870901829</v>
+        <v>0.02741110792853702</v>
       </c>
       <c r="H111">
-        <v>0.02691139020598073</v>
+        <v>0.02744130381193413</v>
       </c>
       <c r="I111">
-        <v>0.03293729834342982</v>
+        <v>0.03062731064344488</v>
       </c>
       <c r="J111">
-        <v>0.02957787841628024</v>
+        <v>0.02885112444981618</v>
       </c>
       <c r="K111">
-        <v>0.02818705478234928</v>
+        <v>0.02811577079057396</v>
       </c>
       <c r="L111">
-        <v>0.02808534479760266</v>
+        <v>0.02806199487848833</v>
       </c>
       <c r="M111">
-        <v>0.03253230224474468</v>
+        <v>0.03041318186688303</v>
       </c>
       <c r="N111">
-        <v>0.019254837330104</v>
+        <v>0.02339314555728589</v>
       </c>
       <c r="O111">
-        <v>0.02350314622947384</v>
+        <v>0.02563930345863916</v>
       </c>
       <c r="P111">
-        <v>0.03105295269068361</v>
+        <v>0.02963102294943459</v>
       </c>
       <c r="Q111">
-        <v>0.03003670476962789</v>
+        <v>0.02909371425750973</v>
       </c>
       <c r="R111">
-        <v>0.02854714867232466</v>
+        <v>0.02830615895569001</v>
       </c>
       <c r="S111">
-        <v>0.02369612337769038</v>
+        <v>0.02574133397396056</v>
       </c>
       <c r="T111">
-        <v>0.03628762184904195</v>
+        <v>0.0323986873941648</v>
       </c>
       <c r="U111">
-        <v>0.02808874939804961</v>
+        <v>0.02806379495244151</v>
       </c>
       <c r="V111">
-        <v>0.02846800914164762</v>
+        <v>0.02826431645168425</v>
       </c>
       <c r="W111">
-        <v>0.03188070636476393</v>
+        <v>0.03006867131716168</v>
       </c>
       <c r="X111">
-        <v>0.02859680074689543</v>
+        <v>0.02833241090729181</v>
       </c>
       <c r="Y111">
-        <v>0.02716470889030176</v>
+        <v>0.0275752379908806</v>
       </c>
       <c r="Z111">
-        <v>0.02884000093767939</v>
+        <v>0.0284609952553417</v>
       </c>
       <c r="AA111">
-        <v>0.02929836568787829</v>
+        <v>0.0287033410050855</v>
       </c>
       <c r="AB111">
-        <v>0.02895676293324346</v>
+        <v>0.0285227294383134</v>
       </c>
       <c r="AC111">
-        <v>0.02874589831157007</v>
+        <v>0.02841124149162529</v>
       </c>
     </row>
     <row r="112" spans="1:29">
@@ -11140,88 +11140,88 @@
         <v>111</v>
       </c>
       <c r="B112">
-        <v>0.01849490548654761</v>
+        <v>0.01415265751376622</v>
       </c>
       <c r="C112">
-        <v>0.06969696459315072</v>
+        <v>0.07275806246264013</v>
       </c>
       <c r="D112">
-        <v>0.04477495147431387</v>
+        <v>0.04423255594092635</v>
       </c>
       <c r="E112">
-        <v>0.03393068873402114</v>
+        <v>0.03182031275469712</v>
       </c>
       <c r="F112">
-        <v>0.04255787042404864</v>
+        <v>0.04169490540455346</v>
       </c>
       <c r="G112">
-        <v>0.01113016815412032</v>
+        <v>0.00572304704028179</v>
       </c>
       <c r="H112">
-        <v>0.01166886018168678</v>
+        <v>0.006339628970171235</v>
       </c>
       <c r="I112">
-        <v>0.06850695487611722</v>
+        <v>0.07139598830826596</v>
       </c>
       <c r="J112">
-        <v>0.03681994213341801</v>
+        <v>0.03512732556679959</v>
       </c>
       <c r="K112">
-        <v>0.02370129451956896</v>
+        <v>0.02011184241620002</v>
       </c>
       <c r="L112">
-        <v>0.02274193675762928</v>
+        <v>0.01901377036381903</v>
       </c>
       <c r="M112">
-        <v>0.06468691545917299</v>
+        <v>0.06702360639908203</v>
       </c>
       <c r="N112">
-        <v>-0.06054994360117666</v>
+        <v>-0.07632134823400843</v>
       </c>
       <c r="O112">
-        <v>-0.02047867500467378</v>
+        <v>-0.03045614351589793</v>
       </c>
       <c r="P112">
-        <v>0.05073326596403125</v>
+        <v>0.0510523877909622</v>
       </c>
       <c r="Q112">
-        <v>0.04114772395899913</v>
+        <v>0.04008086475729379</v>
       </c>
       <c r="R112">
-        <v>0.02709780341921681</v>
+        <v>0.02399945519876186</v>
       </c>
       <c r="S112">
-        <v>-0.01865845916765706</v>
+        <v>-0.0283727412448951</v>
       </c>
       <c r="T112">
-        <v>0.1001081675606456</v>
+        <v>0.1075664450939275</v>
       </c>
       <c r="U112">
-        <v>0.0227740499259993</v>
+        <v>0.01905052680036387</v>
       </c>
       <c r="V112">
-        <v>0.026351336656682</v>
+        <v>0.02314505622218659</v>
       </c>
       <c r="W112">
-        <v>0.05854087614292734</v>
+        <v>0.05998890644277061</v>
       </c>
       <c r="X112">
-        <v>0.02756613603429434</v>
+        <v>0.02453550439358505</v>
       </c>
       <c r="Y112">
-        <v>0.01405823470232163</v>
+        <v>0.009074485024783845</v>
       </c>
       <c r="Z112">
-        <v>0.02986007002037298</v>
+        <v>0.02716112009197374</v>
       </c>
       <c r="AA112">
-        <v>0.03418349787259752</v>
+        <v>0.03210967576469245</v>
       </c>
       <c r="AB112">
-        <v>0.03096140266753653</v>
+        <v>0.02842169528946831</v>
       </c>
       <c r="AC112">
-        <v>0.02897246704804151</v>
+        <v>0.02614517791044921</v>
       </c>
     </row>
     <row r="113" spans="1:29">
@@ -11941,88 +11941,88 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>0.02441864456427719</v>
+        <v>0.02465671752133003</v>
       </c>
       <c r="C121">
-        <v>0.03826933315208517</v>
+        <v>0.04002442595728654</v>
       </c>
       <c r="D121">
-        <v>0.02005744945694194</v>
+        <v>0.01981785522094999</v>
       </c>
       <c r="E121">
-        <v>0.01908528515889189</v>
+        <v>0.01873921300113788</v>
       </c>
       <c r="F121">
-        <v>0.02952599122699721</v>
+        <v>0.03032345487496065</v>
       </c>
       <c r="G121">
-        <v>0.01848962222133982</v>
+        <v>0.0180783090834465</v>
       </c>
       <c r="H121">
-        <v>0.003976013275857743</v>
+        <v>0.001975072828175446</v>
       </c>
       <c r="I121">
-        <v>0.02915021165378683</v>
+        <v>0.02990651741508818</v>
       </c>
       <c r="J121">
-        <v>0.01796309736565034</v>
+        <v>0.01749411571174349</v>
       </c>
       <c r="K121">
-        <v>0.01424181135890334</v>
+        <v>0.0133652496271481</v>
       </c>
       <c r="L121">
-        <v>0.02256966757832865</v>
+        <v>0.02260522823654006</v>
       </c>
       <c r="M121">
-        <v>0.01229536992331767</v>
+        <v>0.0112056209357576</v>
       </c>
       <c r="N121">
-        <v>0.01237825083864082</v>
+        <v>0.01129757952204136</v>
       </c>
       <c r="O121">
-        <v>-0.002392671279967019</v>
+        <v>-0.005091152562282439</v>
       </c>
       <c r="P121">
-        <v>0.03167370569439199</v>
+        <v>0.03270640136382053</v>
       </c>
       <c r="Q121">
-        <v>0.03099946570379895</v>
+        <v>0.03195831410984698</v>
       </c>
       <c r="R121">
-        <v>0.02628490715569621</v>
+        <v>0.0267273856464589</v>
       </c>
       <c r="S121">
-        <v>0.007013046361079739</v>
+        <v>0.005344742044847323</v>
       </c>
       <c r="T121">
-        <v>0.046311048507339</v>
+        <v>0.04894692364547212</v>
       </c>
       <c r="U121">
-        <v>0.0188673562775566</v>
+        <v>0.01849741509434768</v>
       </c>
       <c r="V121">
-        <v>0.02002532611811405</v>
+        <v>0.01978221351967523</v>
       </c>
       <c r="W121">
-        <v>0.03044509917874914</v>
+        <v>0.03134322966335101</v>
       </c>
       <c r="X121">
-        <v>0.02041855739855327</v>
+        <v>0.02021851411421803</v>
       </c>
       <c r="Y121">
-        <v>0.01604604171019687</v>
+        <v>0.01536709132723432</v>
       </c>
       <c r="Z121">
-        <v>0.02116110519303922</v>
+        <v>0.02104239069862607</v>
       </c>
       <c r="AA121">
-        <v>0.02256060135804086</v>
+        <v>0.02259516902330199</v>
       </c>
       <c r="AB121">
-        <v>0.02151760722540323</v>
+        <v>0.02143793921272799</v>
       </c>
       <c r="AC121">
-        <v>0.02087378758342932</v>
+        <v>0.02072360414696771</v>
       </c>
     </row>
     <row r="122" spans="1:29">
@@ -12030,88 +12030,88 @@
         <v>121</v>
       </c>
       <c r="B122">
-        <v>0.03567960358758778</v>
+        <v>0.03585731887049465</v>
       </c>
       <c r="C122">
-        <v>0.04949602956559242</v>
+        <v>0.0509807373637344</v>
       </c>
       <c r="D122">
-        <v>0.03132919681942366</v>
+        <v>0.03109537665218803</v>
       </c>
       <c r="E122">
-        <v>0.03035943737552925</v>
+        <v>0.03003388086947732</v>
       </c>
       <c r="F122">
-        <v>0.04077431614733698</v>
+        <v>0.04143397597896195</v>
       </c>
       <c r="G122">
-        <v>0.02976524793632885</v>
+        <v>0.02938348288901574</v>
       </c>
       <c r="H122">
-        <v>0.01528754147446591</v>
+        <v>0.01353622875877969</v>
       </c>
       <c r="I122">
-        <v>0.04039946614443694</v>
+        <v>0.04102366628851999</v>
       </c>
       <c r="J122">
-        <v>0.02924002555131207</v>
+        <v>0.0288085760394968</v>
       </c>
       <c r="K122">
-        <v>0.02552794493313528</v>
+        <v>0.02474534371308301</v>
       </c>
       <c r="L122">
-        <v>0.03383520043756107</v>
+        <v>0.03383844070674162</v>
       </c>
       <c r="M122">
-        <v>0.02358631843241655</v>
+        <v>0.02262004516086114</v>
       </c>
       <c r="N122">
-        <v>0.02366899432425341</v>
+        <v>0.02271054194443897</v>
       </c>
       <c r="O122">
-        <v>0.008934611207860304</v>
+        <v>0.006582330316939573</v>
       </c>
       <c r="P122">
-        <v>0.04291671778842</v>
+        <v>0.04377904239847469</v>
       </c>
       <c r="Q122">
-        <v>0.04224414567315063</v>
+        <v>0.04304284697555598</v>
       </c>
       <c r="R122">
-        <v>0.03754124958348125</v>
+        <v>0.03789507100168849</v>
       </c>
       <c r="S122">
-        <v>0.01831706181554532</v>
+        <v>0.01685233265025388</v>
       </c>
       <c r="T122">
-        <v>0.05751785203583768</v>
+        <v>0.05976140021309409</v>
       </c>
       <c r="U122">
-        <v>0.0301420475874079</v>
+        <v>0.02979592665851495</v>
       </c>
       <c r="V122">
-        <v>0.03129715294447346</v>
+        <v>0.03106030152264379</v>
       </c>
       <c r="W122">
-        <v>0.04169115049103553</v>
+        <v>0.04243754010551695</v>
       </c>
       <c r="X122">
-        <v>0.03168941148411075</v>
+        <v>0.03148966654525715</v>
       </c>
       <c r="Y122">
-        <v>0.0273277121387787</v>
+        <v>0.02671536350580548</v>
       </c>
       <c r="Z122">
-        <v>0.03243012242946235</v>
+        <v>0.03230044652749776</v>
       </c>
       <c r="AA122">
-        <v>0.03382615664448808</v>
+        <v>0.03382854139793146</v>
       </c>
       <c r="AB122">
-        <v>0.0327857425785935</v>
+        <v>0.03268970727760064</v>
       </c>
       <c r="AC122">
-        <v>0.0321435155607723</v>
+        <v>0.03198672750746054</v>
       </c>
     </row>
     <row r="123" spans="1:29">
@@ -12119,88 +12119,88 @@
         <v>122</v>
       </c>
       <c r="B123">
-        <v>0.05357079315332099</v>
+        <v>0.06156489248851978</v>
       </c>
       <c r="C123">
-        <v>0.1446219457779236</v>
+        <v>0.1390111980841112</v>
       </c>
       <c r="D123">
-        <v>0.1003038449087551</v>
+        <v>0.1013150999635209</v>
       </c>
       <c r="E123">
-        <v>0.08101980362026034</v>
+        <v>0.08491247669411238</v>
       </c>
       <c r="F123">
-        <v>0.09636127328934969</v>
+        <v>0.09796162669418332</v>
       </c>
       <c r="G123">
-        <v>0.04047429206341721</v>
+        <v>0.05042526826186698</v>
       </c>
       <c r="H123">
-        <v>0.04143223263993761</v>
+        <v>0.05124007352784193</v>
       </c>
       <c r="I123">
-        <v>0.1425057856417699</v>
+        <v>0.1372112342190796</v>
       </c>
       <c r="J123">
-        <v>0.08615768004222069</v>
+        <v>0.08928265253502764</v>
       </c>
       <c r="K123">
-        <v>0.06282916538951784</v>
+        <v>0.0694398803920611</v>
       </c>
       <c r="L123">
-        <v>0.06112316700726328</v>
+        <v>0.06798879198462045</v>
       </c>
       <c r="M123">
-        <v>0.1357127191508301</v>
+        <v>0.1314331865148669</v>
       </c>
       <c r="N123">
-        <v>-0.08699239403199491</v>
+        <v>-0.05799536827091191</v>
       </c>
       <c r="O123">
-        <v>-0.01573480680790791</v>
+        <v>0.002614922945434368</v>
       </c>
       <c r="P123">
-        <v>0.11089934461042</v>
+        <v>0.1103274219844879</v>
       </c>
       <c r="Q123">
-        <v>0.09385365029034205</v>
+        <v>0.09582869227763202</v>
       </c>
       <c r="R123">
-        <v>0.06886907971344736</v>
+        <v>0.07457731179208757</v>
       </c>
       <c r="S123">
-        <v>-0.01249796921040289</v>
+        <v>0.005368112844888081</v>
       </c>
       <c r="T123">
-        <v>0.1987013154596411</v>
+        <v>0.1850100379676117</v>
       </c>
       <c r="U123">
-        <v>0.06118027293318769</v>
+        <v>0.06803736515325121</v>
       </c>
       <c r="V123">
-        <v>0.0675416592871859</v>
+        <v>0.07344823428979688</v>
       </c>
       <c r="W123">
-        <v>0.1247833937763331</v>
+        <v>0.1221369189937216</v>
       </c>
       <c r="X123">
-        <v>0.06970190216548433</v>
+        <v>0.07528569406148344</v>
       </c>
       <c r="Y123">
-        <v>0.04568118879427327</v>
+        <v>0.05485415140940006</v>
       </c>
       <c r="Z123">
-        <v>0.07378113915558955</v>
+        <v>0.07875541218614082</v>
       </c>
       <c r="AA123">
-        <v>0.08146936685781468</v>
+        <v>0.08529486627267956</v>
       </c>
       <c r="AB123">
-        <v>0.07573960740270763</v>
+        <v>0.08042124645614639</v>
       </c>
       <c r="AC123">
-        <v>0.07220274025691359</v>
+        <v>0.07741285737013981</v>
       </c>
     </row>
     <row r="124" spans="1:29">
@@ -12208,88 +12208,88 @@
         <v>123</v>
       </c>
       <c r="B124">
-        <v>0.05212198053486391</v>
+        <v>0.05015282530151306</v>
       </c>
       <c r="C124">
-        <v>0.06790852555502733</v>
+        <v>0.07146806894256368</v>
       </c>
       <c r="D124">
-        <v>0.0602246064127426</v>
+        <v>0.06109311936197229</v>
       </c>
       <c r="E124">
-        <v>0.05688111896424594</v>
+        <v>0.05657868954313132</v>
       </c>
       <c r="F124">
-        <v>0.05954103918079803</v>
+        <v>0.0601701560362207</v>
       </c>
       <c r="G124">
-        <v>0.04985129534195049</v>
+        <v>0.04708691011505165</v>
       </c>
       <c r="H124">
-        <v>0.0500173840909884</v>
+        <v>0.04731116578006631</v>
       </c>
       <c r="I124">
-        <v>0.06754162347530299</v>
+        <v>0.07097267193126426</v>
       </c>
       <c r="J124">
-        <v>0.05777192940546815</v>
+        <v>0.0577814759392928</v>
       </c>
       <c r="K124">
-        <v>0.05372720689287335</v>
+        <v>0.05232022740731299</v>
       </c>
       <c r="L124">
-        <v>0.0534314190912974</v>
+        <v>0.05192085002305383</v>
       </c>
       <c r="M124">
-        <v>0.0663638344315297</v>
+        <v>0.06938240247118151</v>
       </c>
       <c r="N124">
-        <v>0.02775098666257925</v>
+        <v>0.01724672257296795</v>
       </c>
       <c r="O124">
-        <v>0.04010570240548915</v>
+        <v>0.03392825585588018</v>
       </c>
       <c r="P124">
-        <v>0.06206166534313404</v>
+        <v>0.06357354548651362</v>
       </c>
       <c r="Q124">
-        <v>0.05910626485640651</v>
+        <v>0.05958311684294302</v>
       </c>
       <c r="R124">
-        <v>0.05477441361836932</v>
+        <v>0.05373418254873139</v>
       </c>
       <c r="S124">
-        <v>0.04066690872724376</v>
+        <v>0.03468600553865235</v>
       </c>
       <c r="T124">
-        <v>0.07728486379494337</v>
+        <v>0.08412814964986473</v>
       </c>
       <c r="U124">
-        <v>0.05344132017705565</v>
+        <v>0.05193421862618888</v>
       </c>
       <c r="V124">
-        <v>0.05454426406269858</v>
+        <v>0.05342343096586538</v>
       </c>
       <c r="W124">
-        <v>0.06446889645335972</v>
+        <v>0.06682382713770713</v>
       </c>
       <c r="X124">
-        <v>0.05491880925482095</v>
+        <v>0.05392914782883163</v>
       </c>
       <c r="Y124">
-        <v>0.05075407259723578</v>
+        <v>0.04830585429349139</v>
       </c>
       <c r="Z124">
-        <v>0.05562607167309825</v>
+        <v>0.05488410477124583</v>
       </c>
       <c r="AA124">
-        <v>0.0569590647132506</v>
+        <v>0.05668393313054683</v>
       </c>
       <c r="AB124">
-        <v>0.05596563296653032</v>
+        <v>0.0553425858189564</v>
       </c>
       <c r="AC124">
-        <v>0.05535240720476958</v>
+        <v>0.05451459866266579</v>
       </c>
     </row>
     <row r="125" spans="1:29">
@@ -12386,88 +12386,88 @@
         <v>125</v>
       </c>
       <c r="B126">
-        <v>0.07918562854513576</v>
+        <v>0.086130170460229</v>
       </c>
       <c r="C126">
-        <v>0.08227928787583581</v>
+        <v>0.08529659989863644</v>
       </c>
       <c r="D126">
-        <v>0.07821152160082923</v>
+        <v>0.08639263855571677</v>
       </c>
       <c r="E126">
-        <v>0.07799438112203141</v>
+        <v>0.08645114593856264</v>
       </c>
       <c r="F126">
-        <v>0.0803263942592788</v>
+        <v>0.08582279701818664</v>
       </c>
       <c r="G126">
-        <v>0.07786133515879083</v>
+        <v>0.08648699448762411</v>
       </c>
       <c r="H126">
-        <v>0.07461960739546175</v>
+        <v>0.08736046132522737</v>
       </c>
       <c r="I126">
-        <v>0.08024246096054215</v>
+        <v>0.08584541241292966</v>
       </c>
       <c r="J126">
-        <v>0.07774373172540752</v>
+        <v>0.08651868212660806</v>
       </c>
       <c r="K126">
-        <v>0.07691255346997333</v>
+        <v>0.08674263882354954</v>
       </c>
       <c r="L126">
-        <v>0.07877264511340483</v>
+        <v>0.08624144671734632</v>
       </c>
       <c r="M126">
-        <v>0.07647780059319859</v>
+        <v>0.08685978074543178</v>
       </c>
       <c r="N126">
-        <v>0.07649631269210261</v>
+        <v>0.08685479275579551</v>
       </c>
       <c r="O126">
-        <v>0.07319711202452722</v>
+        <v>0.08774374537122619</v>
       </c>
       <c r="P126">
-        <v>0.08080610303762675</v>
+        <v>0.08569354196033323</v>
       </c>
       <c r="Q126">
-        <v>0.08065550627669275</v>
+        <v>0.08573411948137442</v>
       </c>
       <c r="R126">
-        <v>0.07960247285167529</v>
+        <v>0.08601785391029387</v>
       </c>
       <c r="S126">
-        <v>0.07529795242373798</v>
+        <v>0.08717768475362413</v>
       </c>
       <c r="T126">
-        <v>0.08407546772537151</v>
+        <v>0.08481262849588994</v>
       </c>
       <c r="U126">
-        <v>0.07794570500655182</v>
+        <v>0.0864642614669965</v>
       </c>
       <c r="V126">
-        <v>0.07820434660254172</v>
+        <v>0.08639457182202459</v>
       </c>
       <c r="W126">
-        <v>0.08053168418929432</v>
+        <v>0.08576748270463111</v>
       </c>
       <c r="X126">
-        <v>0.07829217787621029</v>
+        <v>0.08637090613802675</v>
       </c>
       <c r="Y126">
-        <v>0.07731554239183276</v>
+        <v>0.08663405553560428</v>
       </c>
       <c r="Z126">
-        <v>0.0784580317179409</v>
+        <v>0.08632621767520161</v>
       </c>
       <c r="AA126">
-        <v>0.07877062010238753</v>
+        <v>0.0862419923461278</v>
       </c>
       <c r="AB126">
-        <v>0.07853765922756575</v>
+        <v>0.08630476245314224</v>
       </c>
       <c r="AC126">
-        <v>0.07839385708877289</v>
+        <v>0.08634350919826775</v>
       </c>
     </row>
     <row r="127" spans="1:29">
@@ -12475,88 +12475,88 @@
         <v>126</v>
       </c>
       <c r="B127">
-        <v>0.02455057240057187</v>
+        <v>0.02159036637442814</v>
       </c>
       <c r="C127">
-        <v>0.05944513742359483</v>
+        <v>0.06153517031188553</v>
       </c>
       <c r="D127">
-        <v>0.04246060940941321</v>
+        <v>0.04209249661616502</v>
       </c>
       <c r="E127">
-        <v>0.03507016773733034</v>
+        <v>0.03363244722429583</v>
       </c>
       <c r="F127">
-        <v>0.04094965301000906</v>
+        <v>0.04036286172624952</v>
       </c>
       <c r="G127">
-        <v>0.01953145187675047</v>
+        <v>0.01584483594210335</v>
       </c>
       <c r="H127">
-        <v>0.01989857429938909</v>
+        <v>0.01626509145134006</v>
       </c>
       <c r="I127">
-        <v>0.05863413739403353</v>
+        <v>0.06060679544454661</v>
       </c>
       <c r="J127">
-        <v>0.03703921434155651</v>
+        <v>0.03588647103853843</v>
       </c>
       <c r="K127">
-        <v>0.02809876330964585</v>
+        <v>0.0256520817189844</v>
       </c>
       <c r="L127">
-        <v>0.027444954217034</v>
+        <v>0.02490364780098955</v>
       </c>
       <c r="M127">
-        <v>0.05603075354285789</v>
+        <v>0.05762662768946665</v>
       </c>
       <c r="N127">
-        <v>-0.0293190507035295</v>
+        <v>-0.0400757278055199</v>
       </c>
       <c r="O127">
-        <v>-0.00201019805202814</v>
+        <v>-0.00881450519960951</v>
       </c>
       <c r="P127">
-        <v>0.04652124282956897</v>
+        <v>0.04674081952040499</v>
       </c>
       <c r="Q127">
-        <v>0.03998862823141162</v>
+        <v>0.03926274924928397</v>
       </c>
       <c r="R127">
-        <v>0.03041350812104648</v>
+        <v>0.02830183613190343</v>
       </c>
       <c r="S127">
-        <v>-0.0007697080993003449</v>
+        <v>-0.007394480966167872</v>
       </c>
       <c r="T127">
-        <v>0.08017058710069085</v>
+        <v>0.08526018374366265</v>
       </c>
       <c r="U127">
-        <v>0.02746683956815729</v>
+        <v>0.02492870058669257</v>
       </c>
       <c r="V127">
-        <v>0.02990478574860116</v>
+        <v>0.02771948712103256</v>
       </c>
       <c r="W127">
-        <v>0.0518421843271497</v>
+        <v>0.05283185303073273</v>
       </c>
       <c r="X127">
-        <v>0.03073268010698557</v>
+        <v>0.02866720140848028</v>
       </c>
       <c r="Y127">
-        <v>0.02152694991610124</v>
+        <v>0.01812913946865127</v>
       </c>
       <c r="Z127">
-        <v>0.03229601232511155</v>
+        <v>0.03045679239208908</v>
       </c>
       <c r="AA127">
-        <v>0.03524245895136339</v>
+        <v>0.03382967389154776</v>
       </c>
       <c r="AB127">
-        <v>0.03304657830505415</v>
+        <v>0.03131598667896875</v>
       </c>
       <c r="AC127">
-        <v>0.03169110462856434</v>
+        <v>0.02976433729706512</v>
       </c>
     </row>
     <row r="128" spans="1:29">
@@ -13009,88 +13009,88 @@
         <v>132</v>
       </c>
       <c r="B133">
-        <v>0.0283794887679109</v>
+        <v>0.02785158198171808</v>
       </c>
       <c r="C133">
-        <v>0.07852328544823782</v>
+        <v>0.07869094985580155</v>
       </c>
       <c r="D133">
-        <v>0.01259060727230401</v>
+        <v>0.01184368453843588</v>
       </c>
       <c r="E133">
-        <v>0.009071070420958959</v>
+        <v>0.008275326325103277</v>
       </c>
       <c r="F133">
-        <v>0.0468696707547337</v>
+        <v>0.04659825108776207</v>
       </c>
       <c r="G133">
-        <v>0.006914585489450996</v>
+        <v>0.006088927647580237</v>
       </c>
       <c r="H133">
-        <v>-0.04562918888293952</v>
+        <v>-0.04718370928178171</v>
       </c>
       <c r="I133">
-        <v>0.04550923192916744</v>
+        <v>0.04521894089383963</v>
       </c>
       <c r="J133">
-        <v>0.005008401898400374</v>
+        <v>0.004156302373136574</v>
       </c>
       <c r="K133">
-        <v>-0.008463809806360707</v>
+        <v>-0.009502789524158834</v>
       </c>
       <c r="L133">
-        <v>0.02168561752373182</v>
+        <v>0.02106485649991816</v>
       </c>
       <c r="M133">
-        <v>-0.01551053264453678</v>
+        <v>-0.01664726119152447</v>
       </c>
       <c r="N133">
-        <v>-0.01521047797647487</v>
+        <v>-0.01634304430605038</v>
       </c>
       <c r="O133">
-        <v>-0.06868580599362394</v>
+        <v>-0.07056015695475697</v>
       </c>
       <c r="P133">
-        <v>0.0546450645120692</v>
+        <v>0.05448150145500279</v>
       </c>
       <c r="Q133">
-        <v>0.05220410623135215</v>
+        <v>0.05200668334759467</v>
       </c>
       <c r="R133">
-        <v>0.03513593927525898</v>
+        <v>0.03470175479683064</v>
       </c>
       <c r="S133">
-        <v>-0.03463418538030869</v>
+        <v>-0.03603618825518998</v>
       </c>
       <c r="T133">
-        <v>0.1076367939340082</v>
+        <v>0.1082083072559449</v>
       </c>
       <c r="U133">
-        <v>0.008282100150840618</v>
+        <v>0.007475411829996885</v>
       </c>
       <c r="V133">
-        <v>0.01247431080367235</v>
+        <v>0.01172577485981872</v>
       </c>
       <c r="W133">
-        <v>0.0501971271456375</v>
+        <v>0.04997186439073116</v>
       </c>
       <c r="X133">
-        <v>0.01389793023238766</v>
+        <v>0.01316914206853958</v>
       </c>
       <c r="Y133">
-        <v>-0.001931935284297279</v>
+        <v>-0.002880307906909849</v>
       </c>
       <c r="Z133">
-        <v>0.01658618398930946</v>
+        <v>0.01589468601883751</v>
       </c>
       <c r="AA133">
-        <v>0.02165279498903344</v>
+        <v>0.02103157866643601</v>
       </c>
       <c r="AB133">
-        <v>0.01787683212666774</v>
+        <v>0.01720323742090758</v>
       </c>
       <c r="AC133">
-        <v>0.01554600496083583</v>
+        <v>0.01484007811547895</v>
       </c>
     </row>
     <row r="134" spans="1:29">
@@ -13276,88 +13276,88 @@
         <v>135</v>
       </c>
       <c r="B136">
-        <v>0.03552320230565176</v>
+        <v>0.0346892055011844</v>
       </c>
       <c r="C136">
-        <v>0.0945774698758643</v>
+        <v>0.09383001636250848</v>
       </c>
       <c r="D136">
-        <v>0.01692866231857976</v>
+        <v>0.01606741544814091</v>
       </c>
       <c r="E136">
-        <v>0.01278370950881181</v>
+        <v>0.01191638826183052</v>
       </c>
       <c r="F136">
-        <v>0.05729905947564056</v>
+        <v>0.05649697491771871</v>
       </c>
       <c r="G136">
-        <v>0.01024402072201585</v>
+        <v>0.009372977592856494</v>
       </c>
       <c r="H136">
-        <v>-0.05163669666198332</v>
+        <v>-0.05259842520913363</v>
       </c>
       <c r="I136">
-        <v>0.0556968728895296</v>
+        <v>0.05489244034718864</v>
       </c>
       <c r="J136">
-        <v>0.007999111415656603</v>
+        <v>0.007124778399963842</v>
       </c>
       <c r="K136">
-        <v>-0.007867090337024945</v>
+        <v>-0.008764675073103268</v>
       </c>
       <c r="L136">
-        <v>0.02763984105850884</v>
+        <v>0.02679429128665368</v>
       </c>
       <c r="M136">
-        <v>-0.01616600433094759</v>
+        <v>-0.01707575102177088</v>
       </c>
       <c r="N136">
-        <v>-0.01581263043773437</v>
+        <v>-0.01672185926353334</v>
       </c>
       <c r="O136">
-        <v>-0.07879043702988203</v>
+        <v>-0.07979195904419595</v>
       </c>
       <c r="P136">
-        <v>0.06645612802265785</v>
+        <v>0.06566746303425398</v>
       </c>
       <c r="Q136">
-        <v>0.06358141543644985</v>
+        <v>0.06278853759267673</v>
       </c>
       <c r="R136">
-        <v>0.04348026304896743</v>
+        <v>0.04265792721757847</v>
       </c>
       <c r="S136">
-        <v>-0.03868789896883761</v>
+        <v>-0.03963065121479224</v>
       </c>
       <c r="T136">
-        <v>0.1288644013379342</v>
+        <v>0.1281671948941456</v>
       </c>
       <c r="U136">
-        <v>0.01185454050843592</v>
+        <v>0.01098585757589658</v>
       </c>
       <c r="V136">
-        <v>0.01679170015714177</v>
+        <v>0.01593025257036698</v>
       </c>
       <c r="W136">
-        <v>0.06121779944041352</v>
+        <v>0.06042145774693679</v>
       </c>
       <c r="X136">
-        <v>0.01846829443653926</v>
+        <v>0.0176093038777282</v>
       </c>
       <c r="Y136">
-        <v>-0.0001745123653149458</v>
+        <v>-0.001060823724511364</v>
       </c>
       <c r="Z136">
-        <v>0.021634246501756</v>
+        <v>0.020779895606131</v>
       </c>
       <c r="AA136">
-        <v>0.02760118601292529</v>
+        <v>0.0267555795925839</v>
       </c>
       <c r="AB136">
-        <v>0.02315424070818703</v>
+        <v>0.02230211734507589</v>
       </c>
       <c r="AC136">
-        <v>0.02040922935636491</v>
+        <v>0.01955308321342261</v>
       </c>
     </row>
     <row r="137" spans="1:29">
@@ -13365,88 +13365,88 @@
         <v>136</v>
       </c>
       <c r="B137">
-        <v>-0.02301240400900549</v>
+        <v>-0.01677180446191738</v>
       </c>
       <c r="C137">
-        <v>-0.1316901447691362</v>
+        <v>-0.1258384078810267</v>
       </c>
       <c r="D137">
-        <v>-0.07879250494354879</v>
+        <v>-0.07275149363059023</v>
       </c>
       <c r="E137">
-        <v>-0.05577526705531136</v>
+        <v>-0.04965189716308016</v>
       </c>
       <c r="F137">
-        <v>-0.07408669107924173</v>
+        <v>-0.06802884177094821</v>
       </c>
       <c r="G137">
-        <v>-0.007380551920526317</v>
+        <v>-0.001084019635737073</v>
       </c>
       <c r="H137">
-        <v>-0.008523940165899972</v>
+        <v>-0.002231499068415799</v>
       </c>
       <c r="I137">
-        <v>-0.1291643172968358</v>
+        <v>-0.1233035426795637</v>
       </c>
       <c r="J137">
-        <v>-0.06190778471981064</v>
+        <v>-0.0558063577489962</v>
       </c>
       <c r="K137">
-        <v>-0.03406310406872463</v>
+        <v>-0.02786204531976815</v>
       </c>
       <c r="L137">
-        <v>-0.03202684154398461</v>
+        <v>-0.0258184967909742</v>
       </c>
       <c r="M137">
-        <v>-0.1210561813997268</v>
+        <v>-0.1151663948499075</v>
       </c>
       <c r="N137">
-        <v>0.1447624036348439</v>
+        <v>0.1516033225974232</v>
       </c>
       <c r="O137">
-        <v>0.05971006362262958</v>
+        <v>0.06624665458889445</v>
       </c>
       <c r="P137">
-        <v>-0.09143918690867563</v>
+        <v>-0.08544342701833424</v>
       </c>
       <c r="Q137">
-        <v>-0.07109361746781931</v>
+        <v>-0.06502505856476502</v>
       </c>
       <c r="R137">
-        <v>-0.04127228510804348</v>
+        <v>-0.03509702171780904</v>
       </c>
       <c r="S137">
-        <v>0.05584660679463503</v>
+        <v>0.06236937382524872</v>
       </c>
       <c r="T137">
-        <v>-0.1962387369541505</v>
+        <v>-0.1906179630674324</v>
       </c>
       <c r="U137">
-        <v>-0.03209500260328571</v>
+        <v>-0.02588690173913952</v>
       </c>
       <c r="V137">
-        <v>-0.03968788942708247</v>
+        <v>-0.03350695686933437</v>
       </c>
       <c r="W137">
-        <v>-0.1080110484662668</v>
+        <v>-0.1020745847860273</v>
       </c>
       <c r="X137">
-        <v>-0.04226633361740013</v>
+        <v>-0.03609462705806592</v>
       </c>
       <c r="Y137">
-        <v>-0.01359545153210842</v>
+        <v>-0.007321156941729669</v>
       </c>
       <c r="Z137">
-        <v>-0.04713526989476476</v>
+        <v>-0.04098098500332656</v>
       </c>
       <c r="AA137">
-        <v>-0.05631186121779991</v>
+        <v>-0.05019041132713811</v>
       </c>
       <c r="AB137">
-        <v>-0.04947287791302651</v>
+        <v>-0.04332695727781295</v>
       </c>
       <c r="AC137">
-        <v>-0.04525130883132149</v>
+        <v>-0.03909028288966068</v>
       </c>
     </row>
     <row r="138" spans="1:29">
@@ -13899,88 +13899,88 @@
         <v>142</v>
       </c>
       <c r="B143">
-        <v>0.04135723306207706</v>
+        <v>0.04062346122614617</v>
       </c>
       <c r="C143">
-        <v>0.08070757859328243</v>
+        <v>0.07225710627531953</v>
       </c>
       <c r="D143">
-        <v>0.06155425068672971</v>
+        <v>0.05685979353696412</v>
       </c>
       <c r="E143">
-        <v>0.0532201037147642</v>
+        <v>0.05015999348337297</v>
       </c>
       <c r="F143">
-        <v>0.0598503562160604</v>
+        <v>0.05549003700347552</v>
       </c>
       <c r="G143">
-        <v>0.03569720758977711</v>
+        <v>0.03607338080517428</v>
       </c>
       <c r="H143">
-        <v>0.03611120885827126</v>
+        <v>0.03640619539677846</v>
       </c>
       <c r="I143">
-        <v>0.07979301979686243</v>
+        <v>0.07152189473010942</v>
       </c>
       <c r="J143">
-        <v>0.05544058315596728</v>
+        <v>0.05194503139177716</v>
       </c>
       <c r="K143">
-        <v>0.04535850197574948</v>
+        <v>0.04384007136902355</v>
       </c>
       <c r="L143">
-        <v>0.04462120624821296</v>
+        <v>0.04324736116467055</v>
       </c>
       <c r="M143">
-        <v>0.07685720288593288</v>
+        <v>0.06916179880627418</v>
       </c>
       <c r="N143">
-        <v>-0.01939114656046831</v>
+        <v>-0.008212010288788991</v>
       </c>
       <c r="O143">
-        <v>0.01140484666049138</v>
+        <v>0.01654481218221173</v>
       </c>
       <c r="P143">
-        <v>0.0661333972688196</v>
+        <v>0.06054095810237041</v>
       </c>
       <c r="Q143">
-        <v>0.05876661560840679</v>
+        <v>0.0546188206203639</v>
       </c>
       <c r="R143">
-        <v>0.04796882275450348</v>
+        <v>0.04593850176054588</v>
       </c>
       <c r="S143">
-        <v>0.01280373809919023</v>
+        <v>0.01766937753574933</v>
       </c>
       <c r="T143">
-        <v>0.1040795164737301</v>
+        <v>0.09104574909511651</v>
       </c>
       <c r="U143">
-        <v>0.04464588619846323</v>
+        <v>0.0432672013153861</v>
       </c>
       <c r="V143">
-        <v>0.04739514025919311</v>
+        <v>0.0454773198272594</v>
       </c>
       <c r="W143">
-        <v>0.072133784043751</v>
+        <v>0.06536465412926828</v>
       </c>
       <c r="X143">
-        <v>0.04832875066655219</v>
+        <v>0.04622784691519032</v>
       </c>
       <c r="Y143">
-        <v>0.03794751612073278</v>
+        <v>0.03788239824475247</v>
       </c>
       <c r="Z143">
-        <v>0.05009170896457753</v>
+        <v>0.04764508471281023</v>
       </c>
       <c r="AA143">
-        <v>0.05341439525557344</v>
+        <v>0.05031618397052238</v>
       </c>
       <c r="AB143">
-        <v>0.05093811672564925</v>
+        <v>0.0483255098099514</v>
       </c>
       <c r="AC143">
-        <v>0.04940955898340101</v>
+        <v>0.04709670603700608</v>
       </c>
     </row>
     <row r="144" spans="1:29">
@@ -14344,88 +14344,88 @@
         <v>147</v>
       </c>
       <c r="B148">
-        <v>0.03763029488417722</v>
+        <v>0.03736133701353365</v>
       </c>
       <c r="C148">
-        <v>0.05071750637553178</v>
+        <v>0.04801043536130332</v>
       </c>
       <c r="D148">
-        <v>0.04434745676878718</v>
+        <v>0.04282710927329696</v>
       </c>
       <c r="E148">
-        <v>0.04157567058623257</v>
+        <v>0.04057169957990948</v>
       </c>
       <c r="F148">
-        <v>0.04378077235990657</v>
+        <v>0.0423659966821003</v>
       </c>
       <c r="G148">
-        <v>0.03574787302987097</v>
+        <v>0.03582960540884914</v>
       </c>
       <c r="H148">
-        <v>0.03588556234581802</v>
+        <v>0.03594164356670468</v>
       </c>
       <c r="I148">
-        <v>0.05041334070103889</v>
+        <v>0.04776293495345631</v>
       </c>
       <c r="J148">
-        <v>0.04231416179048857</v>
+        <v>0.04117261181153958</v>
       </c>
       <c r="K148">
-        <v>0.03896104438078549</v>
+        <v>0.03844417137247927</v>
       </c>
       <c r="L148">
-        <v>0.03871583318917625</v>
+        <v>0.03824464238212516</v>
       </c>
       <c r="M148">
-        <v>0.04943694122361216</v>
+        <v>0.04696843613537753</v>
       </c>
       <c r="N148">
-        <v>0.01742648520614331</v>
+        <v>0.02092144403838507</v>
       </c>
       <c r="O148">
-        <v>0.02766867421181315</v>
+        <v>0.02925554012064639</v>
       </c>
       <c r="P148">
-        <v>0.04587039790083391</v>
+        <v>0.0440663304705507</v>
       </c>
       <c r="Q148">
-        <v>0.04342033988230903</v>
+        <v>0.04207271182885236</v>
       </c>
       <c r="R148">
-        <v>0.03982918974598287</v>
+        <v>0.03915058353524247</v>
       </c>
       <c r="S148">
-        <v>0.02813392014204721</v>
+        <v>0.02963411195546659</v>
       </c>
       <c r="T148">
-        <v>0.05849058917506295</v>
+        <v>0.05433541324159863</v>
       </c>
       <c r="U148">
-        <v>0.03872404129317537</v>
+        <v>0.0382513213378976</v>
       </c>
       <c r="V148">
-        <v>0.03963839334906023</v>
+        <v>0.03899533200617751</v>
       </c>
       <c r="W148">
-        <v>0.04786601775355363</v>
+        <v>0.04569017158371776</v>
       </c>
       <c r="X148">
-        <v>0.03994889524394063</v>
+        <v>0.03924798821318804</v>
       </c>
       <c r="Y148">
-        <v>0.03649628484856927</v>
+        <v>0.03643859007049507</v>
       </c>
       <c r="Z148">
-        <v>0.04053522321095682</v>
+        <v>0.03972508481920896</v>
       </c>
       <c r="AA148">
-        <v>0.04164028843014794</v>
+        <v>0.04062427928914168</v>
       </c>
       <c r="AB148">
-        <v>0.04081672308668943</v>
+        <v>0.03995414200710126</v>
       </c>
       <c r="AC148">
-        <v>0.04030835249477972</v>
+        <v>0.0395404795218624</v>
       </c>
     </row>
     <row r="149" spans="1:29">
@@ -14433,88 +14433,88 @@
         <v>148</v>
       </c>
       <c r="B149">
-        <v>0.0310358678830877</v>
+        <v>0.02659552083009516</v>
       </c>
       <c r="C149">
-        <v>0.06159227511543326</v>
+        <v>0.07109162246298489</v>
       </c>
       <c r="D149">
-        <v>0.04671929548929105</v>
+        <v>0.04943365698305821</v>
       </c>
       <c r="E149">
-        <v>0.04024764739136908</v>
+        <v>0.04000967237296277</v>
       </c>
       <c r="F149">
-        <v>0.04539618402422335</v>
+        <v>0.04750694806817722</v>
       </c>
       <c r="G149">
-        <v>0.0266407338393499</v>
+        <v>0.02019534656833465</v>
       </c>
       <c r="H149">
-        <v>0.02696221491363381</v>
+        <v>0.02066348585073186</v>
       </c>
       <c r="I149">
-        <v>0.06088210013109489</v>
+        <v>0.07005746887156379</v>
       </c>
       <c r="J149">
-        <v>0.04197189842755493</v>
+        <v>0.04252051891206525</v>
       </c>
       <c r="K149">
-        <v>0.03414294104145023</v>
+        <v>0.03112002667216206</v>
       </c>
       <c r="L149">
-        <v>0.03357041472186789</v>
+        <v>0.03028631644209702</v>
       </c>
       <c r="M149">
-        <v>0.05860237384460447</v>
+        <v>0.06673774179214884</v>
       </c>
       <c r="N149">
-        <v>-0.01613658260987141</v>
+        <v>-0.04209678764212851</v>
       </c>
       <c r="O149">
-        <v>0.007777182244822434</v>
+        <v>-0.007273671713986588</v>
       </c>
       <c r="P149">
-        <v>0.05027510334434487</v>
+        <v>0.05461160825535369</v>
       </c>
       <c r="Q149">
-        <v>0.04455463564911614</v>
+        <v>0.0462814891409207</v>
       </c>
       <c r="R149">
-        <v>0.03616991243511712</v>
+        <v>0.03407169322293668</v>
       </c>
       <c r="S149">
-        <v>0.008863452159296922</v>
+        <v>-0.005691850390960027</v>
       </c>
       <c r="T149">
-        <v>0.07974109800487152</v>
+        <v>0.0975198560463796</v>
       </c>
       <c r="U149">
-        <v>0.0335895792450796</v>
+        <v>0.03031422373388331</v>
       </c>
       <c r="V149">
-        <v>0.03572443538244752</v>
+        <v>0.03342299155915848</v>
       </c>
       <c r="W149">
-        <v>0.05493453541212646</v>
+        <v>0.06139665210108727</v>
       </c>
       <c r="X149">
-        <v>0.03644940436095361</v>
+        <v>0.03447868809779318</v>
       </c>
       <c r="Y149">
-        <v>0.02838814781861913</v>
+        <v>0.022739922880107</v>
       </c>
       <c r="Z149">
-        <v>0.03781838018469538</v>
+        <v>0.03647218448377215</v>
       </c>
       <c r="AA149">
-        <v>0.04039851903843146</v>
+        <v>0.04022937098118472</v>
       </c>
       <c r="AB149">
-        <v>0.03847563439384624</v>
+        <v>0.03742927508237053</v>
       </c>
       <c r="AC149">
-        <v>0.03728867574787316</v>
+        <v>0.03570083128517738</v>
       </c>
     </row>
     <row r="150" spans="1:29">
@@ -14700,88 +14700,88 @@
         <v>151</v>
       </c>
       <c r="B152">
-        <v>0.01933653408070938</v>
+        <v>0.01894034906668946</v>
       </c>
       <c r="C152">
-        <v>0.04304186090426581</v>
+        <v>0.04246849277316302</v>
       </c>
       <c r="D152">
-        <v>0.01187238854705842</v>
+        <v>0.01153199354942834</v>
       </c>
       <c r="E152">
-        <v>0.010208538243489</v>
+        <v>0.009880579530131224</v>
       </c>
       <c r="F152">
-        <v>0.02807771117623306</v>
+        <v>0.0276161910999174</v>
       </c>
       <c r="G152">
-        <v>0.00918906657449336</v>
+        <v>0.008868727801136192</v>
       </c>
       <c r="H152">
-        <v>-0.01565084237738311</v>
+        <v>-0.01578551771193146</v>
       </c>
       <c r="I152">
-        <v>0.02743456787399971</v>
+        <v>0.02697785490858653</v>
       </c>
       <c r="J152">
-        <v>0.008287924100188384</v>
+        <v>0.007974320826987851</v>
       </c>
       <c r="K152">
-        <v>0.001918977138842703</v>
+        <v>0.001652977928794144</v>
       </c>
       <c r="L152">
-        <v>0.01617202688214842</v>
+        <v>0.01579949466370672</v>
       </c>
       <c r="M152">
-        <v>-0.001412339573749188</v>
+        <v>-0.001653439187031136</v>
       </c>
       <c r="N152">
-        <v>-0.00127048964529868</v>
+        <v>-0.001512649501819116</v>
       </c>
       <c r="O152">
-        <v>-0.0265507877392949</v>
+        <v>-0.02660399251198889</v>
       </c>
       <c r="P152">
-        <v>0.03175350484168945</v>
+        <v>0.03126451040974702</v>
       </c>
       <c r="Q152">
-        <v>0.03059954926517113</v>
+        <v>0.03011917995987405</v>
       </c>
       <c r="R152">
-        <v>0.02253062543491885</v>
+        <v>0.02211056650147995</v>
       </c>
       <c r="S152">
-        <v>-0.01045298803225592</v>
+        <v>-0.01062651421420525</v>
       </c>
       <c r="T152">
-        <v>0.05680518317591855</v>
+        <v>0.05612894245589688</v>
       </c>
       <c r="U152">
-        <v>0.009835554956514191</v>
+        <v>0.009510384069787025</v>
       </c>
       <c r="V152">
-        <v>0.01181740974649184</v>
+        <v>0.01147742568246037</v>
       </c>
       <c r="W152">
-        <v>0.02965075602842817</v>
+        <v>0.02917747838419125</v>
       </c>
       <c r="X152">
-        <v>0.01249042148601377</v>
+        <v>0.01214540706240407</v>
       </c>
       <c r="Y152">
-        <v>0.005006900881496279</v>
+        <v>0.004717821291324299</v>
       </c>
       <c r="Z152">
-        <v>0.01376128524407234</v>
+        <v>0.01340677187519533</v>
       </c>
       <c r="AA152">
-        <v>0.01615651012905606</v>
+        <v>0.01578409388904824</v>
       </c>
       <c r="AB152">
-        <v>0.01437143521148188</v>
+        <v>0.0140123613371152</v>
       </c>
       <c r="AC152">
-        <v>0.01326954378336538</v>
+        <v>0.01291870588732431</v>
       </c>
     </row>
     <row r="153" spans="1:29">
@@ -14878,88 +14878,88 @@
         <v>153</v>
       </c>
       <c r="B154">
-        <v>0.004254614694380141</v>
+        <v>0.005316052300801663</v>
       </c>
       <c r="C154">
-        <v>-0.05541360384309654</v>
+        <v>-0.05368458662807449</v>
       </c>
       <c r="D154">
-        <v>0.02304247069874626</v>
+        <v>0.02389370612609719</v>
       </c>
       <c r="E154">
-        <v>0.02723051603834358</v>
+        <v>0.02803489480167573</v>
       </c>
       <c r="F154">
-        <v>-0.01774763269468342</v>
+        <v>-0.01644002967457359</v>
       </c>
       <c r="G154">
-        <v>0.02979660841037323</v>
+        <v>0.03057227723425451</v>
       </c>
       <c r="H154">
-        <v>0.09232066162522892</v>
+        <v>0.09239679920791727</v>
       </c>
       <c r="I154">
-        <v>-0.01612878915819863</v>
+        <v>-0.01483929807373829</v>
       </c>
       <c r="J154">
-        <v>0.03206485666066945</v>
+        <v>0.03281514788293537</v>
       </c>
       <c r="K154">
-        <v>0.04809600957291427</v>
+        <v>0.04866694114528802</v>
       </c>
       <c r="L154">
-        <v>0.01221993440891446</v>
+        <v>0.01319225447256793</v>
       </c>
       <c r="M154">
-        <v>0.05648120228103404</v>
+        <v>0.05695831869010422</v>
       </c>
       <c r="N154">
-        <v>0.05612415457638482</v>
+        <v>0.05660526570446562</v>
       </c>
       <c r="O154">
-        <v>0.119756702762397</v>
+        <v>0.1195258805924258</v>
       </c>
       <c r="P154">
-        <v>-0.02699990166197619</v>
+        <v>-0.02558878246110469</v>
       </c>
       <c r="Q154">
-        <v>-0.02409530245375886</v>
+        <v>-0.02271668047251434</v>
       </c>
       <c r="R154">
-        <v>-0.003785170724745442</v>
+        <v>-0.002633782438801607</v>
       </c>
       <c r="S154">
-        <v>0.07923724323156969</v>
+        <v>0.07945976063829971</v>
       </c>
       <c r="T154">
-        <v>-0.09005699548326668</v>
+        <v>-0.08794038127945211</v>
       </c>
       <c r="U154">
-        <v>0.02816934503841136</v>
+        <v>0.02896322000069548</v>
       </c>
       <c r="V154">
-        <v>0.02318085677169739</v>
+        <v>0.02403054390880803</v>
       </c>
       <c r="W154">
-        <v>-0.02170711339320552</v>
+        <v>-0.020355210934638</v>
       </c>
       <c r="X154">
-        <v>0.0214868319708169</v>
+        <v>0.02235547218615329</v>
       </c>
       <c r="Y154">
-        <v>0.04032345659040813</v>
+        <v>0.04098134899394243</v>
       </c>
       <c r="Z154">
-        <v>0.01828796544551578</v>
+        <v>0.01919239520033012</v>
       </c>
       <c r="AA154">
-        <v>0.01225899132727711</v>
+        <v>0.01323087441454829</v>
       </c>
       <c r="AB154">
-        <v>0.01675216879242559</v>
+        <v>0.01767378133824141</v>
       </c>
       <c r="AC154">
-        <v>0.01952571834214507</v>
+        <v>0.02041629987734553</v>
       </c>
     </row>
     <row r="155" spans="1:29">
@@ -15234,88 +15234,88 @@
         <v>157</v>
       </c>
       <c r="B158">
-        <v>0.0254319061043813</v>
+        <v>0.02584891080289244</v>
       </c>
       <c r="C158">
-        <v>0.02716325391128518</v>
+        <v>0.02910635349532411</v>
       </c>
       <c r="D158">
-        <v>0.02488675302143556</v>
+        <v>0.02482323305101785</v>
       </c>
       <c r="E158">
-        <v>0.02476523166062316</v>
+        <v>0.02459459680174764</v>
       </c>
       <c r="F158">
-        <v>0.02607032876384256</v>
+        <v>0.02705007051121461</v>
       </c>
       <c r="G158">
-        <v>0.02469077328882116</v>
+        <v>0.02445450716860194</v>
       </c>
       <c r="H158">
-        <v>0.0228765598756238</v>
+        <v>0.02104115705964873</v>
       </c>
       <c r="I158">
-        <v>0.02602335599885456</v>
+        <v>0.02696169364699165</v>
       </c>
       <c r="J158">
-        <v>0.0246249572358214</v>
+        <v>0.02433067761798602</v>
       </c>
       <c r="K158">
-        <v>0.02415979333253974</v>
+        <v>0.02345549543247385</v>
       </c>
       <c r="L158">
-        <v>0.0252007824148013</v>
+        <v>0.02541406335591034</v>
       </c>
       <c r="M158">
-        <v>0.02391648650418938</v>
+        <v>0.02299772603058463</v>
       </c>
       <c r="N158">
-        <v>0.02392684668881625</v>
+        <v>0.02301721819014406</v>
       </c>
       <c r="O158">
-        <v>0.02208046891099871</v>
+        <v>0.01954335246782251</v>
       </c>
       <c r="P158">
-        <v>0.02633879489167485</v>
+        <v>0.02755517585329869</v>
       </c>
       <c r="Q158">
-        <v>0.02625451432167722</v>
+        <v>0.02739660625465536</v>
       </c>
       <c r="R158">
-        <v>0.02566519050928838</v>
+        <v>0.02628782352568138</v>
       </c>
       <c r="S158">
-        <v>0.02325619158405901</v>
+        <v>0.02175541477813053</v>
       </c>
       <c r="T158">
-        <v>0.02816847514312485</v>
+        <v>0.03099762603044164</v>
       </c>
       <c r="U158">
-        <v>0.02473799036584068</v>
+        <v>0.02454334369346534</v>
       </c>
       <c r="V158">
-        <v>0.02488273757686921</v>
+        <v>0.02481567819663946</v>
       </c>
       <c r="W158">
-        <v>0.02618521803642171</v>
+        <v>0.0272662288243562</v>
       </c>
       <c r="X158">
-        <v>0.0249318918200448</v>
+        <v>0.0249081594009335</v>
       </c>
       <c r="Y158">
-        <v>0.02438532365488134</v>
+        <v>0.02387981924395987</v>
       </c>
       <c r="Z158">
-        <v>0.0250247109233951</v>
+        <v>0.02508279381507076</v>
       </c>
       <c r="AA158">
-        <v>0.025199649129585</v>
+        <v>0.02541193113751288</v>
       </c>
       <c r="AB158">
-        <v>0.02506927397944659</v>
+        <v>0.02516663693469612</v>
       </c>
       <c r="AC158">
-        <v>0.02498879597879654</v>
+        <v>0.02501522167655235</v>
       </c>
     </row>
     <row r="159" spans="1:29">
@@ -15501,88 +15501,88 @@
         <v>160</v>
       </c>
       <c r="B161">
-        <v>0.0158606172992376</v>
+        <v>0.01763816483110202</v>
       </c>
       <c r="C161">
-        <v>-0.00333405042393408</v>
+        <v>-0.005102886917179784</v>
       </c>
       <c r="D161">
-        <v>0.006008733228821547</v>
+        <v>0.005966058353689945</v>
       </c>
       <c r="E161">
-        <v>0.01007403887540338</v>
+        <v>0.01078246504615357</v>
       </c>
       <c r="F161">
-        <v>0.006839874296538748</v>
+        <v>0.006950760058542168</v>
       </c>
       <c r="G161">
-        <v>0.0186215157558809</v>
+        <v>0.0209091636095014</v>
       </c>
       <c r="H161">
-        <v>0.0184195704697991</v>
+        <v>0.02066990715206538</v>
       </c>
       <c r="I161">
-        <v>-0.002887938656080235</v>
+        <v>-0.004574352068616887</v>
       </c>
       <c r="J161">
-        <v>0.008990913314886315</v>
+        <v>0.009499222492708879</v>
       </c>
       <c r="K161">
-        <v>0.01390884213100961</v>
+        <v>0.0153257819994835</v>
       </c>
       <c r="L161">
-        <v>0.01426848691462541</v>
+        <v>0.01575187432643394</v>
       </c>
       <c r="M161">
-        <v>-0.001455879309697289</v>
+        <v>-0.002877707137202357</v>
       </c>
       <c r="N161">
-        <v>0.04549301177595604</v>
+        <v>0.05274540533868633</v>
       </c>
       <c r="O161">
-        <v>0.03047106345246283</v>
+        <v>0.03494801967349043</v>
       </c>
       <c r="P161">
-        <v>0.003775075660828638</v>
+        <v>0.003319712864710847</v>
       </c>
       <c r="Q161">
-        <v>0.00736851109962661</v>
+        <v>0.007577067169894491</v>
       </c>
       <c r="R161">
-        <v>0.01263555623421003</v>
+        <v>0.01381724531173865</v>
       </c>
       <c r="S161">
-        <v>0.0297886995244175</v>
+        <v>0.03413958299604242</v>
       </c>
       <c r="T161">
-        <v>-0.01473462583453738</v>
+        <v>-0.01860981910854773</v>
       </c>
       <c r="U161">
-        <v>0.01425644830510157</v>
+        <v>0.0157376114777039</v>
       </c>
       <c r="V161">
-        <v>0.01291539227446412</v>
+        <v>0.01414878352663414</v>
       </c>
       <c r="W161">
-        <v>0.000848152687204777</v>
+        <v>-0.0001479849233609193</v>
       </c>
       <c r="X161">
-        <v>0.0124599873393806</v>
+        <v>0.01360923851629489</v>
       </c>
       <c r="Y161">
-        <v>0.01752383989196608</v>
+        <v>0.0196086824558739</v>
       </c>
       <c r="Z161">
-        <v>0.01160003558333898</v>
+        <v>0.01259040309454075</v>
       </c>
       <c r="AA161">
-        <v>0.009979265588996046</v>
+        <v>0.01067018155984232</v>
       </c>
       <c r="AB161">
-        <v>0.01118716714437694</v>
+        <v>0.01210125357285699</v>
       </c>
       <c r="AC161">
-        <v>0.01193278087564316</v>
+        <v>0.0129846260120936</v>
       </c>
     </row>
     <row r="162" spans="1:29">
@@ -15857,88 +15857,88 @@
         <v>164</v>
       </c>
       <c r="B165">
-        <v>0.03868327697224437</v>
+        <v>0.03775371108573182</v>
       </c>
       <c r="C165">
-        <v>0.1016809231898269</v>
+        <v>0.1007060503070108</v>
       </c>
       <c r="D165">
-        <v>0.01884707715329813</v>
+        <v>0.0179317771748922</v>
       </c>
       <c r="E165">
-        <v>0.01442534301887889</v>
+        <v>0.01351322308773046</v>
       </c>
       <c r="F165">
-        <v>0.061913228041378</v>
+        <v>0.06096695550992851</v>
       </c>
       <c r="G165">
-        <v>0.01171606522615869</v>
+        <v>0.0108058937684265</v>
       </c>
       <c r="H165">
-        <v>-0.05429676842405056</v>
+        <v>-0.05515946440627299</v>
       </c>
       <c r="I165">
-        <v>0.0602040546339461</v>
+        <v>0.05925901131529902</v>
       </c>
       <c r="J165">
-        <v>0.009321250963083928</v>
+        <v>0.008412801821144133</v>
       </c>
       <c r="K165">
-        <v>-0.007604424453071641</v>
+        <v>-0.008500700893973276</v>
       </c>
       <c r="L165">
-        <v>0.03027350028231357</v>
+        <v>0.02934998258560304</v>
       </c>
       <c r="M165">
-        <v>-0.01645750263506224</v>
+        <v>-0.01734741207013828</v>
       </c>
       <c r="N165">
-        <v>-0.01608053202102985</v>
+        <v>-0.01697071256792104</v>
       </c>
       <c r="O165">
-        <v>-0.08326371356729746</v>
+        <v>-0.0841055769413936</v>
       </c>
       <c r="P165">
-        <v>0.07168176448168305</v>
+        <v>0.0707284665600648</v>
       </c>
       <c r="Q165">
-        <v>0.06861509150554557</v>
+        <v>0.06766399909079204</v>
       </c>
       <c r="R165">
-        <v>0.04717167447955783</v>
+        <v>0.04623600386028814</v>
       </c>
       <c r="S165">
-        <v>-0.04048330820212901</v>
+        <v>-0.04135593862522012</v>
       </c>
       <c r="T165">
-        <v>0.1382573818778608</v>
+        <v>0.1372562037347997</v>
       </c>
       <c r="U165">
-        <v>0.01343412828757383</v>
+        <v>0.0125227212237286</v>
       </c>
       <c r="V165">
-        <v>0.01870096927411383</v>
+        <v>0.0177857743743821</v>
       </c>
       <c r="W165">
-        <v>0.06609364385342664</v>
+        <v>0.06514436482736798</v>
       </c>
       <c r="X165">
-        <v>0.02048951898626336</v>
+        <v>0.01957303778743853</v>
       </c>
       <c r="Y165">
-        <v>0.0006018293115148537</v>
+        <v>-0.0003003489484435405</v>
       </c>
       <c r="Z165">
-        <v>0.02386687910522879</v>
+        <v>0.02294796895783821</v>
       </c>
       <c r="AA165">
-        <v>0.03023226402646971</v>
+        <v>0.02930877598627816</v>
       </c>
       <c r="AB165">
-        <v>0.02548837169517021</v>
+        <v>0.02456829539375341</v>
       </c>
       <c r="AC165">
-        <v>0.02256006081908096</v>
+        <v>0.02164209051650704</v>
       </c>
     </row>
     <row r="166" spans="1:29">
@@ -16124,88 +16124,88 @@
         <v>167</v>
       </c>
       <c r="B168">
-        <v>0.06715490620607822</v>
+        <v>0.06255167292926853</v>
       </c>
       <c r="C168">
-        <v>0.1352497430996673</v>
+        <v>0.1344589738429911</v>
       </c>
       <c r="D168">
-        <v>0.10210536476805</v>
+        <v>0.09945892251730459</v>
       </c>
       <c r="E168">
-        <v>0.08768332168196974</v>
+        <v>0.08422942437485319</v>
       </c>
       <c r="F168">
-        <v>0.09915681591802519</v>
+        <v>0.09634529160063363</v>
       </c>
       <c r="G168">
-        <v>0.0573603667643805</v>
+        <v>0.0522087610863915</v>
       </c>
       <c r="H168">
-        <v>0.05807678611143532</v>
+        <v>0.05296529100729559</v>
       </c>
       <c r="I168">
-        <v>0.1336671208575721</v>
+        <v>0.1327877444372591</v>
       </c>
       <c r="J168">
-        <v>0.09152580853521439</v>
+        <v>0.0882870427056682</v>
       </c>
       <c r="K168">
-        <v>0.07407900688081923</v>
+        <v>0.0698634371317963</v>
       </c>
       <c r="L168">
-        <v>0.07280313416277348</v>
+        <v>0.06851613140864002</v>
       </c>
       <c r="M168">
-        <v>0.1285867595290889</v>
+        <v>0.1274229460551357</v>
       </c>
       <c r="N168">
-        <v>-0.03796871967585045</v>
+        <v>-0.0484575686560522</v>
       </c>
       <c r="O168">
-        <v>0.01532301403190916</v>
+        <v>0.007817839388850837</v>
       </c>
       <c r="P168">
-        <v>0.1100294690016957</v>
+        <v>0.1078266780417196</v>
       </c>
       <c r="Q168">
-        <v>0.09728142857601038</v>
+        <v>0.09436490589029292</v>
       </c>
       <c r="R168">
-        <v>0.07859610489532695</v>
+        <v>0.0746334364592573</v>
       </c>
       <c r="S168">
-        <v>0.01774376239038282</v>
+        <v>0.01037411955031421</v>
       </c>
       <c r="T168">
-        <v>0.1756943256407302</v>
+        <v>0.1771679500265277</v>
       </c>
       <c r="U168">
-        <v>0.07284584222960611</v>
+        <v>0.06856123059608615</v>
       </c>
       <c r="V168">
-        <v>0.07760336098369122</v>
+        <v>0.07358511123460318</v>
       </c>
       <c r="W168">
-        <v>0.120412995581237</v>
+        <v>0.1187915529773552</v>
       </c>
       <c r="X168">
-        <v>0.07921895158532541</v>
+        <v>0.07529115481800486</v>
       </c>
       <c r="Y168">
-        <v>0.06125447214788116</v>
+        <v>0.05632088794321479</v>
       </c>
       <c r="Z168">
-        <v>0.0822697089836063</v>
+        <v>0.07851271669054094</v>
       </c>
       <c r="AA168">
-        <v>0.08801953857162112</v>
+        <v>0.08458446522904037</v>
       </c>
       <c r="AB168">
-        <v>0.08373439748017723</v>
+        <v>0.08005940952765543</v>
       </c>
       <c r="AC168">
-        <v>0.08108926466785452</v>
+        <v>0.07726618217343353</v>
       </c>
     </row>
     <row r="169" spans="1:29">
@@ -17548,88 +17548,88 @@
         <v>183</v>
       </c>
       <c r="B184">
-        <v>0.03466354423557447</v>
+        <v>0.03412986010581618</v>
       </c>
       <c r="C184">
-        <v>0.08291939690018788</v>
+        <v>0.08296656012501127</v>
       </c>
       <c r="D184">
-        <v>0.01946912359670075</v>
+        <v>0.01875254685298678</v>
       </c>
       <c r="E184">
-        <v>0.0160820994184375</v>
+        <v>0.01532475365034172</v>
       </c>
       <c r="F184">
-        <v>0.05245755978222877</v>
+        <v>0.05213805914083393</v>
       </c>
       <c r="G184">
-        <v>0.01400680743782179</v>
+        <v>0.01322448173899505</v>
       </c>
       <c r="H184">
-        <v>-0.03655866231950802</v>
+        <v>-0.0379496358345045</v>
       </c>
       <c r="I184">
-        <v>0.05114834229428571</v>
+        <v>0.05081308282836592</v>
       </c>
       <c r="J184">
-        <v>0.01217239280209216</v>
+        <v>0.01136798657148465</v>
       </c>
       <c r="K184">
-        <v>-0.0007925820528432198</v>
+        <v>-0.001753045443999672</v>
       </c>
       <c r="L184">
-        <v>0.02822170125798181</v>
+        <v>0.02761047777816435</v>
       </c>
       <c r="M184">
-        <v>-0.007573991550317548</v>
+        <v>-0.008616081595018383</v>
       </c>
       <c r="N184">
-        <v>-0.007285234120447751</v>
+        <v>-0.008323848441894427</v>
       </c>
       <c r="O184">
-        <v>-0.05874718396916818</v>
+        <v>-0.06040523688263388</v>
       </c>
       <c r="P184">
-        <v>0.05994020530178001</v>
+        <v>0.05971077197067624</v>
       </c>
       <c r="Q184">
-        <v>0.05759115056414856</v>
+        <v>0.05733344206734409</v>
       </c>
       <c r="R184">
-        <v>0.0411656103295497</v>
+        <v>0.04071019044508927</v>
       </c>
       <c r="S184">
-        <v>-0.02597762729233739</v>
+        <v>-0.02724123871828358</v>
       </c>
       <c r="T184">
-        <v>0.1109367643324089</v>
+        <v>0.1113211677645178</v>
       </c>
       <c r="U184">
-        <v>0.01532283435212616</v>
+        <v>0.01455634944171207</v>
       </c>
       <c r="V184">
-        <v>0.01935720575985483</v>
+        <v>0.01863928188049051</v>
       </c>
       <c r="W184">
-        <v>0.05565973544457498</v>
+        <v>0.0553787788379381</v>
       </c>
       <c r="X184">
-        <v>0.02072722506334964</v>
+        <v>0.0200257918694508</v>
       </c>
       <c r="Y184">
-        <v>0.005493363476369143</v>
+        <v>0.004608562924642013</v>
       </c>
       <c r="Z184">
-        <v>0.02331426445420627</v>
+        <v>0.02264397100612898</v>
       </c>
       <c r="AA184">
-        <v>0.02819011451139816</v>
+        <v>0.02757851082737374</v>
       </c>
       <c r="AB184">
-        <v>0.02455631891520512</v>
+        <v>0.02390097586191064</v>
       </c>
       <c r="AC184">
-        <v>0.02231324878993893</v>
+        <v>0.02163090628939694</v>
       </c>
     </row>
     <row r="185" spans="1:29">
@@ -18082,88 +18082,88 @@
         <v>189</v>
       </c>
       <c r="B190">
-        <v>0.04659107883105475</v>
+        <v>0.04626515839692349</v>
       </c>
       <c r="C190">
-        <v>0.04528595982434284</v>
+        <v>0.04701966637549471</v>
       </c>
       <c r="D190">
-        <v>0.04592121148364033</v>
+        <v>0.04665241829859473</v>
       </c>
       <c r="E190">
-        <v>0.04619762719158416</v>
+        <v>0.04649261842136249</v>
       </c>
       <c r="F190">
-        <v>0.04597772394951787</v>
+        <v>0.04661974763318103</v>
       </c>
       <c r="G190">
-        <v>0.04677880289605729</v>
+        <v>0.04615663242796141</v>
       </c>
       <c r="H190">
-        <v>0.04676507186226278</v>
+        <v>0.04616457053513686</v>
       </c>
       <c r="I190">
-        <v>0.04531629267280581</v>
+        <v>0.04700213052162973</v>
       </c>
       <c r="J190">
-        <v>0.04612398133451211</v>
+        <v>0.04653519414546413</v>
       </c>
       <c r="K190">
-        <v>0.0464583701587495</v>
+        <v>0.0463418791799057</v>
       </c>
       <c r="L190">
-        <v>0.04648282378563855</v>
+        <v>0.04632774218818472</v>
       </c>
       <c r="M190">
-        <v>0.04541366387498856</v>
+        <v>0.0469458388359274</v>
       </c>
       <c r="N190">
-        <v>0.04860589887398071</v>
+        <v>0.04510036209102739</v>
       </c>
       <c r="O190">
-        <v>0.04758449904786299</v>
+        <v>0.0456908479502891</v>
       </c>
       <c r="P190">
-        <v>0.04576933654688619</v>
+        <v>0.04674021937339073</v>
       </c>
       <c r="Q190">
-        <v>0.0460136679913376</v>
+        <v>0.04659896786812083</v>
       </c>
       <c r="R190">
-        <v>0.04637179457177618</v>
+        <v>0.04639192976593266</v>
       </c>
       <c r="S190">
-        <v>0.04753810250978113</v>
+        <v>0.04571767045305</v>
       </c>
       <c r="T190">
-        <v>0.04451079101858806</v>
+        <v>0.04746780255746252</v>
       </c>
       <c r="U190">
-        <v>0.04648200523444868</v>
+        <v>0.04632821540434389</v>
       </c>
       <c r="V190">
-        <v>0.04639082169640089</v>
+        <v>0.04638092991284281</v>
       </c>
       <c r="W190">
-        <v>0.04557032383881796</v>
+        <v>0.04685527146848882</v>
       </c>
       <c r="X190">
-        <v>0.04635985696988935</v>
+        <v>0.04639883106445204</v>
       </c>
       <c r="Y190">
-        <v>0.04670416770810482</v>
+        <v>0.04619978009840579</v>
       </c>
       <c r="Z190">
-        <v>0.0463013855549187</v>
+        <v>0.04643263422637583</v>
       </c>
       <c r="AA190">
-        <v>0.0461911831926985</v>
+        <v>0.04649634378935431</v>
       </c>
       <c r="AB190">
-        <v>0.04627331304776557</v>
+        <v>0.04644886334457624</v>
       </c>
       <c r="AC190">
-        <v>0.04632401018232269</v>
+        <v>0.04641955460543649</v>
       </c>
     </row>
     <row r="191" spans="1:29">
@@ -18340,88 +18340,88 @@
         <v>192</v>
       </c>
       <c r="B193">
-        <v>0.01308233311247024</v>
+        <v>0.01469546213546375</v>
       </c>
       <c r="C193">
-        <v>0.003665919064623826</v>
+        <v>-0.0002771469115188004</v>
       </c>
       <c r="D193">
-        <v>0.008249250253399466</v>
+        <v>0.007010598261291892</v>
       </c>
       <c r="E193">
-        <v>0.01024358543811592</v>
+        <v>0.01018169937023584</v>
       </c>
       <c r="F193">
-        <v>0.00865698684663814</v>
+        <v>0.00765892155864174</v>
       </c>
       <c r="G193">
-        <v>0.01443675942433752</v>
+        <v>0.01684907343032534</v>
       </c>
       <c r="H193">
-        <v>0.01433769022156818</v>
+        <v>0.01669154802478088</v>
       </c>
       <c r="I193">
-        <v>0.003884770111086972</v>
+        <v>7.083812201582468E-05</v>
       </c>
       <c r="J193">
-        <v>0.009712231684525173</v>
+        <v>0.009336818083396035</v>
       </c>
       <c r="K193">
-        <v>0.01212484203331218</v>
+        <v>0.01317299938888501</v>
       </c>
       <c r="L193">
-        <v>0.01230127458434751</v>
+        <v>0.01345353671406962</v>
       </c>
       <c r="M193">
-        <v>0.004587301873611378</v>
+        <v>0.00118790172711199</v>
       </c>
       <c r="N193">
-        <v>0.02761922948630294</v>
+        <v>0.03780991579648076</v>
       </c>
       <c r="O193">
-        <v>0.02024984506874392</v>
+        <v>0.02609219488484863</v>
       </c>
       <c r="P193">
-        <v>0.007153474863865845</v>
+        <v>0.005268255961194731</v>
       </c>
       <c r="Q193">
-        <v>0.008916322568964602</v>
+        <v>0.008071279422535691</v>
       </c>
       <c r="R193">
-        <v>0.01150020047251693</v>
+        <v>0.01217978542900999</v>
       </c>
       <c r="S193">
-        <v>0.01991509474274412</v>
+        <v>0.02555992371090941</v>
       </c>
       <c r="T193">
-        <v>-0.001926912236141127</v>
+        <v>-0.009170052013884405</v>
       </c>
       <c r="U193">
-        <v>0.01229536874979639</v>
+        <v>0.01344414611682307</v>
       </c>
       <c r="V193">
-        <v>0.01163748089114909</v>
+        <v>0.01239806874020907</v>
       </c>
       <c r="W193">
-        <v>0.005717601161685291</v>
+        <v>0.002985138898334717</v>
       </c>
       <c r="X193">
-        <v>0.0114140708540479</v>
+        <v>0.01204283466429743</v>
       </c>
       <c r="Y193">
-        <v>0.01389826766329121</v>
+        <v>0.01599284232449249</v>
       </c>
       <c r="Z193">
-        <v>0.01099220047249995</v>
+        <v>0.01137203787697228</v>
       </c>
       <c r="AA193">
-        <v>0.01019709208285928</v>
+        <v>0.01010777241375294</v>
       </c>
       <c r="AB193">
-        <v>0.01078965775466684</v>
+        <v>0.01104998397046188</v>
       </c>
       <c r="AC193">
-        <v>0.01115543681969784</v>
+        <v>0.01163159252234288</v>
       </c>
     </row>
     <row r="194" spans="1:29">
@@ -18785,88 +18785,88 @@
         <v>197</v>
       </c>
       <c r="B198">
-        <v>0.01105705718838996</v>
+        <v>0.002023134526827099</v>
       </c>
       <c r="C198">
-        <v>0.1225051789138545</v>
+        <v>0.127435353272542</v>
       </c>
       <c r="D198">
-        <v>0.06825908803049859</v>
+        <v>0.06639239884104589</v>
       </c>
       <c r="E198">
-        <v>0.04465510149185557</v>
+        <v>0.03983090747426198</v>
       </c>
       <c r="F198">
-        <v>0.06343331494487449</v>
+        <v>0.06096197165697616</v>
       </c>
       <c r="G198">
-        <v>-0.004973277470447596</v>
+        <v>-0.01601575034333216</v>
       </c>
       <c r="H198">
-        <v>-0.003800742308614186</v>
+        <v>-0.01469630023572847</v>
       </c>
       <c r="I198">
-        <v>0.1199149637914058</v>
+        <v>0.1245205923909257</v>
       </c>
       <c r="J198">
-        <v>0.05094394749082769</v>
+        <v>0.04690772597842701</v>
       </c>
       <c r="K198">
-        <v>0.02238945843995327</v>
+        <v>0.01477544979846741</v>
       </c>
       <c r="L198">
-        <v>0.02030128811054684</v>
+        <v>0.01242563833394639</v>
       </c>
       <c r="M198">
-        <v>0.1116001376815947</v>
+        <v>0.1151639448784181</v>
       </c>
       <c r="N198">
-        <v>-0.1609946164475946</v>
+        <v>-0.1915860694286691</v>
       </c>
       <c r="O198">
-        <v>-0.0737741472289863</v>
+        <v>-0.09343715139043293</v>
       </c>
       <c r="P198">
-        <v>0.08122815548823654</v>
+        <v>0.08098644941593444</v>
       </c>
       <c r="Q198">
-        <v>0.06036394278231426</v>
+        <v>0.05750801687421864</v>
       </c>
       <c r="R198">
-        <v>0.02978241379945289</v>
+        <v>0.02309471907253203</v>
       </c>
       <c r="S198">
-        <v>-0.06981220429719714</v>
+        <v>-0.08897878954523684</v>
       </c>
       <c r="T198">
-        <v>0.1886992248033506</v>
+        <v>0.2019233036680358</v>
       </c>
       <c r="U198">
-        <v>0.02037118671150039</v>
+        <v>0.01250429500843393</v>
       </c>
       <c r="V198">
-        <v>0.02815762917034673</v>
+        <v>0.02126635407036458</v>
       </c>
       <c r="W198">
-        <v>0.0982224620607699</v>
+        <v>0.1001100888304811</v>
       </c>
       <c r="X198">
-        <v>0.03080180230069451</v>
+        <v>0.0242418337275417</v>
       </c>
       <c r="Y198">
-        <v>0.001400050531943545</v>
+        <v>-0.008843864508028411</v>
       </c>
       <c r="Z198">
-        <v>0.03579485606789551</v>
+        <v>0.02986050133329867</v>
       </c>
       <c r="AA198">
-        <v>0.04520537435472444</v>
+        <v>0.04045012778573514</v>
       </c>
       <c r="AB198">
-        <v>0.03819205370140789</v>
+        <v>0.03255806024533976</v>
       </c>
       <c r="AC198">
-        <v>0.03386286962378929</v>
+        <v>0.02768644310072602</v>
       </c>
     </row>
     <row r="199" spans="1:29">
@@ -19141,88 +19141,88 @@
         <v>201</v>
       </c>
       <c r="B202">
-        <v>0.04791112238157877</v>
+        <v>0.04692780191636883</v>
       </c>
       <c r="C202">
-        <v>0.04363417665909253</v>
+        <v>0.04896399493896803</v>
       </c>
       <c r="D202">
-        <v>0.04571593077727035</v>
+        <v>0.04797290141446645</v>
       </c>
       <c r="E202">
-        <v>0.04662176003394239</v>
+        <v>0.04754164899000744</v>
       </c>
       <c r="F202">
-        <v>0.0459011251909285</v>
+        <v>0.04788473298835515</v>
       </c>
       <c r="G202">
-        <v>0.04852630431724232</v>
+        <v>0.04663492254723366</v>
       </c>
       <c r="H202">
-        <v>0.04848130697527525</v>
+        <v>0.04665634514169566</v>
       </c>
       <c r="I202">
-        <v>0.043733579047547</v>
+        <v>0.04891667087573838</v>
       </c>
       <c r="J202">
-        <v>0.04638041856870948</v>
+        <v>0.04765654822872993</v>
       </c>
       <c r="K202">
-        <v>0.04747622886962022</v>
+        <v>0.04713484853142592</v>
       </c>
       <c r="L202">
-        <v>0.04755636473032299</v>
+        <v>0.04709669698800906</v>
       </c>
       <c r="M202">
-        <v>0.04405266975462213</v>
+        <v>0.04876475632889093</v>
       </c>
       <c r="N202">
-        <v>0.05451379686555698</v>
+        <v>0.04378436251191579</v>
       </c>
       <c r="O202">
-        <v>0.05116661427546641</v>
+        <v>0.04537790853226275</v>
       </c>
       <c r="P202">
-        <v>0.04521822837790068</v>
+        <v>0.04820985044741754</v>
       </c>
       <c r="Q202">
-        <v>0.04601891576413993</v>
+        <v>0.04782865457191884</v>
       </c>
       <c r="R202">
-        <v>0.04719251597870912</v>
+        <v>0.04726992020321669</v>
       </c>
       <c r="S202">
-        <v>0.05101457030547837</v>
+        <v>0.04545029450367928</v>
       </c>
       <c r="T202">
-        <v>0.04109390646846041</v>
+        <v>0.05017338144356809</v>
       </c>
       <c r="U202">
-        <v>0.04755368229370829</v>
+        <v>0.04709797405792597</v>
       </c>
       <c r="V202">
-        <v>0.04725486889737503</v>
+        <v>0.04724023486555652</v>
       </c>
       <c r="W202">
-        <v>0.04456605294706603</v>
+        <v>0.04852034189340301</v>
       </c>
       <c r="X202">
-        <v>0.04715339581030756</v>
+        <v>0.04728854475894191</v>
       </c>
       <c r="Y202">
-        <v>0.04828172076109253</v>
+        <v>0.04675136529932572</v>
       </c>
       <c r="Z202">
-        <v>0.04696178181429623</v>
+        <v>0.04737976945689852</v>
       </c>
       <c r="AA202">
-        <v>0.04660064270032913</v>
+        <v>0.04755170265216479</v>
       </c>
       <c r="AB202">
-        <v>0.04686978668682463</v>
+        <v>0.04742356702853614</v>
       </c>
       <c r="AC202">
-        <v>0.04703592394455462</v>
+        <v>0.04734447144329058</v>
       </c>
     </row>
     <row r="203" spans="1:29">
@@ -19230,88 +19230,88 @@
         <v>202</v>
       </c>
       <c r="B203">
-        <v>0.02929422588137899</v>
+        <v>0.02809917504511752</v>
       </c>
       <c r="C203">
-        <v>0.05949770320700293</v>
+        <v>0.05569465576691991</v>
       </c>
       <c r="D203">
-        <v>0.01978399419131189</v>
+        <v>0.0194101286669883</v>
       </c>
       <c r="E203">
-        <v>0.01766404599185686</v>
+        <v>0.01747323282421559</v>
       </c>
       <c r="F203">
-        <v>0.04043155152000116</v>
+        <v>0.03827481977766272</v>
       </c>
       <c r="G203">
-        <v>0.01636511475721016</v>
+        <v>0.01628646113371787</v>
       </c>
       <c r="H203">
-        <v>-0.01528395856638667</v>
+        <v>-0.01262979189729581</v>
       </c>
       <c r="I203">
-        <v>0.03961210851924789</v>
+        <v>0.03752613368148536</v>
       </c>
       <c r="J203">
-        <v>0.01521694934728295</v>
+        <v>0.01523743700667782</v>
       </c>
       <c r="K203">
-        <v>0.0071021342018554</v>
+        <v>0.007823316357839252</v>
       </c>
       <c r="L203">
-        <v>0.02526225778703781</v>
+        <v>0.02441535756215769</v>
       </c>
       <c r="M203">
-        <v>0.002857630443600697</v>
+        <v>0.003945315147191704</v>
       </c>
       <c r="N203">
-        <v>0.003038364551570845</v>
+        <v>0.004110443305730957</v>
       </c>
       <c r="O203">
-        <v>-0.02917181824617367</v>
+        <v>-0.02531846876482739</v>
       </c>
       <c r="P203">
-        <v>0.04511496092644561</v>
+        <v>0.0425538282042256</v>
       </c>
       <c r="Q203">
-        <v>0.04364468079280434</v>
+        <v>0.04121050317425876</v>
       </c>
       <c r="R203">
-        <v>0.03336388779791374</v>
+        <v>0.03181743158065595</v>
       </c>
       <c r="S203">
-        <v>-0.008661258233103862</v>
+        <v>-0.006578945585691375</v>
       </c>
       <c r="T203">
-        <v>0.07703385426922028</v>
+        <v>0.07171660295382504</v>
       </c>
       <c r="U203">
-        <v>0.01718881979755754</v>
+        <v>0.01703904125276508</v>
       </c>
       <c r="V203">
-        <v>0.01971394449452169</v>
+        <v>0.01934612759067176</v>
       </c>
       <c r="W203">
-        <v>0.04243580250034416</v>
+        <v>0.04010600857401984</v>
       </c>
       <c r="X203">
-        <v>0.02057144352694718</v>
+        <v>0.02012958367300127</v>
       </c>
       <c r="Y203">
-        <v>0.01103652563373445</v>
+        <v>0.01141798268516088</v>
       </c>
       <c r="Z203">
-        <v>0.02219067894125649</v>
+        <v>0.02160900205843744</v>
       </c>
       <c r="AA203">
-        <v>0.02524248755127263</v>
+        <v>0.0243972944380332</v>
       </c>
       <c r="AB203">
-        <v>0.02296808440978483</v>
+        <v>0.02231928046077217</v>
       </c>
       <c r="AC203">
-        <v>0.02156414035062323</v>
+        <v>0.0210365635470407</v>
       </c>
     </row>
     <row r="204" spans="1:29">
@@ -19319,88 +19319,88 @@
         <v>203</v>
       </c>
       <c r="B204">
-        <v>0.02942377308029305</v>
+        <v>0.02716401974153672</v>
       </c>
       <c r="C204">
-        <v>0.05690455258598879</v>
+        <v>0.0582537514069163</v>
       </c>
       <c r="D204">
-        <v>0.04352859936639475</v>
+        <v>0.0431211822496383</v>
       </c>
       <c r="E204">
-        <v>0.03770834919545222</v>
+        <v>0.03653657950929468</v>
       </c>
       <c r="F204">
-        <v>0.04233866449753051</v>
+        <v>0.04177497750444174</v>
       </c>
       <c r="G204">
-        <v>0.02547102730636969</v>
+        <v>0.02269217404926768</v>
       </c>
       <c r="H204">
-        <v>0.02576014999185014</v>
+        <v>0.02301926617953634</v>
       </c>
       <c r="I204">
-        <v>0.05626585962687661</v>
+        <v>0.05753118119338763</v>
       </c>
       <c r="J204">
-        <v>0.03925904729217521</v>
+        <v>0.03829092522249179</v>
       </c>
       <c r="K204">
-        <v>0.03221810658042529</v>
+        <v>0.0303253230329767</v>
       </c>
       <c r="L204">
-        <v>0.03170320738334316</v>
+        <v>0.02974280397202047</v>
       </c>
       <c r="M204">
-        <v>0.05421559714228499</v>
+        <v>0.05521166509391394</v>
       </c>
       <c r="N204">
-        <v>-0.01300057677482073</v>
+        <v>-0.02083176774332344</v>
       </c>
       <c r="O204">
-        <v>0.008506169555855529</v>
+        <v>0.003499382407549394</v>
       </c>
       <c r="P204">
-        <v>0.04672650057534045</v>
+        <v>0.04673905234891654</v>
       </c>
       <c r="Q204">
-        <v>0.04158182141830825</v>
+        <v>0.04091874093950213</v>
       </c>
       <c r="R204">
-        <v>0.03404105498892629</v>
+        <v>0.03238767271444698</v>
       </c>
       <c r="S204">
-        <v>0.009483101947689376</v>
+        <v>0.004604611824751212</v>
       </c>
       <c r="T204">
-        <v>0.07322662200731231</v>
+        <v>0.076719339634771</v>
       </c>
       <c r="U204">
-        <v>0.03172044291868303</v>
+        <v>0.02976230298836804</v>
       </c>
       <c r="V204">
-        <v>0.03364041702890128</v>
+        <v>0.03193442040879236</v>
       </c>
       <c r="W204">
-        <v>0.05091694169306885</v>
+        <v>0.05147980906153987</v>
       </c>
       <c r="X204">
-        <v>0.03429241490598501</v>
+        <v>0.03267204282742606</v>
       </c>
       <c r="Y204">
-        <v>0.02704255690094309</v>
+        <v>0.02447008698617558</v>
       </c>
       <c r="Z204">
-        <v>0.03552359769769269</v>
+        <v>0.03406491243715787</v>
       </c>
       <c r="AA204">
-        <v>0.03784403499238038</v>
+        <v>0.03669008443503471</v>
       </c>
       <c r="AB204">
-        <v>0.03611469657471465</v>
+        <v>0.03473363820858336</v>
       </c>
       <c r="AC204">
-        <v>0.03504721018522063</v>
+        <v>0.03352596266215516</v>
       </c>
     </row>
     <row r="205" spans="1:29">
@@ -19586,88 +19586,88 @@
         <v>206</v>
       </c>
       <c r="B207">
-        <v>0.02578549581614217</v>
+        <v>0.02094002090855639</v>
       </c>
       <c r="C207">
-        <v>0.08943457848467459</v>
+        <v>0.09094774884327689</v>
       </c>
       <c r="D207">
-        <v>0.05845411986748338</v>
+        <v>0.05687229280787574</v>
       </c>
       <c r="E207">
-        <v>0.04497365857980119</v>
+        <v>0.04204511185418759</v>
       </c>
       <c r="F207">
-        <v>0.05569807494441954</v>
+        <v>0.05384091458433519</v>
       </c>
       <c r="G207">
-        <v>0.01663041917503031</v>
+        <v>0.0108703374529401</v>
       </c>
       <c r="H207">
-        <v>0.01730006516180735</v>
+        <v>0.01160688214595641</v>
       </c>
       <c r="I207">
-        <v>0.08795528198415446</v>
+        <v>0.08932066825387514</v>
       </c>
       <c r="J207">
-        <v>0.04856527836379605</v>
+        <v>0.04599554020509267</v>
       </c>
       <c r="K207">
-        <v>0.03225753799080115</v>
+        <v>0.02805863045875447</v>
       </c>
       <c r="L207">
-        <v>0.03106496404819339</v>
+        <v>0.02674691646986775</v>
       </c>
       <c r="M207">
-        <v>0.08320660568307227</v>
+        <v>0.08409759158727967</v>
       </c>
       <c r="N207">
-        <v>-0.07247485194900086</v>
+        <v>-0.08713669292150904</v>
       </c>
       <c r="O207">
-        <v>-0.02266241213634376</v>
+        <v>-0.03234791061760933</v>
       </c>
       <c r="P207">
-        <v>0.06586087768422572</v>
+        <v>0.06501899758936067</v>
       </c>
       <c r="Q207">
-        <v>0.0539451272994468</v>
+        <v>0.05191284466301122</v>
       </c>
       <c r="R207">
-        <v>0.03647972513542347</v>
+        <v>0.03270262085920575</v>
       </c>
       <c r="S207">
-        <v>-0.02039970883287627</v>
+        <v>-0.02985915963134476</v>
       </c>
       <c r="T207">
-        <v>0.1272386278823281</v>
+        <v>0.1325284833032584</v>
       </c>
       <c r="U207">
-        <v>0.03110488380423438</v>
+        <v>0.02679082427345217</v>
       </c>
       <c r="V207">
-        <v>0.03555179517504883</v>
+        <v>0.03168198921009478</v>
       </c>
       <c r="W207">
-        <v>0.07556648785676943</v>
+        <v>0.07569421375764991</v>
       </c>
       <c r="X207">
-        <v>0.03706190760725292</v>
+        <v>0.03334296429209467</v>
       </c>
       <c r="Y207">
-        <v>0.02027028743496509</v>
+        <v>0.01487383437978142</v>
       </c>
       <c r="Z207">
-        <v>0.03991348811912429</v>
+        <v>0.03647942226272523</v>
       </c>
       <c r="AA207">
-        <v>0.04528792464724796</v>
+        <v>0.04239077360493902</v>
       </c>
       <c r="AB207">
-        <v>0.04128255049528615</v>
+        <v>0.03798525616225111</v>
       </c>
       <c r="AC207">
-        <v>0.03881011227939218</v>
+        <v>0.0352658174100052</v>
       </c>
     </row>
     <row r="208" spans="1:29">
@@ -19675,88 +19675,88 @@
         <v>207</v>
       </c>
       <c r="B208">
-        <v>0.001913122330951207</v>
+        <v>0.001640033022272519</v>
       </c>
       <c r="C208">
-        <v>-0.003790158597536853</v>
+        <v>-0.0009908540294963565</v>
       </c>
       <c r="D208">
-        <v>-0.001014152229819092</v>
+        <v>0.0002896999709170035</v>
       </c>
       <c r="E208">
-        <v>0.0001937655365632611</v>
+        <v>0.0008469047186795116</v>
       </c>
       <c r="F208">
-        <v>-0.0007671966133552359</v>
+        <v>0.0004036190188935855</v>
       </c>
       <c r="G208">
-        <v>0.002733463674722277</v>
+        <v>0.002018451242665203</v>
       </c>
       <c r="H208">
-        <v>0.002673459994777456</v>
+        <v>0.001990771928494165</v>
       </c>
       <c r="I208">
-        <v>-0.003657606121283073</v>
+        <v>-0.0009297084191312679</v>
       </c>
       <c r="J208">
-        <v>-0.000128061829325319</v>
+        <v>0.000698447811078853</v>
       </c>
       <c r="K208">
-        <v>0.001333194496086246</v>
+        <v>0.00137251601744017</v>
       </c>
       <c r="L208">
-        <v>0.001440055175573294</v>
+        <v>0.001421810166111929</v>
       </c>
       <c r="M208">
-        <v>-0.00323210061754209</v>
+        <v>-0.0007334254489803813</v>
       </c>
       <c r="N208">
-        <v>0.01071774831989111</v>
+        <v>0.005701550734693969</v>
       </c>
       <c r="O208">
-        <v>0.006254300834489395</v>
+        <v>0.003642590928429134</v>
       </c>
       <c r="P208">
-        <v>-0.001677835331398825</v>
+        <v>-1.645280330497649E-05</v>
       </c>
       <c r="Q208">
-        <v>-0.0006101236053391475</v>
+        <v>0.0004760757938891435</v>
       </c>
       <c r="R208">
-        <v>0.0009548650935426789</v>
+        <v>0.001197995081344674</v>
       </c>
       <c r="S208">
-        <v>0.006051551131642961</v>
+        <v>0.003549063785955008</v>
       </c>
       <c r="T208">
-        <v>-0.007177593339873715</v>
+        <v>-0.002553456032461104</v>
       </c>
       <c r="U208">
-        <v>0.001436478162775102</v>
+        <v>0.001420160112963088</v>
       </c>
       <c r="V208">
-        <v>0.001038012328728109</v>
+        <v>0.001236350369674776</v>
       </c>
       <c r="W208">
-        <v>-0.002547507274428647</v>
+        <v>-0.0004176269139427959</v>
       </c>
       <c r="X208">
-        <v>0.0009026985885550666</v>
+        <v>0.001173931005906551</v>
       </c>
       <c r="Y208">
-        <v>0.002407313000450922</v>
+        <v>0.001868000020530917</v>
       </c>
       <c r="Z208">
-        <v>0.0006471824983374039</v>
+        <v>0.001056063066083628</v>
       </c>
       <c r="AA208">
-        <v>0.0001656057015146685</v>
+        <v>0.0008339147666960435</v>
       </c>
       <c r="AB208">
-        <v>0.0005245075592414669</v>
+        <v>0.0009994739004979172</v>
       </c>
       <c r="AC208">
-        <v>0.0007460505749830675</v>
+        <v>0.001101670278132592</v>
       </c>
     </row>
     <row r="209" spans="1:29">
@@ -20120,88 +20120,88 @@
         <v>212</v>
       </c>
       <c r="B213">
-        <v>0.004968670414090284</v>
+        <v>0.004196755625407458</v>
       </c>
       <c r="C213">
-        <v>0.03066867661763914</v>
+        <v>0.02852299907568175</v>
       </c>
       <c r="D213">
-        <v>-0.003123543962317189</v>
+        <v>-0.003462899217209457</v>
       </c>
       <c r="E213">
-        <v>-0.00492739857448049</v>
+        <v>-0.005170330962433127</v>
       </c>
       <c r="F213">
-        <v>0.01444537188517233</v>
+        <v>0.01316689147927666</v>
       </c>
       <c r="G213">
-        <v>-0.006032653457171854</v>
+        <v>-0.006216505781925651</v>
       </c>
       <c r="H213">
-        <v>-0.03296271094637878</v>
+        <v>-0.03170704961385157</v>
       </c>
       <c r="I213">
-        <v>0.01374811143480203</v>
+        <v>0.01250690224310233</v>
       </c>
       <c r="J213">
-        <v>-0.00700962236176866</v>
+        <v>-0.007141251995149831</v>
       </c>
       <c r="K213">
-        <v>-0.01391448292897264</v>
+        <v>-0.01367702159059874</v>
       </c>
       <c r="L213">
-        <v>0.001537886470906065</v>
+        <v>0.0009493600891500881</v>
       </c>
       <c r="M213">
-        <v>-0.01752611253513021</v>
+        <v>-0.01709559590360709</v>
       </c>
       <c r="N213">
-        <v>-0.01737232667643754</v>
+        <v>-0.01695003048202168</v>
       </c>
       <c r="O213">
-        <v>-0.04477982975281968</v>
+        <v>-0.04289249862462266</v>
       </c>
       <c r="P213">
-        <v>0.01843046437971326</v>
+        <v>0.01693896567358861</v>
       </c>
       <c r="Q213">
-        <v>0.01717940947142698</v>
+        <v>0.01575478439255724</v>
       </c>
       <c r="R213">
-        <v>0.008431527865028807</v>
+        <v>0.00747451021884777</v>
       </c>
       <c r="S213">
-        <v>-0.0273274843195024</v>
+        <v>-0.02637304721178471</v>
       </c>
       <c r="T213">
-        <v>0.04559011053819668</v>
+        <v>0.04264682579011034</v>
       </c>
       <c r="U213">
-        <v>-0.005331766456029679</v>
+        <v>-0.005553083847865462</v>
       </c>
       <c r="V213">
-        <v>-0.003183148941659669</v>
+        <v>-0.003519318084459905</v>
       </c>
       <c r="W213">
-        <v>0.01615078024173214</v>
+        <v>0.01478113929444168</v>
       </c>
       <c r="X213">
-        <v>-0.002453506781080507</v>
+        <v>-0.002828678063237581</v>
       </c>
       <c r="Y213">
-        <v>-0.01056672653932348</v>
+        <v>-0.01050821547040524</v>
       </c>
       <c r="Z213">
-        <v>-0.001075706478681196</v>
+        <v>-0.00152452640986565</v>
       </c>
       <c r="AA213">
-        <v>0.001521064064123785</v>
+        <v>0.0009334369037794638</v>
       </c>
       <c r="AB213">
-        <v>-0.000414215579853423</v>
+        <v>-0.0008983947071113073</v>
       </c>
       <c r="AC213">
-        <v>-0.001608825413711136</v>
+        <v>-0.002029148116910157</v>
       </c>
     </row>
     <row r="214" spans="1:29">
@@ -20387,88 +20387,88 @@
         <v>215</v>
       </c>
       <c r="B216">
-        <v>0.01088882893915406</v>
+        <v>0.009896635323697263</v>
       </c>
       <c r="C216">
-        <v>0.02361626209470889</v>
+        <v>0.02401544287272077</v>
       </c>
       <c r="D216">
-        <v>0.01742133045316186</v>
+        <v>0.01714327575486127</v>
       </c>
       <c r="E216">
-        <v>0.01472574297959969</v>
+        <v>0.01415300424405216</v>
       </c>
       <c r="F216">
-        <v>0.01687022467030754</v>
+        <v>0.01653192259415909</v>
       </c>
       <c r="G216">
-        <v>0.009058156428278435</v>
+        <v>0.007865832054063913</v>
       </c>
       <c r="H216">
-        <v>0.00919206055033743</v>
+        <v>0.008014374694694227</v>
       </c>
       <c r="I216">
-        <v>0.02332045818775134</v>
+        <v>0.02368730141768118</v>
       </c>
       <c r="J216">
-        <v>0.01544393244603739</v>
+        <v>0.01494970682629627</v>
       </c>
       <c r="K216">
-        <v>0.01218299502457713</v>
+        <v>0.01133228080485908</v>
       </c>
       <c r="L216">
-        <v>0.01194452489270356</v>
+        <v>0.01106774090455375</v>
       </c>
       <c r="M216">
-        <v>0.0223709007445728</v>
+        <v>0.02263393750422551</v>
       </c>
       <c r="N216">
-        <v>-0.008759561196101037</v>
+        <v>-0.01189973442166052</v>
       </c>
       <c r="O216">
-        <v>0.001201061509685856</v>
+        <v>-0.0008502075192103782</v>
       </c>
       <c r="P216">
-        <v>0.01890240466601265</v>
+        <v>0.01878626232736864</v>
       </c>
       <c r="Q216">
-        <v>0.01651970078149102</v>
+        <v>0.01614307911982697</v>
       </c>
       <c r="R216">
-        <v>0.01302727435116656</v>
+        <v>0.01226885750371472</v>
       </c>
       <c r="S216">
-        <v>0.001653517442094342</v>
+        <v>-0.0003482886989727473</v>
       </c>
       <c r="T216">
-        <v>0.03117565637889082</v>
+        <v>0.03240123691155816</v>
       </c>
       <c r="U216">
-        <v>0.0119525073490925</v>
+        <v>0.01107659601022561</v>
       </c>
       <c r="V216">
-        <v>0.01284172310598665</v>
+        <v>0.01206302163019977</v>
       </c>
       <c r="W216">
-        <v>0.02084316326811571</v>
+        <v>0.02093918639833466</v>
       </c>
       <c r="X216">
-        <v>0.01314368904535992</v>
+        <v>0.01239799875655855</v>
       </c>
       <c r="Y216">
-        <v>0.009785993783210949</v>
+        <v>0.008673237240615413</v>
       </c>
       <c r="Z216">
-        <v>0.01371389836858821</v>
+        <v>0.01303054387378083</v>
       </c>
       <c r="AA216">
-        <v>0.01478858442520728</v>
+        <v>0.01422271557278531</v>
       </c>
       <c r="AB216">
-        <v>0.01398765957845714</v>
+        <v>0.01333423290434081</v>
       </c>
       <c r="AC216">
-        <v>0.0134932645172132</v>
+        <v>0.01278579013213545</v>
       </c>
     </row>
     <row r="217" spans="1:29">
@@ -20476,88 +20476,88 @@
         <v>216</v>
       </c>
       <c r="B217">
-        <v>0.01548537699316458</v>
+        <v>0.01430160444016906</v>
       </c>
       <c r="C217">
-        <v>0.01369027017373336</v>
+        <v>0.01912687259174866</v>
       </c>
       <c r="D217">
-        <v>0.01456401776287688</v>
+        <v>0.01677822884042609</v>
       </c>
       <c r="E217">
-        <v>0.01494420969922603</v>
+        <v>0.01575626846341954</v>
       </c>
       <c r="F217">
-        <v>0.01464174700623165</v>
+        <v>0.01656929172406828</v>
       </c>
       <c r="G217">
-        <v>0.01574357930845106</v>
+        <v>0.01360755359309429</v>
       </c>
       <c r="H217">
-        <v>0.01572469315916077</v>
+        <v>0.01365831978354601</v>
       </c>
       <c r="I217">
-        <v>0.01373199104581369</v>
+        <v>0.01901472639903955</v>
       </c>
       <c r="J217">
-        <v>0.01484291458393538</v>
+        <v>0.01602855091950058</v>
       </c>
       <c r="K217">
-        <v>0.01530284479385732</v>
+        <v>0.01479225312938421</v>
       </c>
       <c r="L217">
-        <v>0.01533647917674702</v>
+        <v>0.01470184351431345</v>
       </c>
       <c r="M217">
-        <v>0.01386591883949042</v>
+        <v>0.01865472692132358</v>
       </c>
       <c r="N217">
-        <v>0.01825663170662955</v>
+        <v>0.006852439318600275</v>
       </c>
       <c r="O217">
-        <v>0.01685176227801772</v>
+        <v>0.01062874479392366</v>
       </c>
       <c r="P217">
-        <v>0.01435512360589505</v>
+        <v>0.01733973878057263</v>
       </c>
       <c r="Q217">
-        <v>0.01469118571201762</v>
+        <v>0.01643639990398153</v>
       </c>
       <c r="R217">
-        <v>0.01518376567097825</v>
+        <v>0.01511233920611611</v>
       </c>
       <c r="S217">
-        <v>0.01678794683936393</v>
+        <v>0.01080028144031265</v>
       </c>
       <c r="T217">
-        <v>0.01262407559510523</v>
+        <v>0.02199281610438664</v>
       </c>
       <c r="U217">
-        <v>0.01533535331250365</v>
+        <v>0.01470486985058363</v>
       </c>
       <c r="V217">
-        <v>0.01520993625081988</v>
+        <v>0.01504199238104072</v>
       </c>
       <c r="W217">
-        <v>0.01408139449186828</v>
+        <v>0.01807552584448228</v>
       </c>
       <c r="X217">
-        <v>0.01516734627133385</v>
+        <v>0.0151564747446337</v>
       </c>
       <c r="Y217">
-        <v>0.01564092343249339</v>
+        <v>0.01388349378978296</v>
       </c>
       <c r="Z217">
-        <v>0.0150869226201451</v>
+        <v>0.01537265446080109</v>
       </c>
       <c r="AA217">
-        <v>0.01493534639535522</v>
+        <v>0.01578009312801478</v>
       </c>
       <c r="AB217">
-        <v>0.01504831070140822</v>
+        <v>0.01547644375051674</v>
       </c>
       <c r="AC217">
-        <v>0.0151180413324856</v>
+        <v>0.01528900699762541</v>
       </c>
     </row>
     <row r="218" spans="1:29">
@@ -20565,88 +20565,88 @@
         <v>217</v>
       </c>
       <c r="B218">
-        <v>0.01010544356204262</v>
+        <v>0.005518794893584845</v>
       </c>
       <c r="C218">
-        <v>0.07096923079247899</v>
+        <v>0.0722220349118225</v>
       </c>
       <c r="D218">
-        <v>0.04134448268106145</v>
+        <v>0.03975500034701418</v>
       </c>
       <c r="E218">
-        <v>0.02845392883200721</v>
+        <v>0.02562768841839501</v>
       </c>
       <c r="F218">
-        <v>0.03870904278527466</v>
+        <v>0.0368667085084413</v>
       </c>
       <c r="G218">
-        <v>0.00135099474045023</v>
+        <v>-0.004075581788286129</v>
       </c>
       <c r="H218">
-        <v>0.001991336897008332</v>
+        <v>-0.003373803300513494</v>
       </c>
       <c r="I218">
-        <v>0.06955466857596965</v>
+        <v>0.07067175538860926</v>
       </c>
       <c r="J218">
-        <v>0.03188837868078347</v>
+        <v>0.02939164960152299</v>
       </c>
       <c r="K218">
-        <v>0.01629426799359412</v>
+        <v>0.01230139354991813</v>
       </c>
       <c r="L218">
-        <v>0.01515388130369566</v>
+        <v>0.01105159476888103</v>
       </c>
       <c r="M218">
-        <v>0.06501379521381243</v>
+        <v>0.06569521712914111</v>
       </c>
       <c r="N218">
-        <v>-0.08385501350709058</v>
+        <v>-0.09745650791457676</v>
       </c>
       <c r="O218">
-        <v>-0.03622237512367262</v>
+        <v>-0.04525385252013579</v>
       </c>
       <c r="P218">
-        <v>0.04842711942813355</v>
+        <v>0.04751716633108702</v>
       </c>
       <c r="Q218">
-        <v>0.03703280444818292</v>
+        <v>0.03502964687927458</v>
       </c>
       <c r="R218">
-        <v>0.02033169146056931</v>
+        <v>0.01672617943373571</v>
       </c>
       <c r="S218">
-        <v>-0.03405868812844846</v>
+        <v>-0.04288257495864677</v>
       </c>
       <c r="T218">
-        <v>0.1071189681102995</v>
+        <v>0.1118400855562457</v>
       </c>
       <c r="U218">
-        <v>0.01519205416394917</v>
+        <v>0.01109343004689342</v>
       </c>
       <c r="V218">
-        <v>0.01944436788409126</v>
+        <v>0.01575372339396337</v>
       </c>
       <c r="W218">
-        <v>0.05770801033365648</v>
+        <v>0.05768849351633645</v>
       </c>
       <c r="X218">
-        <v>0.02088839752150734</v>
+        <v>0.01733629753009674</v>
       </c>
       <c r="Y218">
-        <v>0.004831581703080796</v>
+        <v>-0.0002610569593646216</v>
       </c>
       <c r="Z218">
-        <v>0.02361519235135339</v>
+        <v>0.02032470916684014</v>
       </c>
       <c r="AA218">
-        <v>0.02875444255916391</v>
+        <v>0.025957034326421</v>
       </c>
       <c r="AB218">
-        <v>0.02492434430884274</v>
+        <v>0.02175946505723747</v>
       </c>
       <c r="AC218">
-        <v>0.02256010043911974</v>
+        <v>0.01916838859814855</v>
       </c>
     </row>
     <row r="219" spans="1:29">
@@ -20654,88 +20654,88 @@
         <v>218</v>
       </c>
       <c r="B219">
-        <v>0.01040051518218265</v>
+        <v>0.008213681958326856</v>
       </c>
       <c r="C219">
-        <v>0.03253855002104871</v>
+        <v>0.03514592447800433</v>
       </c>
       <c r="D219">
-        <v>0.02176311629228416</v>
+        <v>0.02203696532466946</v>
       </c>
       <c r="E219">
-        <v>0.01707442465496956</v>
+        <v>0.01633289171582115</v>
       </c>
       <c r="F219">
-        <v>0.02080452559519574</v>
+        <v>0.02087078244895336</v>
       </c>
       <c r="G219">
-        <v>0.007216252391014027</v>
+        <v>0.004339835956983628</v>
       </c>
       <c r="H219">
-        <v>0.007449164564504093</v>
+        <v>0.004623187536646286</v>
       </c>
       <c r="I219">
-        <v>0.03202403015536465</v>
+        <v>0.03451998030975922</v>
       </c>
       <c r="J219">
-        <v>0.01832363989221207</v>
+        <v>0.01785263671457891</v>
       </c>
       <c r="K219">
-        <v>0.0126515813269591</v>
+        <v>0.01095223846436857</v>
       </c>
       <c r="L219">
-        <v>0.0122367875485968</v>
+        <v>0.01044761704174374</v>
       </c>
       <c r="M219">
-        <v>0.03037237459358184</v>
+        <v>0.03251064260328793</v>
       </c>
       <c r="N219">
-        <v>-0.02377579829953981</v>
+        <v>-0.03336384602994413</v>
       </c>
       <c r="O219">
-        <v>-0.006450339993654246</v>
+        <v>-0.01228639049900095</v>
       </c>
       <c r="P219">
-        <v>0.02433928951765495</v>
+        <v>0.02517103402513862</v>
       </c>
       <c r="Q219">
-        <v>0.02019482606131227</v>
+        <v>0.0201290465256791</v>
       </c>
       <c r="R219">
-        <v>0.01412011664883692</v>
+        <v>0.01273879945433004</v>
       </c>
       <c r="S219">
-        <v>-0.005663340362834025</v>
+        <v>-0.01132895841099397</v>
       </c>
       <c r="T219">
-        <v>0.04568732338159907</v>
+        <v>0.05114219314232609</v>
       </c>
       <c r="U219">
-        <v>0.01225067219410846</v>
+        <v>0.01046450854286123</v>
       </c>
       <c r="V219">
-        <v>0.01379736972257277</v>
+        <v>0.01234615852870614</v>
       </c>
       <c r="W219">
-        <v>0.02771503551624501</v>
+        <v>0.02927783079281029</v>
       </c>
       <c r="X219">
-        <v>0.01432260779723346</v>
+        <v>0.01298514203877341</v>
       </c>
       <c r="Y219">
-        <v>0.008482249118208916</v>
+        <v>0.005879996641258581</v>
       </c>
       <c r="Z219">
-        <v>0.01531442709879977</v>
+        <v>0.01419174949783228</v>
       </c>
       <c r="AA219">
-        <v>0.01718373075740063</v>
+        <v>0.01646586912239682</v>
       </c>
       <c r="AB219">
-        <v>0.0157906060052247</v>
+        <v>0.01477104959758983</v>
       </c>
       <c r="AC219">
-        <v>0.01493065765930039</v>
+        <v>0.01372487103768584</v>
       </c>
     </row>
     <row r="220" spans="1:29">
@@ -20832,88 +20832,88 @@
         <v>220</v>
       </c>
       <c r="B221">
-        <v>0.001430970281339362</v>
+        <v>-0.001322852351107837</v>
       </c>
       <c r="C221">
-        <v>0.05619284912279161</v>
+        <v>0.05162266869656217</v>
       </c>
       <c r="D221">
-        <v>0.02953813470872183</v>
+        <v>0.02585204553887908</v>
       </c>
       <c r="E221">
-        <v>0.01793992532670497</v>
+        <v>0.01463852891121305</v>
       </c>
       <c r="F221">
-        <v>0.02716691124672152</v>
+        <v>0.02355947150065901</v>
       </c>
       <c r="G221">
-        <v>-0.006445799921550626</v>
+        <v>-0.00893836356781013</v>
       </c>
       <c r="H221">
-        <v>-0.005869655366796837</v>
+        <v>-0.00838132874184052</v>
       </c>
       <c r="I221">
-        <v>0.05492010405977255</v>
+        <v>0.05039213840892372</v>
       </c>
       <c r="J221">
-        <v>0.02103005387545353</v>
+        <v>0.01762616318489194</v>
       </c>
       <c r="K221">
-        <v>0.00699933316366361</v>
+        <v>0.004060817464910198</v>
       </c>
       <c r="L221">
-        <v>0.005973276117489611</v>
+        <v>0.003068792974815566</v>
       </c>
       <c r="M221">
-        <v>0.05083447665786023</v>
+        <v>0.04644202427520001</v>
       </c>
       <c r="N221">
-        <v>-0.08310946665246755</v>
+        <v>-0.08305922768653434</v>
       </c>
       <c r="O221">
-        <v>-0.04025224578687173</v>
+        <v>-0.04162350748501266</v>
       </c>
       <c r="P221">
-        <v>0.03591070061482801</v>
+        <v>0.0320132443408094</v>
       </c>
       <c r="Q221">
-        <v>0.025658724443004</v>
+        <v>0.02210130867189208</v>
       </c>
       <c r="R221">
-        <v>0.01063198411739143</v>
+        <v>0.007572979603946373</v>
       </c>
       <c r="S221">
-        <v>-0.03830547956552757</v>
+        <v>-0.0397413121672536</v>
       </c>
       <c r="T221">
-        <v>0.08871838894261494</v>
+        <v>0.08306939202946848</v>
       </c>
       <c r="U221">
-        <v>0.006007621951742745</v>
+        <v>0.003101999616530942</v>
       </c>
       <c r="V221">
-        <v>0.009833619303117175</v>
+        <v>0.00680109518412474</v>
       </c>
       <c r="W221">
-        <v>0.04426113436921696</v>
+        <v>0.04008670849970366</v>
       </c>
       <c r="X221">
-        <v>0.01113287752620883</v>
+        <v>0.008057259235694621</v>
       </c>
       <c r="Y221">
-        <v>-0.003314159742422933</v>
+        <v>-0.005910594533482798</v>
       </c>
       <c r="Z221">
-        <v>0.01358629711924484</v>
+        <v>0.01042930309996627</v>
       </c>
       <c r="AA221">
-        <v>0.0182103110037323</v>
+        <v>0.01489994635811049</v>
       </c>
       <c r="AB221">
-        <v>0.01476419984504221</v>
+        <v>0.01156813680838179</v>
       </c>
       <c r="AC221">
-        <v>0.0126369836096274</v>
+        <v>0.009511476694670583</v>
       </c>
     </row>
     <row r="222" spans="1:29">
@@ -21010,88 +21010,88 @@
         <v>222</v>
       </c>
       <c r="B223">
-        <v>0.02150302474543735</v>
+        <v>0.02022167503916447</v>
       </c>
       <c r="C223">
-        <v>0.03689252166788305</v>
+        <v>0.03771392535399826</v>
       </c>
       <c r="D223">
-        <v>0.02940186111856875</v>
+        <v>0.02919977378605778</v>
       </c>
       <c r="E223">
-        <v>0.02614246587197396</v>
+        <v>0.0254950290620597</v>
       </c>
       <c r="F223">
-        <v>0.0287354863165548</v>
+        <v>0.02844234845246387</v>
       </c>
       <c r="G223">
-        <v>0.01928944965705982</v>
+        <v>0.01770564675495811</v>
       </c>
       <c r="H223">
-        <v>0.01945136110056486</v>
+        <v>0.01788968106828873</v>
       </c>
       <c r="I223">
-        <v>0.03653484755872587</v>
+        <v>0.03730738022259845</v>
       </c>
       <c r="J223">
-        <v>0.02701087150006812</v>
+        <v>0.0264820898281123</v>
       </c>
       <c r="K223">
-        <v>0.02306787798374011</v>
+        <v>0.02200034296367905</v>
       </c>
       <c r="L223">
-        <v>0.02277952955435066</v>
+        <v>0.02167259586900873</v>
       </c>
       <c r="M223">
-        <v>0.03538668113970967</v>
+        <v>0.03600233337761516</v>
       </c>
       <c r="N223">
-        <v>-0.002255013173272839</v>
+        <v>-0.006782557026229595</v>
       </c>
       <c r="O223">
-        <v>0.009788968563095421</v>
+        <v>0.006907061574139792</v>
       </c>
       <c r="P223">
-        <v>0.03119271609788821</v>
+        <v>0.0312353233386967</v>
       </c>
       <c r="Q223">
-        <v>0.02831164702058245</v>
+        <v>0.02796059761318868</v>
       </c>
       <c r="R223">
-        <v>0.0240887463661886</v>
+        <v>0.02316069832644881</v>
       </c>
       <c r="S223">
-        <v>0.01033605995962762</v>
+        <v>0.007528905140661807</v>
       </c>
       <c r="T223">
-        <v>0.04603303520663989</v>
+        <v>0.04810335859095246</v>
       </c>
       <c r="U223">
-        <v>0.02278918161745951</v>
+        <v>0.02168356674770642</v>
       </c>
       <c r="V223">
-        <v>0.02386438531225482</v>
+        <v>0.02290568156169767</v>
       </c>
       <c r="W223">
-        <v>0.03353940283112315</v>
+        <v>0.03390265105935632</v>
       </c>
       <c r="X223">
-        <v>0.02422951030154931</v>
+        <v>0.02332069562883231</v>
       </c>
       <c r="Y223">
-        <v>0.02016952112134296</v>
+        <v>0.01870596732591388</v>
       </c>
       <c r="Z223">
-        <v>0.02491898433120797</v>
+        <v>0.02410437636726998</v>
       </c>
       <c r="AA223">
-        <v>0.02621845120396983</v>
+        <v>0.02558139669670206</v>
       </c>
       <c r="AB223">
-        <v>0.02525000530340802</v>
+        <v>0.02448062659392539</v>
       </c>
       <c r="AC223">
-        <v>0.02465220281012482</v>
+        <v>0.02380114298870825</v>
       </c>
     </row>
     <row r="224" spans="1:29">
@@ -21722,88 +21722,88 @@
         <v>230</v>
       </c>
       <c r="B231">
-        <v>0.02347135581324308</v>
+        <v>0.02383042231980463</v>
       </c>
       <c r="C231">
-        <v>0.06370845238890825</v>
+        <v>0.06732685356580559</v>
       </c>
       <c r="D231">
-        <v>0.01080181757283863</v>
+        <v>0.01013461059651004</v>
       </c>
       <c r="E231">
-        <v>0.007977620891203156</v>
+        <v>0.00708164486979717</v>
       </c>
       <c r="F231">
-        <v>0.03830850990926121</v>
+        <v>0.03986943377805386</v>
       </c>
       <c r="G231">
-        <v>0.006247183664715763</v>
+        <v>0.005211036643731714</v>
       </c>
       <c r="H231">
-        <v>-0.03591573705208174</v>
+        <v>-0.04036721671359205</v>
       </c>
       <c r="I231">
-        <v>0.03721684729028225</v>
+        <v>0.0386893429640719</v>
       </c>
       <c r="J231">
-        <v>0.004717596790131458</v>
+        <v>0.003557548296230542</v>
       </c>
       <c r="K231">
-        <v>-0.006092966416881453</v>
+        <v>-0.008128705416935422</v>
       </c>
       <c r="L231">
-        <v>0.01809996470310854</v>
+        <v>0.0180239311959235</v>
       </c>
       <c r="M231">
-        <v>-0.01174749770794498</v>
+        <v>-0.01424127199011242</v>
       </c>
       <c r="N231">
-        <v>-0.01150672358520044</v>
+        <v>-0.01398099438643195</v>
       </c>
       <c r="O231">
-        <v>-0.05441715479085306</v>
+        <v>-0.06036730899447267</v>
       </c>
       <c r="P231">
-        <v>0.04454775165480056</v>
+        <v>0.04661407423941757</v>
       </c>
       <c r="Q231">
-        <v>0.04258904328844912</v>
+        <v>0.04449670417451339</v>
       </c>
       <c r="R231">
-        <v>0.02889296266335872</v>
+        <v>0.02969119682065477</v>
       </c>
       <c r="S231">
-        <v>-0.0270929703875323</v>
+        <v>-0.0308297774775768</v>
       </c>
       <c r="T231">
-        <v>0.08707012681628536</v>
+        <v>0.09258089901143099</v>
       </c>
       <c r="U231">
-        <v>0.007344524176240298</v>
+        <v>0.006397265277878372</v>
       </c>
       <c r="V231">
-        <v>0.01070849731092123</v>
+        <v>0.01003373109222683</v>
       </c>
       <c r="W231">
-        <v>0.04097857466334552</v>
+        <v>0.04275578239369023</v>
       </c>
       <c r="X231">
-        <v>0.01185085820563754</v>
+        <v>0.01126862690588747</v>
       </c>
       <c r="Y231">
-        <v>-0.000851567014280824</v>
+        <v>-0.002462735748390075</v>
       </c>
       <c r="Z231">
-        <v>0.01400800491566309</v>
+        <v>0.01360050946067672</v>
       </c>
       <c r="AA231">
-        <v>0.01807362677925853</v>
+        <v>0.01799545981524747</v>
       </c>
       <c r="AB231">
-        <v>0.01504366510069376</v>
+        <v>0.01472006146283711</v>
       </c>
       <c r="AC231">
-        <v>0.0131733297056566</v>
+        <v>0.01269822286510893</v>
       </c>
     </row>
     <row r="232" spans="1:29">
@@ -22167,88 +22167,88 @@
         <v>235</v>
       </c>
       <c r="B236">
-        <v>0.03353205144661163</v>
+        <v>0.03307599023399801</v>
       </c>
       <c r="C236">
-        <v>0.06206961981636838</v>
+        <v>0.06147233465173894</v>
       </c>
       <c r="D236">
-        <v>0.02454636797243535</v>
+        <v>0.02413477423915789</v>
       </c>
       <c r="E236">
-        <v>0.02254334805422993</v>
+        <v>0.02214166667175791</v>
       </c>
       <c r="F236">
-        <v>0.04405508455441817</v>
+        <v>0.0435469479756268</v>
       </c>
       <c r="G236">
-        <v>0.02131606092709854</v>
+        <v>0.02092045302419233</v>
       </c>
       <c r="H236">
-        <v>-0.008587369862486234</v>
+        <v>-0.008834994565835324</v>
       </c>
       <c r="I236">
-        <v>0.04328083891352716</v>
+        <v>0.04277653384651076</v>
       </c>
       <c r="J236">
-        <v>0.0202312239551056</v>
+        <v>0.01984098458824608</v>
       </c>
       <c r="K236">
-        <v>0.01256399115525472</v>
+        <v>0.01221169464684026</v>
       </c>
       <c r="L236">
-        <v>0.02972247138016933</v>
+        <v>0.02928526264810109</v>
       </c>
       <c r="M236">
-        <v>0.008553598083920479</v>
+        <v>0.008221147819983914</v>
       </c>
       <c r="N236">
-        <v>0.008724363585764514</v>
+        <v>0.008391068254065836</v>
       </c>
       <c r="O236">
-        <v>-0.02170922801307991</v>
+        <v>-0.02189191653680055</v>
       </c>
       <c r="P236">
-        <v>0.04848017490739492</v>
+        <v>0.04795013987041757</v>
       </c>
       <c r="Q236">
-        <v>0.04709098983495671</v>
+        <v>0.04656782946240309</v>
       </c>
       <c r="R236">
-        <v>0.03737724628735192</v>
+        <v>0.03690215634725023</v>
       </c>
       <c r="S236">
-        <v>-0.002329952495740549</v>
+        <v>-0.002608543299581956</v>
       </c>
       <c r="T236">
-        <v>0.07863854346993224</v>
+        <v>0.07795926362205977</v>
       </c>
       <c r="U236">
-        <v>0.02209433352968673</v>
+        <v>0.02169487418676787</v>
       </c>
       <c r="V236">
-        <v>0.02448018195054524</v>
+        <v>0.02406891575223707</v>
       </c>
       <c r="W236">
-        <v>0.04594878867216114</v>
+        <v>0.04543128071400096</v>
       </c>
       <c r="X236">
-        <v>0.0252903845971154</v>
+        <v>0.02487510894648811</v>
       </c>
       <c r="Y236">
-        <v>0.0162813765168859</v>
+        <v>0.01591068377214418</v>
       </c>
       <c r="Z236">
-        <v>0.02682030914336561</v>
+        <v>0.02639746235044938</v>
       </c>
       <c r="AA236">
-        <v>0.02970379159542955</v>
+        <v>0.02926667530406929</v>
       </c>
       <c r="AB236">
-        <v>0.02755483588245498</v>
+        <v>0.02712835413481481</v>
       </c>
       <c r="AC236">
-        <v>0.02622832803888137</v>
+        <v>0.02580841078467042</v>
       </c>
     </row>
     <row r="237" spans="1:29">
@@ -22701,88 +22701,88 @@
         <v>241</v>
       </c>
       <c r="B242">
-        <v>0.02023003349610865</v>
+        <v>0.01920629843128038</v>
       </c>
       <c r="C242">
-        <v>0.08104296901617876</v>
+        <v>0.07953924481119914</v>
       </c>
       <c r="D242">
-        <v>0.001081738075888183</v>
+        <v>0.0002091381893820077</v>
       </c>
       <c r="E242">
-        <v>-0.003186653664885797</v>
+        <v>-0.004025563651965765</v>
       </c>
       <c r="F242">
-        <v>0.04265438744137288</v>
+        <v>0.04145365966477057</v>
       </c>
       <c r="G242">
-        <v>-0.00580197575399374</v>
+        <v>-0.006620243320344731</v>
       </c>
       <c r="H242">
-        <v>-0.06952553428826275</v>
+        <v>-0.06984083951927057</v>
       </c>
       <c r="I242">
-        <v>0.04100448687429797</v>
+        <v>0.03981678156319175</v>
       </c>
       <c r="J242">
-        <v>-0.008113739670694859</v>
+        <v>-0.00891376076423343</v>
       </c>
       <c r="K242">
-        <v>-0.02445244547188127</v>
+        <v>-0.02512350713792914</v>
       </c>
       <c r="L242">
-        <v>0.01211190149770688</v>
+        <v>0.011152241866242</v>
       </c>
       <c r="M242">
-        <v>-0.03299850560206551</v>
+        <v>-0.033602114249796</v>
       </c>
       <c r="N242">
-        <v>-0.03263460804365619</v>
+        <v>-0.03324108889077435</v>
       </c>
       <c r="O242">
-        <v>-0.09748792769460612</v>
+        <v>-0.09758252913861695</v>
       </c>
       <c r="P242">
-        <v>0.05208415843024401</v>
+        <v>0.05080900261246816</v>
       </c>
       <c r="Q242">
-        <v>0.04912383535222177</v>
+        <v>0.04787204500622651</v>
       </c>
       <c r="R242">
-        <v>0.02842405980144235</v>
+        <v>0.02733565027867122</v>
       </c>
       <c r="S242">
-        <v>-0.0561911144135355</v>
+        <v>-0.05661166660681133</v>
       </c>
       <c r="T242">
-        <v>0.1163509837960565</v>
+        <v>0.1145685777035852</v>
       </c>
       <c r="U242">
-        <v>-0.004143493819408497</v>
+        <v>-0.004974851582950766</v>
       </c>
       <c r="V242">
-        <v>0.0009406971073872179</v>
+        <v>6.92104401758889E-05</v>
       </c>
       <c r="W242">
-        <v>0.04668982959657904</v>
+        <v>0.0454572505634366</v>
       </c>
       <c r="X242">
-        <v>0.00266722126899999</v>
+        <v>0.001782107355534291</v>
       </c>
       <c r="Y242">
-        <v>-0.01653077837778835</v>
+        <v>-0.01726436480348712</v>
       </c>
       <c r="Z242">
-        <v>0.005927457094848633</v>
+        <v>0.005016610534580784</v>
       </c>
       <c r="AA242">
-        <v>0.01207209528401025</v>
+        <v>0.01111274983817252</v>
       </c>
       <c r="AB242">
-        <v>0.007492717548831396</v>
+        <v>0.006569516577236499</v>
       </c>
       <c r="AC242">
-        <v>0.00466595827793289</v>
+        <v>0.003765068575153584</v>
       </c>
     </row>
     <row r="243" spans="1:29">
@@ -23235,88 +23235,88 @@
         <v>247</v>
       </c>
       <c r="B248">
-        <v>0.07426890816957794</v>
+        <v>0.08056900577959066</v>
       </c>
       <c r="C248">
-        <v>0.1815329874182182</v>
+        <v>0.1843875425353503</v>
       </c>
       <c r="D248">
-        <v>0.04049444456465878</v>
+        <v>0.04787944730172012</v>
       </c>
       <c r="E248">
-        <v>0.03296569914181172</v>
+        <v>0.04059254064217768</v>
       </c>
       <c r="F248">
-        <v>0.1138218035875364</v>
+        <v>0.1188513809746221</v>
       </c>
       <c r="G248">
-        <v>0.02835269841379702</v>
+        <v>0.0361277189703708</v>
       </c>
       <c r="H248">
-        <v>-0.08404524413198522</v>
+        <v>-0.07265977085100825</v>
       </c>
       <c r="I248">
-        <v>0.110911648639981</v>
+        <v>0.1160347061800024</v>
       </c>
       <c r="J248">
-        <v>0.02427512468964521</v>
+        <v>0.03218112528756025</v>
       </c>
       <c r="K248">
-        <v>-0.00454368201473237</v>
+        <v>0.004288037834115463</v>
       </c>
       <c r="L248">
-        <v>0.05994985011752742</v>
+        <v>0.06670990527644148</v>
       </c>
       <c r="M248">
-        <v>-0.01961753535248472</v>
+        <v>-0.01030161238018226</v>
       </c>
       <c r="N248">
-        <v>-0.01897567953332725</v>
+        <v>-0.009680374287990807</v>
       </c>
       <c r="O248">
-        <v>-0.13336633604556</v>
+        <v>-0.1203965680111682</v>
       </c>
       <c r="P248">
-        <v>0.1304543784500504</v>
+        <v>0.1349496833774624</v>
       </c>
       <c r="Q248">
-        <v>0.1252328523630921</v>
+        <v>0.1298958834308515</v>
       </c>
       <c r="R248">
-        <v>0.08872183137521215</v>
+        <v>0.09455767141269752</v>
       </c>
       <c r="S248">
-        <v>-0.06052550679410676</v>
+        <v>-0.04989553577434069</v>
       </c>
       <c r="T248">
-        <v>0.243810554897444</v>
+        <v>0.2446646266597941</v>
       </c>
       <c r="U248">
-        <v>0.03127798949113827</v>
+        <v>0.0389590436912055</v>
       </c>
       <c r="V248">
-        <v>0.04024567134736196</v>
+        <v>0.04763866519102012</v>
       </c>
       <c r="W248">
-        <v>0.120939664013736</v>
+        <v>0.1257406011073642</v>
       </c>
       <c r="X248">
-        <v>0.0432909777926462</v>
+        <v>0.05058615013972723</v>
       </c>
       <c r="Y248">
-        <v>0.009428844055509705</v>
+        <v>0.01781173767431733</v>
       </c>
       <c r="Z248">
-        <v>0.04904150095030024</v>
+        <v>0.05615195468482447</v>
       </c>
       <c r="AA248">
-        <v>0.05987963846232564</v>
+        <v>0.06664194896378482</v>
       </c>
       <c r="AB248">
-        <v>0.0518023645715829</v>
+        <v>0.05882413369714194</v>
       </c>
       <c r="AC248">
-        <v>0.04681642321128764</v>
+        <v>0.05399835101199912</v>
       </c>
     </row>
     <row r="249" spans="1:29">
@@ -23769,88 +23769,88 @@
         <v>253</v>
       </c>
       <c r="B254">
-        <v>0.03734038267163466</v>
+        <v>0.03460924606512709</v>
       </c>
       <c r="C254">
-        <v>0.06597895380165412</v>
+        <v>0.06894598851948686</v>
       </c>
       <c r="D254">
-        <v>0.05203945883093246</v>
+        <v>0.05223297422207322</v>
       </c>
       <c r="E254">
-        <v>0.04597399593238192</v>
+        <v>0.04496067573802999</v>
       </c>
       <c r="F254">
-        <v>0.05079939086361021</v>
+        <v>0.0507461718873292</v>
       </c>
       <c r="G254">
-        <v>0.03322110392330346</v>
+        <v>0.02967036092183503</v>
       </c>
       <c r="H254">
-        <v>0.03352240762510414</v>
+        <v>0.03003161454591792</v>
       </c>
       <c r="I254">
-        <v>0.06531335209497816</v>
+        <v>0.06814795309112856</v>
       </c>
       <c r="J254">
-        <v>0.04759002642871418</v>
+        <v>0.04689824527315206</v>
       </c>
       <c r="K254">
-        <v>0.04025244412491139</v>
+        <v>0.03810071579238661</v>
       </c>
       <c r="L254">
-        <v>0.03971585173031172</v>
+        <v>0.03745735845543401</v>
       </c>
       <c r="M254">
-        <v>0.06317671008349454</v>
+        <v>0.0655861867888784</v>
       </c>
       <c r="N254">
-        <v>-0.006871345773647917</v>
+        <v>-0.01839922025100396</v>
       </c>
       <c r="O254">
-        <v>0.0155415004281383</v>
+        <v>0.00847307460637518</v>
       </c>
       <c r="P254">
-        <v>0.05537209068805227</v>
+        <v>0.05622869458303661</v>
       </c>
       <c r="Q254">
-        <v>0.05001066125883036</v>
+        <v>0.04980050999719857</v>
       </c>
       <c r="R254">
-        <v>0.04215219510003897</v>
+        <v>0.04037845722243994</v>
       </c>
       <c r="S254">
-        <v>0.01655959191957342</v>
+        <v>0.009693734155962115</v>
       </c>
       <c r="T254">
-        <v>0.08298868767819158</v>
+        <v>0.08934012231492768</v>
       </c>
       <c r="U254">
-        <v>0.03973381341530295</v>
+        <v>0.03747889394855587</v>
       </c>
       <c r="V254">
-        <v>0.04173467787811357</v>
+        <v>0.03987786725744394</v>
       </c>
       <c r="W254">
-        <v>0.05973907911322957</v>
+        <v>0.06146457580684896</v>
       </c>
       <c r="X254">
-        <v>0.04241414505172902</v>
+        <v>0.04069252694282781</v>
       </c>
       <c r="Y254">
-        <v>0.03485884356849049</v>
+        <v>0.03163395904091631</v>
       </c>
       <c r="Z254">
-        <v>0.04369719875648539</v>
+        <v>0.04223086781937915</v>
       </c>
       <c r="AA254">
-        <v>0.0461153983022039</v>
+        <v>0.0451302127143327</v>
       </c>
       <c r="AB254">
-        <v>0.04431320119669856</v>
+        <v>0.04296943529346255</v>
       </c>
       <c r="AC254">
-        <v>0.04320074058074275</v>
+        <v>0.04163563014350334</v>
       </c>
     </row>
     <row r="255" spans="1:29">
@@ -24570,88 +24570,88 @@
         <v>262</v>
       </c>
       <c r="B263">
-        <v>0.01468091869656056</v>
+        <v>0.01320303028624505</v>
       </c>
       <c r="C263">
-        <v>0.03210765166663496</v>
+        <v>0.03314948145980334</v>
       </c>
       <c r="D263">
-        <v>0.02362538991238743</v>
+        <v>0.02344077586289209</v>
       </c>
       <c r="E263">
-        <v>0.01993452133542355</v>
+        <v>0.01921624737640801</v>
       </c>
       <c r="F263">
-        <v>0.02287080152062876</v>
+        <v>0.02257708210352854</v>
       </c>
       <c r="G263">
-        <v>0.01217431421372645</v>
+        <v>0.01033399774789547</v>
       </c>
       <c r="H263">
-        <v>0.01235765922526131</v>
+        <v>0.01054385247664903</v>
       </c>
       <c r="I263">
-        <v>0.03170262925284179</v>
+        <v>0.0326858971600499</v>
       </c>
       <c r="J263">
-        <v>0.02091788505853748</v>
+        <v>0.02034179492009409</v>
       </c>
       <c r="K263">
-        <v>0.01645292460803935</v>
+        <v>0.01523124919872072</v>
       </c>
       <c r="L263">
-        <v>0.01612640509238309</v>
+        <v>0.01485751847205868</v>
       </c>
       <c r="M263">
-        <v>0.03040247046985916</v>
+        <v>0.03119774939723229</v>
       </c>
       <c r="N263">
-        <v>-0.01222216883051812</v>
+        <v>-0.01758995441710345</v>
       </c>
       <c r="O263">
-        <v>0.001416175208527136</v>
+        <v>-0.001979652478687698</v>
       </c>
       <c r="P263">
-        <v>0.02565331530007246</v>
+        <v>0.02576191745601458</v>
       </c>
       <c r="Q263">
-        <v>0.02239085508246016</v>
+        <v>0.02202774057110864</v>
       </c>
       <c r="R263">
-        <v>0.01760893385175765</v>
+        <v>0.01655440494888948</v>
       </c>
       <c r="S263">
-        <v>0.00203568965566194</v>
+        <v>-0.001270562903934459</v>
       </c>
       <c r="T263">
-        <v>0.04245817120941095</v>
+        <v>0.04499657483269621</v>
       </c>
       <c r="U263">
-        <v>0.01613733487957861</v>
+        <v>0.01487002858895822</v>
       </c>
       <c r="V263">
-        <v>0.01735487225406592</v>
+        <v>0.0162636087760132</v>
       </c>
       <c r="W263">
-        <v>0.02831065252627222</v>
+        <v>0.02880347707164034</v>
       </c>
       <c r="X263">
-        <v>0.01776833188313644</v>
+        <v>0.01673685022165047</v>
       </c>
       <c r="Y263">
-        <v>0.01317088807705241</v>
+        <v>0.0114746654760239</v>
       </c>
       <c r="Z263">
-        <v>0.01854907733993811</v>
+        <v>0.01763048307640382</v>
       </c>
       <c r="AA263">
-        <v>0.02002056547949191</v>
+        <v>0.01931473257850397</v>
       </c>
       <c r="AB263">
-        <v>0.01892391831876251</v>
+        <v>0.01805952203022317</v>
       </c>
       <c r="AC263">
-        <v>0.0182469797240969</v>
+        <v>0.01728470539366934</v>
       </c>
     </row>
     <row r="264" spans="1:29">
@@ -25015,88 +25015,88 @@
         <v>267</v>
       </c>
       <c r="B268">
-        <v>0.0004761902418342276</v>
+        <v>-0.003923164199161479</v>
       </c>
       <c r="C268">
-        <v>0.06121554437801695</v>
+        <v>0.06172749983631169</v>
       </c>
       <c r="D268">
-        <v>0.03165136264345059</v>
+        <v>0.02977279451975514</v>
       </c>
       <c r="E268">
-        <v>0.01878716291357082</v>
+        <v>0.01586841133092464</v>
       </c>
       <c r="F268">
-        <v>0.02902131077814752</v>
+        <v>0.02693007987682772</v>
       </c>
       <c r="G268">
-        <v>-0.008260360528964325</v>
+        <v>-0.0133661417816458</v>
       </c>
       <c r="H268">
-        <v>-0.007621327521237529</v>
+        <v>-0.01267543734636669</v>
       </c>
       <c r="I268">
-        <v>0.05980387416612356</v>
+        <v>0.06020168369736972</v>
       </c>
       <c r="J268">
-        <v>0.0222145911943312</v>
+        <v>0.01957297727117784</v>
       </c>
       <c r="K268">
-        <v>0.006652361918622125</v>
+        <v>0.00275240516677399</v>
       </c>
       <c r="L268">
-        <v>0.005514306694623619</v>
+        <v>0.001522328189053318</v>
       </c>
       <c r="M268">
-        <v>0.05527228440179648</v>
+        <v>0.05530367512623145</v>
       </c>
       <c r="N268">
-        <v>-0.09329216917871963</v>
+        <v>-0.1052735184962142</v>
       </c>
       <c r="O268">
-        <v>-0.04575691344024084</v>
+        <v>-0.05389462010802509</v>
       </c>
       <c r="P268">
-        <v>0.03871951927934301</v>
+        <v>0.03741247365780921</v>
       </c>
       <c r="Q268">
-        <v>0.02734849942995152</v>
+        <v>0.02512200704864264</v>
       </c>
       <c r="R268">
-        <v>0.0106815310669348</v>
+        <v>0.007107368005280605</v>
       </c>
       <c r="S268">
-        <v>-0.04359764999931824</v>
+        <v>-0.05156076126576183</v>
       </c>
       <c r="T268">
-        <v>0.09729137529146137</v>
+        <v>0.1007203783214684</v>
       </c>
       <c r="U268">
-        <v>0.005552401512294927</v>
+        <v>0.001563503307096634</v>
       </c>
       <c r="V268">
-        <v>0.009796021580957021</v>
+        <v>0.006150257305127131</v>
       </c>
       <c r="W268">
-        <v>0.04798143584847717</v>
+        <v>0.04742329747462999</v>
       </c>
       <c r="X268">
-        <v>0.01123709896902822</v>
+        <v>0.007707858448551562</v>
       </c>
       <c r="Y268">
-        <v>-0.004786889459466391</v>
+        <v>-0.009611810089061951</v>
       </c>
       <c r="Z268">
-        <v>0.01395831899760881</v>
+        <v>0.01064911300095258</v>
       </c>
       <c r="AA268">
-        <v>0.01908706225482357</v>
+        <v>0.01619256016617403</v>
       </c>
       <c r="AB268">
-        <v>0.01526479445670181</v>
+        <v>0.01206122846802191</v>
       </c>
       <c r="AC268">
-        <v>0.01290538417019252</v>
+        <v>0.009511039150990823</v>
       </c>
     </row>
     <row r="269" spans="1:29">
@@ -25104,88 +25104,88 @@
         <v>268</v>
       </c>
       <c r="B269">
-        <v>0.03676595341818025</v>
+        <v>0.0358494585653005</v>
       </c>
       <c r="C269">
-        <v>0.1061925048227308</v>
+        <v>0.1055985796930136</v>
       </c>
       <c r="D269">
-        <v>0.01490547085912481</v>
+        <v>0.01388740780698101</v>
       </c>
       <c r="E269">
-        <v>0.01003249907982627</v>
+        <v>0.008991795220584511</v>
       </c>
       <c r="F269">
-        <v>0.06236651929418399</v>
+        <v>0.06156896981998663</v>
       </c>
       <c r="G269">
-        <v>0.007046739686596774</v>
+        <v>0.005992163388620556</v>
       </c>
       <c r="H269">
-        <v>-0.06570269880745885</v>
+        <v>-0.06709528363042309</v>
       </c>
       <c r="I269">
-        <v>0.06048292486558385</v>
+        <v>0.05967662383278114</v>
       </c>
       <c r="J269">
-        <v>0.004407534803203732</v>
+        <v>0.003340696228456131</v>
       </c>
       <c r="K269">
-        <v>-0.01424540455071925</v>
+        <v>-0.01539890843379394</v>
       </c>
       <c r="L269">
-        <v>0.02749795963238517</v>
+        <v>0.02653840381609482</v>
       </c>
       <c r="M269">
-        <v>-0.02400193871340246</v>
+        <v>-0.02520077341675</v>
       </c>
       <c r="N269">
-        <v>-0.023586498275791</v>
+        <v>-0.02478340275929843</v>
       </c>
       <c r="O269">
-        <v>-0.09762571858306343</v>
+        <v>-0.09916662417730614</v>
       </c>
       <c r="P269">
-        <v>0.0731319341634586</v>
+        <v>0.07238440297223596</v>
       </c>
       <c r="Q269">
-        <v>0.06975230743449466</v>
+        <v>0.06898907381766829</v>
       </c>
       <c r="R269">
-        <v>0.0461205912700192</v>
+        <v>0.04524755994630959</v>
       </c>
       <c r="S269">
-        <v>-0.05047957598062078</v>
+        <v>-0.05180143111275955</v>
       </c>
       <c r="T269">
-        <v>0.1465015884435799</v>
+        <v>0.1460949474246454</v>
       </c>
       <c r="U269">
-        <v>0.008940130957718692</v>
+        <v>0.007894351736448839</v>
       </c>
       <c r="V269">
-        <v>0.01474445268156047</v>
+        <v>0.01372564150657446</v>
       </c>
       <c r="W269">
-        <v>0.06697354623397127</v>
+        <v>0.06619740193365199</v>
       </c>
       <c r="X269">
-        <v>0.01671552376096672</v>
+        <v>0.01570587057870187</v>
       </c>
       <c r="Y269">
-        <v>-0.005201703189908093</v>
+        <v>-0.006313188217295681</v>
       </c>
       <c r="Z269">
-        <v>0.02043754323295121</v>
+        <v>0.01944518330184739</v>
       </c>
       <c r="AA269">
-        <v>0.0274525152196497</v>
+        <v>0.02649274825947651</v>
       </c>
       <c r="AB269">
-        <v>0.02222450902305156</v>
+        <v>0.02124045169446152</v>
       </c>
       <c r="AC269">
-        <v>0.01899736423632185</v>
+        <v>0.01799831294390383</v>
       </c>
     </row>
     <row r="270" spans="1:29">
@@ -25460,88 +25460,88 @@
         <v>272</v>
       </c>
       <c r="B273">
-        <v>0.008669259795025398</v>
+        <v>0.001244583502886545</v>
       </c>
       <c r="C273">
-        <v>0.1098448967785504</v>
+        <v>0.1110981990255839</v>
       </c>
       <c r="D273">
-        <v>0.06059881964402931</v>
+        <v>0.05762821568940092</v>
       </c>
       <c r="E273">
-        <v>0.03917047848920396</v>
+        <v>0.0343619351826156</v>
       </c>
       <c r="F273">
-        <v>0.05621785154589751</v>
+        <v>0.05287148571548696</v>
       </c>
       <c r="G273">
-        <v>-0.005883514132939218</v>
+        <v>-0.01455640257967877</v>
       </c>
       <c r="H273">
-        <v>-0.004819054812787486</v>
+        <v>-0.01340064306699548</v>
       </c>
       <c r="I273">
-        <v>0.1074934290204516</v>
+        <v>0.1085450425275005</v>
       </c>
       <c r="J273">
-        <v>0.04487966398274389</v>
+        <v>0.04056080565038667</v>
       </c>
       <c r="K273">
-        <v>0.01895712196289752</v>
+        <v>0.01241485026704793</v>
       </c>
       <c r="L273">
-        <v>0.01706142412665915</v>
+        <v>0.01035655572640423</v>
       </c>
       <c r="M273">
-        <v>0.09994500366304901</v>
+        <v>0.1003491779721935</v>
       </c>
       <c r="N273">
-        <v>-0.1475239304059082</v>
+        <v>-0.1683455191657124</v>
       </c>
       <c r="O273">
-        <v>-0.0683428155107407</v>
+        <v>-0.08237292722869641</v>
       </c>
       <c r="P273">
-        <v>0.07237249192135339</v>
+        <v>0.07041173261308493</v>
       </c>
       <c r="Q273">
-        <v>0.05343139199073773</v>
+        <v>0.04984602755413223</v>
       </c>
       <c r="R273">
-        <v>0.02566864797255689</v>
+        <v>0.01970203342514121</v>
       </c>
       <c r="S273">
-        <v>-0.06474605592780597</v>
+        <v>-0.07846766845166861</v>
       </c>
       <c r="T273">
-        <v>0.169937652526234</v>
+        <v>0.1763451960539331</v>
       </c>
       <c r="U273">
-        <v>0.0171248799782809</v>
+        <v>0.0104254542768315</v>
       </c>
       <c r="V273">
-        <v>0.02419362428202038</v>
+        <v>0.01810049485105295</v>
       </c>
       <c r="W273">
-        <v>0.08780038577859464</v>
+        <v>0.08716289890813221</v>
       </c>
       <c r="X273">
-        <v>0.026594076587683</v>
+        <v>0.02070683737113783</v>
       </c>
       <c r="Y273">
-        <v>-9.763357826024499E-05</v>
+        <v>-0.008274258806099631</v>
       </c>
       <c r="Z273">
-        <v>0.03112690663962386</v>
+        <v>0.02562845471501206</v>
       </c>
       <c r="AA273">
-        <v>0.03967003116495609</v>
+        <v>0.03490433520312988</v>
       </c>
       <c r="AB273">
-        <v>0.03330314786999176</v>
+        <v>0.02799135525641813</v>
       </c>
       <c r="AC273">
-        <v>0.02937299678363282</v>
+        <v>0.02372410951170106</v>
       </c>
     </row>
     <row r="274" spans="1:29">
@@ -25549,88 +25549,88 @@
         <v>273</v>
       </c>
       <c r="B274">
-        <v>0.04761859896437012</v>
+        <v>0.04732037859321946</v>
       </c>
       <c r="C274">
-        <v>0.07427456225955563</v>
+        <v>0.07428539348568916</v>
       </c>
       <c r="D274">
-        <v>0.03922538039135267</v>
+        <v>0.03882984830133364</v>
       </c>
       <c r="E274">
-        <v>0.03735442822305957</v>
+        <v>0.03693720414803701</v>
       </c>
       <c r="F274">
-        <v>0.05744780307318902</v>
+        <v>0.05726354336428205</v>
       </c>
       <c r="G274">
-        <v>0.03620806143421508</v>
+        <v>0.03577754628119837</v>
       </c>
       <c r="H274">
-        <v>0.00827629292474252</v>
+        <v>0.007521934375888585</v>
       </c>
       <c r="I274">
-        <v>0.05672460678969207</v>
+        <v>0.05653196227907713</v>
       </c>
       <c r="J274">
-        <v>0.03519475244684706</v>
+        <v>0.03475248889976105</v>
       </c>
       <c r="K274">
-        <v>0.02803305340366366</v>
+        <v>0.02750775648411783</v>
       </c>
       <c r="L274">
-        <v>0.04406020095703415</v>
+        <v>0.04372072420449663</v>
       </c>
       <c r="M274">
-        <v>0.02428708285972474</v>
+        <v>0.02371835482620401</v>
       </c>
       <c r="N274">
-        <v>0.02444658905486583</v>
+        <v>0.02387971035028659</v>
       </c>
       <c r="O274">
-        <v>-0.003980384473095538</v>
+        <v>-0.004876848024318047</v>
       </c>
       <c r="P274">
-        <v>0.06158112811681231</v>
+        <v>0.06144479054422736</v>
       </c>
       <c r="Q274">
-        <v>0.06028353801308168</v>
+        <v>0.06013215606600772</v>
       </c>
       <c r="R274">
-        <v>0.05121026351019154</v>
+        <v>0.05095368521561874</v>
       </c>
       <c r="S274">
-        <v>0.01412113175226491</v>
+        <v>0.01343453878199882</v>
       </c>
       <c r="T274">
-        <v>0.08975102525134254</v>
+        <v>0.08994129195894621</v>
       </c>
       <c r="U274">
-        <v>0.03693501916444079</v>
+        <v>0.03651293242367826</v>
       </c>
       <c r="V274">
-        <v>0.03916355829959987</v>
+        <v>0.03876730943877829</v>
       </c>
       <c r="W274">
-        <v>0.05921664710364236</v>
+        <v>0.05905289552895303</v>
       </c>
       <c r="X274">
-        <v>0.0399203407881711</v>
+        <v>0.03953286613049123</v>
       </c>
       <c r="Y274">
-        <v>0.03150533550106596</v>
+        <v>0.03102029652742664</v>
       </c>
       <c r="Z274">
-        <v>0.04134939080465631</v>
+        <v>0.04097848467932708</v>
       </c>
       <c r="AA274">
-        <v>0.04404275281113981</v>
+        <v>0.04370307376325476</v>
       </c>
       <c r="AB274">
-        <v>0.04203548702500733</v>
+        <v>0.04167253555997088</v>
       </c>
       <c r="AC274">
-        <v>0.04079644156987504</v>
+        <v>0.04041912450218615</v>
       </c>
     </row>
     <row r="275" spans="1:29">
@@ -26528,88 +26528,88 @@
         <v>284</v>
       </c>
       <c r="B285">
-        <v>0.01872425231060032</v>
+        <v>0.01796037747904064</v>
       </c>
       <c r="C285">
-        <v>0.02762640758049211</v>
+        <v>0.02819562447864963</v>
       </c>
       <c r="D285">
-        <v>0.02329338593461939</v>
+        <v>0.0232137357724219</v>
       </c>
       <c r="E285">
-        <v>0.02140796741071595</v>
+        <v>0.02104597709997353</v>
       </c>
       <c r="F285">
-        <v>0.02290791706676969</v>
+        <v>0.02277054320236585</v>
       </c>
       <c r="G285">
-        <v>0.0174437953055659</v>
+        <v>0.01648817290367985</v>
       </c>
       <c r="H285">
-        <v>0.01753745404030673</v>
+        <v>0.01659585697059176</v>
       </c>
       <c r="I285">
-        <v>0.02741950864989137</v>
+        <v>0.02795774257315021</v>
       </c>
       <c r="J285">
-        <v>0.021910302332871</v>
+        <v>0.02162353633691198</v>
       </c>
       <c r="K285">
-        <v>0.01962945191343115</v>
+        <v>0.01900113011006435</v>
       </c>
       <c r="L285">
-        <v>0.01946265487625767</v>
+        <v>0.01880935532940561</v>
       </c>
       <c r="M285">
-        <v>0.02675534426626877</v>
+        <v>0.02719412002236057</v>
       </c>
       <c r="N285">
-        <v>0.004981259701669495</v>
+        <v>0.002159381023502783</v>
       </c>
       <c r="O285">
-        <v>0.01194817980472457</v>
+        <v>0.01016959269914983</v>
       </c>
       <c r="P285">
-        <v>0.02432931772446941</v>
+        <v>0.02440479764703588</v>
       </c>
       <c r="Q285">
-        <v>0.02266274445058596</v>
+        <v>0.022488656152758</v>
       </c>
       <c r="R285">
-        <v>0.02021997991421491</v>
+        <v>0.01968008927949711</v>
       </c>
       <c r="S285">
-        <v>0.01226464840556936</v>
+        <v>0.01053345225889287</v>
       </c>
       <c r="T285">
-        <v>0.03291379749184667</v>
+        <v>0.03427479745252346</v>
       </c>
       <c r="U285">
-        <v>0.01946823817536763</v>
+        <v>0.01881577472378041</v>
       </c>
       <c r="V285">
-        <v>0.02009019679338254</v>
+        <v>0.01953087122411314</v>
       </c>
       <c r="W285">
-        <v>0.02568677403212711</v>
+        <v>0.02596553211850086</v>
       </c>
       <c r="X285">
-        <v>0.02030140573438934</v>
+        <v>0.01977370856116137</v>
       </c>
       <c r="Y285">
-        <v>0.0179528784070559</v>
+        <v>0.01707349085524379</v>
       </c>
       <c r="Z285">
-        <v>0.02070023650173089</v>
+        <v>0.02023226396611938</v>
       </c>
       <c r="AA285">
-        <v>0.02145192162358401</v>
+        <v>0.02109651342648533</v>
       </c>
       <c r="AB285">
-        <v>0.02089171775072594</v>
+        <v>0.0204524194026221</v>
       </c>
       <c r="AC285">
-        <v>0.02054591498389386</v>
+        <v>0.02005483290537854</v>
       </c>
     </row>
     <row r="286" spans="1:29">
@@ -26795,88 +26795,88 @@
         <v>287</v>
       </c>
       <c r="B288">
-        <v>0.01556050830946731</v>
+        <v>0.01307291100592102</v>
       </c>
       <c r="C288">
-        <v>0.0607509433396126</v>
+        <v>0.05787211823369033</v>
       </c>
       <c r="D288">
-        <v>0.03875501906784862</v>
+        <v>0.03606661959310981</v>
       </c>
       <c r="E288">
-        <v>0.02918397916504469</v>
+        <v>0.02657843919155053</v>
       </c>
       <c r="F288">
-        <v>0.03679824508440435</v>
+        <v>0.03412678601718272</v>
       </c>
       <c r="G288">
-        <v>0.009060463394433414</v>
+        <v>0.006629139023107343</v>
       </c>
       <c r="H288">
-        <v>0.009535907692919843</v>
+        <v>0.007100467250838422</v>
       </c>
       <c r="I288">
-        <v>0.05970065243840334</v>
+        <v>0.05683092003098821</v>
       </c>
       <c r="J288">
-        <v>0.03173400586922918</v>
+        <v>0.02910638951291612</v>
       </c>
       <c r="K288">
-        <v>0.02015561619074529</v>
+        <v>0.01762823759372674</v>
       </c>
       <c r="L288">
-        <v>0.01930889644220279</v>
+        <v>0.01678884816422697</v>
       </c>
       <c r="M288">
-        <v>0.05632912312696301</v>
+        <v>0.05348857910868999</v>
       </c>
       <c r="N288">
-        <v>-0.05420369999569792</v>
+        <v>-0.05608732661647645</v>
       </c>
       <c r="O288">
-        <v>-0.01883719146689863</v>
+        <v>-0.02102699707002604</v>
       </c>
       <c r="P288">
-        <v>0.04401376898015483</v>
+        <v>0.04127984285425491</v>
       </c>
       <c r="Q288">
-        <v>0.03555366364913175</v>
+        <v>0.03289297931464891</v>
       </c>
       <c r="R288">
-        <v>0.02315334162282761</v>
+        <v>0.02060001077436165</v>
       </c>
       <c r="S288">
-        <v>-0.01723068682706985</v>
+        <v>-0.01943440044589412</v>
       </c>
       <c r="T288">
-        <v>0.08759157271801012</v>
+        <v>0.08448037984578745</v>
       </c>
       <c r="U288">
-        <v>0.01933723920954768</v>
+        <v>0.01681694555932496</v>
       </c>
       <c r="V288">
-        <v>0.02249451738171145</v>
+        <v>0.01994689018181254</v>
       </c>
       <c r="W288">
-        <v>0.05090468912450901</v>
+        <v>0.04811110613665089</v>
       </c>
       <c r="X288">
-        <v>0.02356668739413918</v>
+        <v>0.02100977808138927</v>
       </c>
       <c r="Y288">
-        <v>0.01164474620296149</v>
+        <v>0.009191048882952274</v>
       </c>
       <c r="Z288">
-        <v>0.02559129102473731</v>
+        <v>0.0230168540818915</v>
       </c>
       <c r="AA288">
-        <v>0.02940710603047167</v>
+        <v>0.02679963437756009</v>
       </c>
       <c r="AB288">
-        <v>0.02656331641407958</v>
+        <v>0.02398046434186685</v>
       </c>
       <c r="AC288">
-        <v>0.02480790134952527</v>
+        <v>0.02224024645736856</v>
       </c>
     </row>
     <row r="289" spans="1:29">
